--- a/src/attributions/attributions_saliency_traj_332.xlsx
+++ b/src/attributions/attributions_saliency_traj_332.xlsx
@@ -2137,2278 +2137,2278 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.0006225608522072434</v>
+        <v>0.000364329491276294</v>
       </c>
       <c r="B4" t="n">
-        <v>0.004281850531697273</v>
+        <v>0.0003797300742007792</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0004303362802602351</v>
+        <v>0.0002274048456456512</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001557856099680066</v>
+        <v>8.5528998170048e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0003523535560816526</v>
+        <v>0.0003546567750163376</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002946384716778994</v>
+        <v>0.0007564583793282509</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0001776703866198659</v>
+        <v>8.629045623820275e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0004278387932572514</v>
+        <v>0.0001993759069591761</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0001655575906625018</v>
+        <v>0.00010945629037451</v>
       </c>
       <c r="J4" t="n">
-        <v>0.00120028795208782</v>
+        <v>0.0003381627611815929</v>
       </c>
       <c r="K4" t="n">
-        <v>0.003126270137727261</v>
+        <v>0.000673026661388576</v>
       </c>
       <c r="L4" t="n">
-        <v>7.736961561022326e-05</v>
+        <v>0.0002188094222219661</v>
       </c>
       <c r="M4" t="n">
-        <v>0.001658197725191712</v>
+        <v>8.49616335472092e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0003607486141845584</v>
+        <v>0.0001279769639950246</v>
       </c>
       <c r="O4" t="n">
-        <v>0.002638787729665637</v>
+        <v>0.0005776147008873522</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0001675623934715986</v>
+        <v>0.0003614525776356459</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0005399444489739835</v>
+        <v>0.0001922124647535384</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0002648200024850667</v>
+        <v>0.0001087826167349704</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0001871733693405986</v>
+        <v>0.0002125233586411923</v>
       </c>
       <c r="T4" t="n">
-        <v>0.000243969407165423</v>
+        <v>0.0003287199069745839</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0002417365612927824</v>
+        <v>0.0002498488174751401</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0001861797936726362</v>
+        <v>0.0001436825550626963</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0004402823396958411</v>
+        <v>0.0003215984324924648</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0003386071184650064</v>
+        <v>0.0003035124973393977</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0004286448529455811</v>
+        <v>0.0002669263631105423</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0003007501945830882</v>
+        <v>0.0001184794527944177</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0002073796349577606</v>
+        <v>9.568629320710897e-05</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0002769735874608159</v>
+        <v>8.298943430418149e-05</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.0004531377635430545</v>
+        <v>4.747732600662857e-05</v>
       </c>
       <c r="AD4" t="n">
-        <v>8.11280042398721e-05</v>
+        <v>0.0002132826775778085</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.0003977475862484425</v>
+        <v>8.904604328563437e-05</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.00046972167911008</v>
+        <v>0.000115584785817191</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.000350992864696309</v>
+        <v>0.0001025373276206665</v>
       </c>
       <c r="AH4" t="n">
-        <v>3.532343544065952e-05</v>
+        <v>0.0001015441594063304</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.000259376218309626</v>
+        <v>0.000428708444815129</v>
       </c>
       <c r="AJ4" t="n">
-        <v>4.010149950772757e-06</v>
+        <v>0.0002355389733565971</v>
       </c>
       <c r="AK4" t="n">
-        <v>6.146985833765939e-05</v>
+        <v>5.046404112363234e-05</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.0003632479056250304</v>
+        <v>1.394228547724197e-05</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.0003817008691839874</v>
+        <v>2.147635677829385e-05</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.000297080259770155</v>
+        <v>0.0001606623991392553</v>
       </c>
       <c r="AO4" t="n">
-        <v>7.919420750113204e-05</v>
+        <v>0.0002493730571586639</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.0006856743711978197</v>
+        <v>0.0002149655192624778</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.000343587773386389</v>
+        <v>0.0001223741419380531</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.0002621765597723424</v>
+        <v>0.0001564512494951487</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.0007047134567983449</v>
+        <v>8.532782521797344e-05</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.0004212841740809381</v>
+        <v>1.335572505922755e-05</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.002248626668006182</v>
+        <v>0.0008075984078459442</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.0006276690401136875</v>
+        <v>0.0001739993458613753</v>
       </c>
       <c r="AW4" t="n">
-        <v>9.786563168745488e-05</v>
+        <v>0.0001100854933611117</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.0004998843651264906</v>
+        <v>8.659437298774719e-06</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.001277488307096064</v>
+        <v>0.0004855216830037534</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.0006292493781074882</v>
+        <v>1.102097303373739e-05</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.0001928466372191906</v>
+        <v>0.0001485626708017662</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.001172668766230345</v>
+        <v>8.005418203538284e-05</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.0009304319391958416</v>
+        <v>0.0003519520978443325</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.0006028722273185849</v>
+        <v>6.32380397291854e-05</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.000728389248251915</v>
+        <v>2.206451608799398e-05</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.0003465021145530045</v>
+        <v>0.0001615057844901457</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.00134048645850271</v>
+        <v>0.0001438968611182645</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.001193877193145454</v>
+        <v>0.0001080395159078762</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.0007401012117043138</v>
+        <v>2.270490949740633e-05</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.0005810440052300692</v>
+        <v>0.0003425363975111395</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.0004406453226692975</v>
+        <v>2.157325252483133e-05</v>
       </c>
       <c r="BL4" t="n">
-        <v>3.19238388328813e-05</v>
+        <v>0.0001112660975195467</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.0001312353415414691</v>
+        <v>0.000203833871637471</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.0001734034594846889</v>
+        <v>1.201738177769585e-05</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.0007830216200090945</v>
+        <v>5.121189678902738e-05</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.0004274857346899807</v>
+        <v>7.008208194747567e-05</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.0001529118308098987</v>
+        <v>0.0001064422031049617</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.0004687545588240027</v>
+        <v>0.0001664950395934284</v>
       </c>
       <c r="BS4" t="n">
-        <v>9.368159953737631e-05</v>
+        <v>0.0001165622961707413</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.0001862413046183065</v>
+        <v>5.781662912340835e-05</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.0002005932328756899</v>
+        <v>0.00017761584604159</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.001225778949446976</v>
+        <v>8.111116767395288e-05</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.0004907551337964833</v>
+        <v>0.0002603174070827663</v>
       </c>
       <c r="BX4" t="n">
-        <v>9.028444765135646e-06</v>
+        <v>0.0002924528962466866</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.0003190912248101085</v>
+        <v>0.0001962390961125493</v>
       </c>
       <c r="BZ4" t="n">
-        <v>8.539282134734094e-06</v>
+        <v>0.000516265572514385</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.697756670182571e-05</v>
+        <v>0.0001920827344292775</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.0003142269561067224</v>
+        <v>6.916865822859108e-05</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.0006653839373029768</v>
+        <v>4.283218731870875e-05</v>
       </c>
       <c r="CD4" t="n">
-        <v>6.950058013899252e-05</v>
+        <v>5.89510818826966e-05</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.0007297704578377306</v>
+        <v>0.0001347971265204251</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.0004069185815751553</v>
+        <v>1.062817136698868e-05</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.0003841637808363885</v>
+        <v>7.617377559654415e-05</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.0002763466618489474</v>
+        <v>0.0001030127750709653</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.0004876614257227629</v>
+        <v>0.0001594719069544226</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.0002835546038113534</v>
+        <v>3.487407229840755e-05</v>
       </c>
       <c r="CK4" t="n">
-        <v>4.584499038173817e-05</v>
+        <v>8.04255687398836e-05</v>
       </c>
       <c r="CL4" t="n">
-        <v>0.000421794451540336</v>
+        <v>6.296318315435201e-05</v>
       </c>
       <c r="CM4" t="n">
-        <v>6.134858995210379e-05</v>
+        <v>3.891023879987188e-05</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.000452908338047564</v>
+        <v>0.0002693210262805223</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.0003451395605225116</v>
+        <v>8.764366793911904e-05</v>
       </c>
       <c r="CP4" t="n">
-        <v>0.000803353323135525</v>
+        <v>0.0001475121680414304</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.0004164283454883844</v>
+        <v>3.839547571260482e-05</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.0001025168021442369</v>
+        <v>0.0002379661600571126</v>
       </c>
       <c r="CS4" t="n">
-        <v>0.0002705620718188584</v>
+        <v>0.0003258305659983307</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.0003884886973537505</v>
+        <v>0.0002537484688218683</v>
       </c>
       <c r="CU4" t="n">
-        <v>0.000269984477199614</v>
+        <v>2.299722837051377e-05</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.044658711180091e-05</v>
+        <v>8.845966658554971e-05</v>
       </c>
       <c r="CW4" t="n">
-        <v>0.0006774021894671023</v>
+        <v>0.0001059074566001073</v>
       </c>
       <c r="CX4" t="n">
-        <v>0.0003819148114416748</v>
+        <v>2.930021946667694e-05</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.0005295614246279001</v>
+        <v>8.16778265289031e-05</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.0004002191417384893</v>
+        <v>0.0001156664729933254</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.000485624885186553</v>
+        <v>0.0001331981329713017</v>
       </c>
       <c r="DB4" t="n">
-        <v>0.0001891615684144199</v>
+        <v>3.027710408787243e-05</v>
       </c>
       <c r="DC4" t="n">
-        <v>0.0001109729200834408</v>
+        <v>2.704951111809351e-05</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.0004087435663677752</v>
+        <v>2.97436308756005e-05</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.0002130679640686139</v>
+        <v>0.000272530858637765</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.0007463632500730455</v>
+        <v>5.539583071367815e-05</v>
       </c>
       <c r="DG4" t="n">
-        <v>8.660105231683701e-05</v>
+        <v>0.000102727317425888</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.0008360838983207941</v>
+        <v>7.978050416568294e-05</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.0005858260556124151</v>
+        <v>0.0001635434746276587</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.001390496734529734</v>
+        <v>0.0005840096273459494</v>
       </c>
       <c r="DK4" t="n">
-        <v>0.0006300659733824432</v>
+        <v>3.597950853873044e-05</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.0006133053102530539</v>
+        <v>9.042119927471504e-05</v>
       </c>
       <c r="DM4" t="n">
-        <v>0.001183728338219225</v>
+        <v>0.0001504082174506038</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.0002655905263964087</v>
+        <v>9.040351869771257e-06</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.0002609648217912763</v>
+        <v>1.729261202854104e-05</v>
       </c>
       <c r="DP4" t="n">
-        <v>0.0003505917848087847</v>
+        <v>0.0001304490579059348</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0.0003288163570687175</v>
+        <v>0.0002489925245754421</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.434288611169904e-05</v>
+        <v>2.46431227424182e-06</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.0001150826137745753</v>
+        <v>0.0001402840425726026</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.000212687358725816</v>
+        <v>5.903446435695514e-05</v>
       </c>
       <c r="DU4" t="n">
-        <v>7.455582090187818e-05</v>
+        <v>2.453058186802082e-05</v>
       </c>
       <c r="DV4" t="n">
-        <v>5.032867920817807e-05</v>
+        <v>3.187527909176424e-05</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.000233006154303439</v>
+        <v>2.984226375701837e-05</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.0002571231452748179</v>
+        <v>0.0001420417538611218</v>
       </c>
       <c r="DY4" t="n">
-        <v>0.0003802280116360635</v>
+        <v>0.0001416070008417591</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0.0003506817738525569</v>
+        <v>7.358405855484307e-05</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.0003044079639948905</v>
+        <v>0.0001633123029023409</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.0001737618586048484</v>
+        <v>0.0001101737143471837</v>
       </c>
       <c r="EC4" t="n">
-        <v>0.000176887697307393</v>
+        <v>3.009791907970794e-05</v>
       </c>
       <c r="ED4" t="n">
-        <v>0.0002106548490701243</v>
+        <v>0.0003126865776721388</v>
       </c>
       <c r="EE4" t="n">
-        <v>0.000443166820332408</v>
+        <v>0.0002609679650049657</v>
       </c>
       <c r="EF4" t="n">
-        <v>0.000102112753666006</v>
+        <v>0.0001268885971512645</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.0004240001435391605</v>
+        <v>0.0001303055178141221</v>
       </c>
       <c r="EH4" t="n">
-        <v>0.0001547548454254866</v>
+        <v>0.0001031230713124387</v>
       </c>
       <c r="EI4" t="n">
-        <v>3.144476795569062e-05</v>
+        <v>0.0001023462391458452</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.0001284265163121745</v>
+        <v>0.0002177409478463233</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.0001508293498773128</v>
+        <v>9.327147563453764e-05</v>
       </c>
       <c r="EL4" t="n">
-        <v>0.0005589485517702997</v>
+        <v>6.618965926463716e-06</v>
       </c>
       <c r="EM4" t="n">
-        <v>2.321507054148242e-06</v>
+        <v>5.102958675706759e-05</v>
       </c>
       <c r="EN4" t="n">
-        <v>0.0001131843237089925</v>
+        <v>8.925167639972642e-05</v>
       </c>
       <c r="EO4" t="n">
-        <v>0.0002510190533939749</v>
+        <v>6.601729546673596e-05</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.0003441189764998853</v>
+        <v>2.256502375530545e-05</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0.0002967105829156935</v>
+        <v>0.0002314059529453516</v>
       </c>
       <c r="ER4" t="n">
-        <v>0.0005601372686214745</v>
+        <v>5.22175723745022e-05</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.0007496624020859599</v>
+        <v>0.0001179623723146506</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.00117875449359417</v>
+        <v>0.0003459563013166189</v>
       </c>
       <c r="EU4" t="n">
-        <v>0.0004086221451871097</v>
+        <v>2.915343065978959e-05</v>
       </c>
       <c r="EV4" t="n">
-        <v>0.0002788033743854612</v>
+        <v>8.580516441725194e-05</v>
       </c>
       <c r="EW4" t="n">
-        <v>0.0002877129300031811</v>
+        <v>2.997800038428977e-05</v>
       </c>
       <c r="EX4" t="n">
-        <v>2.339919592486694e-05</v>
+        <v>0.0001156071812147275</v>
       </c>
       <c r="EY4" t="n">
-        <v>0.0007077741320244968</v>
+        <v>0.0001308528444496915</v>
       </c>
       <c r="EZ4" t="n">
-        <v>0.000187614539754577</v>
+        <v>5.363195668905973e-05</v>
       </c>
       <c r="FA4" t="n">
-        <v>0.0003756557125598192</v>
+        <v>9.040268923854455e-05</v>
       </c>
       <c r="FB4" t="n">
-        <v>0.0004587035509757698</v>
+        <v>0.0001700651773717254</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.0003767275484278798</v>
+        <v>0.0001787245855666697</v>
       </c>
       <c r="FD4" t="n">
-        <v>0.0003960502799600363</v>
+        <v>3.418384949327447e-05</v>
       </c>
       <c r="FE4" t="n">
-        <v>8.943302964325994e-05</v>
+        <v>4.235922096995637e-05</v>
       </c>
       <c r="FF4" t="n">
-        <v>0.0005866654100827873</v>
+        <v>4.185659054201096e-05</v>
       </c>
       <c r="FG4" t="n">
-        <v>0.0001410535187460482</v>
+        <v>8.306593372253701e-05</v>
       </c>
       <c r="FH4" t="n">
-        <v>0.0003813348594121635</v>
+        <v>3.582270801416598e-05</v>
       </c>
       <c r="FI4" t="n">
-        <v>0.0002089562913170084</v>
+        <v>4.189075116300955e-05</v>
       </c>
       <c r="FJ4" t="n">
-        <v>0.0006419030833058059</v>
+        <v>3.6525925679598e-05</v>
       </c>
       <c r="FK4" t="n">
-        <v>0.0001743109751259908</v>
+        <v>0.0002607107162475586</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.0002382445672992617</v>
+        <v>0.0001225030864588916</v>
       </c>
       <c r="FM4" t="n">
-        <v>1.137758954428136e-05</v>
+        <v>7.004580402281135e-05</v>
       </c>
       <c r="FN4" t="n">
-        <v>0.0003261428792029619</v>
+        <v>6.544251664308831e-05</v>
       </c>
       <c r="FO4" t="n">
-        <v>0.0004760236188303679</v>
+        <v>0.0002875599602703005</v>
       </c>
       <c r="FP4" t="n">
-        <v>0.000328377413097769</v>
+        <v>0.0002905211295001209</v>
       </c>
       <c r="FQ4" t="n">
-        <v>0.0004556471249088645</v>
+        <v>5.624830009764992e-05</v>
       </c>
       <c r="FR4" t="n">
-        <v>0.0001597646332811564</v>
+        <v>0.0001666962925810367</v>
       </c>
       <c r="FS4" t="n">
-        <v>0.0002097788819810376</v>
+        <v>0.0001536188938189298</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.0001121574168791994</v>
+        <v>0.0002749520936049521</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.0009840083075687289</v>
+        <v>7.403564086416736e-05</v>
       </c>
       <c r="FV4" t="n">
-        <v>9.06374043552205e-05</v>
+        <v>0.0002827354765031487</v>
       </c>
       <c r="FW4" t="n">
-        <v>0.0005636111600324512</v>
+        <v>0.0002132547087967396</v>
       </c>
       <c r="FX4" t="n">
-        <v>0.0002624483313411474</v>
+        <v>0.0001706191978882998</v>
       </c>
       <c r="FY4" t="n">
-        <v>0.0006273316685110331</v>
+        <v>0.0001128888688981533</v>
       </c>
       <c r="FZ4" t="n">
-        <v>0.0002493704087100923</v>
+        <v>0.0001370991813018918</v>
       </c>
       <c r="GA4" t="n">
-        <v>0.0001393838028889149</v>
+        <v>9.590431727701798e-05</v>
       </c>
       <c r="GB4" t="n">
-        <v>0.0001083742754417472</v>
+        <v>3.736513463081792e-07</v>
       </c>
       <c r="GC4" t="n">
-        <v>0.0007503239903599024</v>
+        <v>0.0003812903305515647</v>
       </c>
       <c r="GD4" t="n">
-        <v>0.0002558934211265296</v>
+        <v>0.000177414549398236</v>
       </c>
       <c r="GE4" t="n">
-        <v>0.0007672918727621436</v>
+        <v>5.198817598284222e-05</v>
       </c>
       <c r="GF4" t="n">
-        <v>0.0001165561989182606</v>
+        <v>8.567028271500021e-05</v>
       </c>
       <c r="GG4" t="n">
-        <v>3.277120413258672e-06</v>
+        <v>0.0001015212037600577</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.0008177238050848246</v>
+        <v>0.0103509072214365</v>
       </c>
       <c r="B5" t="n">
-        <v>0.003180947620421648</v>
+        <v>0.03904082998633385</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0002211301762145013</v>
+        <v>0.004179384559392929</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001013662782497704</v>
+        <v>0.04369603097438812</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0008543530711904168</v>
+        <v>0.01170883607119322</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0007195424987003207</v>
+        <v>0.01255392096936703</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0002203281910624355</v>
+        <v>0.02637703530490398</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0001262069708900526</v>
+        <v>0.01262248959392309</v>
       </c>
       <c r="I5" t="n">
-        <v>8.934663128457032e-06</v>
+        <v>0.01286748331040144</v>
       </c>
       <c r="J5" t="n">
-        <v>0.000649051449727267</v>
+        <v>0.02151543274521828</v>
       </c>
       <c r="K5" t="n">
-        <v>0.002082891296595335</v>
+        <v>0.04069134593009949</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0002092575596179813</v>
+        <v>0.00273689697496593</v>
       </c>
       <c r="M5" t="n">
-        <v>0.001347134704701602</v>
+        <v>0.0595720112323761</v>
       </c>
       <c r="N5" t="n">
-        <v>0.002111529931426048</v>
+        <v>0.02716538868844509</v>
       </c>
       <c r="O5" t="n">
-        <v>0.001354171079583466</v>
+        <v>0.01425842847675085</v>
       </c>
       <c r="P5" t="n">
-        <v>0.000248832511715591</v>
+        <v>0.02049013040959835</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0001620591938262805</v>
+        <v>0.003399353008717299</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0004284691240172833</v>
+        <v>0.0114224785938859</v>
       </c>
       <c r="S5" t="n">
-        <v>8.620160224381834e-05</v>
+        <v>0.004158450290560722</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0003943644696846604</v>
+        <v>0.01033543609082699</v>
       </c>
       <c r="U5" t="n">
-        <v>0.000227213982725516</v>
+        <v>0.0006325573194772005</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0001587854203535244</v>
+        <v>0.008518999442458153</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0002482457202859223</v>
+        <v>0.008101336658000946</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0006548049859702587</v>
+        <v>0.002431169617921114</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.000523712020367384</v>
+        <v>0.003894218243658543</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0003658155910670757</v>
+        <v>0.01511122938245535</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.00016615359345451</v>
+        <v>0.004372958559542894</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.00050604238640517</v>
+        <v>0.001465481705963612</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.0005930242477916181</v>
+        <v>0.003467170288786292</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.0001692335645202547</v>
+        <v>0.00171095272526145</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.000157985050464049</v>
+        <v>0.003800722770392895</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.000877582817338407</v>
+        <v>0.00452406844124198</v>
       </c>
       <c r="AG5" t="n">
-        <v>5.693871935363859e-05</v>
+        <v>0.005081860814243555</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.0004160829121246934</v>
+        <v>0.002314891666173935</v>
       </c>
       <c r="AI5" t="n">
-        <v>4.553314647637308e-05</v>
+        <v>0.00922323577105999</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.370057725580409e-05</v>
+        <v>0.00118347886018455</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.0002140825090464205</v>
+        <v>0.005806438159197569</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.0001867772225523368</v>
+        <v>0.004540408961474895</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.0001498892961535603</v>
+        <v>0.000124000187497586</v>
       </c>
       <c r="AN5" t="n">
-        <v>3.078601730521768e-05</v>
+        <v>0.0008304950315505266</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.0003292124019935727</v>
+        <v>0.002936132252216339</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.0002067450695903972</v>
+        <v>0.005502157844603062</v>
       </c>
       <c r="AQ5" t="n">
-        <v>6.240466609597206e-05</v>
+        <v>0.006678006146103144</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.0001056175970006734</v>
+        <v>0.006447538267821074</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.000228264631005004</v>
+        <v>0.004851703997701406</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.000107509309600573</v>
+        <v>0.0003694302868098021</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.00229320814833045</v>
+        <v>0.0196929294615984</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.0001122252797358669</v>
+        <v>0.008339910767972469</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.0001170901814475656</v>
+        <v>0.02144039422273636</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.0004922593361698091</v>
+        <v>0.02357313595712185</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.0001961900707101449</v>
+        <v>0.001656376523897052</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.000221366819459945</v>
+        <v>0.0002965983003377914</v>
       </c>
       <c r="BA5" t="n">
-        <v>9.3379698228091e-05</v>
+        <v>0.005097576417028904</v>
       </c>
       <c r="BB5" t="n">
-        <v>7.302794983843341e-05</v>
+        <v>0.01044411677867174</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.0001079579524230212</v>
+        <v>0.006678990088403225</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.0005851160385645926</v>
+        <v>0.00715310825034976</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.0007518368656747043</v>
+        <v>0.006518449634313583</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.0001665081072133034</v>
+        <v>0.002131858607754111</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.001597991096787155</v>
+        <v>0.001606395002454519</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.0008327860850840807</v>
+        <v>0.008524677716195583</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.0004736306727863848</v>
+        <v>0.01057621650397778</v>
       </c>
       <c r="BJ5" t="n">
-        <v>5.65419250051491e-05</v>
+        <v>0.01761606894433498</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.0001506542757852003</v>
+        <v>0.004960197955369949</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.0004554578044917434</v>
+        <v>0.003557282499969006</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.000200005917577073</v>
+        <v>0.004307962488383055</v>
       </c>
       <c r="BN5" t="n">
-        <v>0.0004496796173043549</v>
+        <v>0.00103790417779237</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.0001557089708512649</v>
+        <v>0.01174044050276279</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.0007768144714646041</v>
+        <v>5.778373451903462e-05</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.0002156533591914922</v>
+        <v>0.002931819530203938</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.0005845468258485198</v>
+        <v>0.004768462851643562</v>
       </c>
       <c r="BS5" t="n">
-        <v>0.0006738691008649766</v>
+        <v>0.001114426995627582</v>
       </c>
       <c r="BT5" t="n">
-        <v>0.0004507456906139851</v>
+        <v>0.003230514470487833</v>
       </c>
       <c r="BU5" t="n">
-        <v>8.124625310301781e-07</v>
+        <v>0.007518534548580647</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.001108981086872518</v>
+        <v>0.01820431090891361</v>
       </c>
       <c r="BW5" t="n">
-        <v>0.0001244009472429752</v>
+        <v>0.001033883076161146</v>
       </c>
       <c r="BX5" t="n">
-        <v>3.514485433697701e-05</v>
+        <v>0.01719830371439457</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.0001126998758991249</v>
+        <v>0.008214596658945084</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.0005540451384149492</v>
+        <v>0.001460597501136363</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.085166877601296e-05</v>
+        <v>0.005966454278677702</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.0001896863832371309</v>
+        <v>0.005106195341795683</v>
       </c>
       <c r="CC5" t="n">
-        <v>0.0002124601742252707</v>
+        <v>0.006427586078643799</v>
       </c>
       <c r="CD5" t="n">
-        <v>0.0001692922814982012</v>
+        <v>0.0007489031995646656</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.0005566327017731965</v>
+        <v>0.007350324187427759</v>
       </c>
       <c r="CF5" t="n">
-        <v>0.0002153464447474107</v>
+        <v>0.0005984189338050783</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.0001240842248080298</v>
+        <v>0.01354916580021381</v>
       </c>
       <c r="CH5" t="n">
-        <v>7.795679266564548e-05</v>
+        <v>0.0002644535270519555</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.0001702991721685976</v>
+        <v>0.001546130864880979</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.000243682210566476</v>
+        <v>0.001403029076755047</v>
       </c>
       <c r="CK5" t="n">
-        <v>9.554183634463698e-05</v>
+        <v>0.0002276183950016275</v>
       </c>
       <c r="CL5" t="n">
-        <v>4.069703209097497e-05</v>
+        <v>0.0002526165335439146</v>
       </c>
       <c r="CM5" t="n">
-        <v>0.000644247978925705</v>
+        <v>2.872548066079617e-05</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.0003427620104048401</v>
+        <v>0.00576294306665659</v>
       </c>
       <c r="CO5" t="n">
-        <v>0.0001237535325344652</v>
+        <v>0.004382330924272537</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.0005312156281434</v>
+        <v>0.01263054087758064</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.0003441364387981594</v>
+        <v>0.000982927274890244</v>
       </c>
       <c r="CR5" t="n">
-        <v>0.0004452129651326686</v>
+        <v>0.0101685794070363</v>
       </c>
       <c r="CS5" t="n">
-        <v>0.0002057204255834222</v>
+        <v>0.01266327686607838</v>
       </c>
       <c r="CT5" t="n">
-        <v>0.0004037951584905386</v>
+        <v>0.007420820184051991</v>
       </c>
       <c r="CU5" t="n">
-        <v>3.310478496132419e-05</v>
+        <v>0.00370754674077034</v>
       </c>
       <c r="CV5" t="n">
-        <v>0.0001893910521175712</v>
+        <v>0.0008417398203164339</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.000466329453047365</v>
+        <v>0.008432943373918533</v>
       </c>
       <c r="CX5" t="n">
-        <v>0.0002662301703821868</v>
+        <v>0.0004745852202177048</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.0001419764739694074</v>
+        <v>0.01439884956926107</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.056554694718216e-05</v>
+        <v>0.001144377514719963</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.0001331271196249872</v>
+        <v>0.0002821874804794788</v>
       </c>
       <c r="DB5" t="n">
-        <v>0.0003003281308338046</v>
+        <v>0.00136901531368494</v>
       </c>
       <c r="DC5" t="n">
-        <v>0.0001682718575466424</v>
+        <v>0.00236336886882782</v>
       </c>
       <c r="DD5" t="n">
-        <v>4.393116614664905e-05</v>
+        <v>0.0002022144326474518</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.0001299756695516407</v>
+        <v>0.01232587639242411</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.0001588006853125989</v>
+        <v>0.02070110104978085</v>
       </c>
       <c r="DG5" t="n">
-        <v>6.711816968163475e-05</v>
+        <v>0.01893122680485249</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.0007551307789981365</v>
+        <v>0.02243358269333839</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.001080189016647637</v>
+        <v>0.01476445980370045</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.0001323592005064711</v>
+        <v>0.003754379227757454</v>
       </c>
       <c r="DK5" t="n">
-        <v>6.050824595149606e-06</v>
+        <v>0.003400062676519156</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.0003193358425050974</v>
+        <v>0.01475866045802832</v>
       </c>
       <c r="DM5" t="n">
-        <v>1.569191226735711e-05</v>
+        <v>0.006225304678082466</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.0003149951226077974</v>
+        <v>0.005385840311646461</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.0003715315542649478</v>
+        <v>0.006523297633975744</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.0002489789039827883</v>
+        <v>0.002078205579891801</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.0003374252701178193</v>
+        <v>0.01168225519359112</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.0001588187005836517</v>
+        <v>0.0004540562222246081</v>
       </c>
       <c r="DS5" t="n">
-        <v>3.368876059539616e-05</v>
+        <v>0.01275128684937954</v>
       </c>
       <c r="DT5" t="n">
-        <v>4.016747698187828e-05</v>
+        <v>0.01028997078537941</v>
       </c>
       <c r="DU5" t="n">
-        <v>0.0001269220665562898</v>
+        <v>0.0003150959964841604</v>
       </c>
       <c r="DV5" t="n">
-        <v>7.344444748014212e-05</v>
+        <v>0.01338602416217327</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.0001537197967991233</v>
+        <v>0.00210701092146337</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.0002164054603781551</v>
+        <v>0.002329234499484301</v>
       </c>
       <c r="DY5" t="n">
-        <v>0.0005193506949581206</v>
+        <v>0.008344431407749653</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0.0002933887008111924</v>
+        <v>0.001121745212003589</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.0003135737788397819</v>
+        <v>0.003397504333406687</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.000513282255269587</v>
+        <v>0.0004595932550728321</v>
       </c>
       <c r="EC5" t="n">
-        <v>0.0003098636516369879</v>
+        <v>0.001326597412116826</v>
       </c>
       <c r="ED5" t="n">
-        <v>0.0005540525889955461</v>
+        <v>0.01980170980095863</v>
       </c>
       <c r="EE5" t="n">
-        <v>6.020984437782317e-05</v>
+        <v>0.00774629320949316</v>
       </c>
       <c r="EF5" t="n">
-        <v>0.0002342866937397048</v>
+        <v>0.003913591615855694</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.000328012538375333</v>
+        <v>0.002241787500679493</v>
       </c>
       <c r="EH5" t="n">
-        <v>1.00039233075222e-05</v>
+        <v>0.0002512109349481761</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.0001227095490321517</v>
+        <v>0.01771323941648006</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.0004526411648839712</v>
+        <v>0.003631545696407557</v>
       </c>
       <c r="EK5" t="n">
-        <v>5.574767783400603e-05</v>
+        <v>0.001013056142255664</v>
       </c>
       <c r="EL5" t="n">
-        <v>0.0005404100520536304</v>
+        <v>0.002058920217677951</v>
       </c>
       <c r="EM5" t="n">
-        <v>0.000314590404741466</v>
+        <v>0.002519886940717697</v>
       </c>
       <c r="EN5" t="n">
-        <v>0.000169250852195546</v>
+        <v>0.001370886689983308</v>
       </c>
       <c r="EO5" t="n">
-        <v>0.0001969460863620043</v>
+        <v>0.005581374745815992</v>
       </c>
       <c r="EP5" t="n">
-        <v>0.000530458870343864</v>
+        <v>0.009998663328588009</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0.0001175541401607916</v>
+        <v>0.0008409844012930989</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.0001169841270893812</v>
+        <v>0.005236881319433451</v>
       </c>
       <c r="ES5" t="n">
-        <v>6.582227069884539e-05</v>
+        <v>0.01052671764045954</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.0007230434566736221</v>
+        <v>0.01433321088552475</v>
       </c>
       <c r="EU5" t="n">
-        <v>0.0003209466813132167</v>
+        <v>0.004116668365895748</v>
       </c>
       <c r="EV5" t="n">
-        <v>0.000343239662470296</v>
+        <v>0.005141726695001125</v>
       </c>
       <c r="EW5" t="n">
-        <v>7.009004184510559e-05</v>
+        <v>0.007118944078683853</v>
       </c>
       <c r="EX5" t="n">
-        <v>0.0001050089413183741</v>
+        <v>0.001333874999545515</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.0004598161613103002</v>
+        <v>0.007821410894393921</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0.0001639875990804285</v>
+        <v>0.001846479019150138</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.000139625568408519</v>
+        <v>0.01661202870309353</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.0001259549026144668</v>
+        <v>0.0007079945062287152</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.0002368573623243719</v>
+        <v>0.001052159816026688</v>
       </c>
       <c r="FD5" t="n">
-        <v>0.0002511211205273867</v>
+        <v>0.0003015336114913225</v>
       </c>
       <c r="FE5" t="n">
-        <v>0.0001077987253665924</v>
+        <v>0.001286564627662301</v>
       </c>
       <c r="FF5" t="n">
-        <v>5.528701876755804e-06</v>
+        <v>0.0005612695240415633</v>
       </c>
       <c r="FG5" t="n">
-        <v>4.304625690565445e-05</v>
+        <v>0.007017501164227724</v>
       </c>
       <c r="FH5" t="n">
-        <v>4.190569961792789e-05</v>
+        <v>0.003691470483317971</v>
       </c>
       <c r="FI5" t="n">
-        <v>8.062422421062365e-05</v>
+        <v>0.005001673474907875</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.0004453350848052651</v>
+        <v>0.008233954198658466</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.0002175867120968178</v>
+        <v>0.003841631347313523</v>
       </c>
       <c r="FL5" t="n">
-        <v>0.0002611768431961536</v>
+        <v>0.0006668706191703677</v>
       </c>
       <c r="FM5" t="n">
-        <v>0.0004997376818209887</v>
+        <v>0.004371349234133959</v>
       </c>
       <c r="FN5" t="n">
-        <v>2.03316449187696e-06</v>
+        <v>0.01038357149809599</v>
       </c>
       <c r="FO5" t="n">
-        <v>0.0001720640721032396</v>
+        <v>0.005178187973797321</v>
       </c>
       <c r="FP5" t="n">
-        <v>0.0006164549267850816</v>
+        <v>0.007870113477110863</v>
       </c>
       <c r="FQ5" t="n">
-        <v>4.771273961523548e-05</v>
+        <v>0.002931540831923485</v>
       </c>
       <c r="FR5" t="n">
-        <v>0.0004441842320375144</v>
+        <v>0.001522013451904058</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.0004854160652030259</v>
+        <v>0.009854000061750412</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.0009161048219539225</v>
+        <v>0.01929096132516861</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.000175309949554503</v>
+        <v>0.02135413326323032</v>
       </c>
       <c r="FV5" t="n">
-        <v>0.0004007224342785776</v>
+        <v>0.001960286870598793</v>
       </c>
       <c r="FW5" t="n">
-        <v>0.0005295743467286229</v>
+        <v>0.006700146943330765</v>
       </c>
       <c r="FX5" t="n">
-        <v>0.0003494292323011905</v>
+        <v>0.01567831821739674</v>
       </c>
       <c r="FY5" t="n">
-        <v>0.0002815865154843777</v>
+        <v>0.008223196491599083</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.0001378626184305176</v>
+        <v>0.002855867613106966</v>
       </c>
       <c r="GA5" t="n">
-        <v>5.402195165515877e-05</v>
+        <v>0.005377945490181446</v>
       </c>
       <c r="GB5" t="n">
-        <v>8.787399565335363e-06</v>
+        <v>0.008488048799335957</v>
       </c>
       <c r="GC5" t="n">
-        <v>0.0005105431191623211</v>
+        <v>0.01231693848967552</v>
       </c>
       <c r="GD5" t="n">
-        <v>0.0003117892774753273</v>
+        <v>0.004698571749031544</v>
       </c>
       <c r="GE5" t="n">
-        <v>0.0009463232127018273</v>
+        <v>0.008559763431549072</v>
       </c>
       <c r="GF5" t="n">
-        <v>0.0002808568824548274</v>
+        <v>0.0003235506592318416</v>
       </c>
       <c r="GG5" t="n">
-        <v>2.587596463854425e-05</v>
+        <v>0.002358633792027831</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>3.699131775647402e-05</v>
+        <v>3.923015245987926e-10</v>
       </c>
       <c r="B6" t="n">
-        <v>0.0008704750798642635</v>
+        <v>9.455627392185306e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>6.347569433273748e-05</v>
+        <v>1.701199181525226e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0003441663575358689</v>
+        <v>7.916989286371745e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0006293822661973536</v>
+        <v>8.254508188088039e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>0.000453517452115193</v>
+        <v>9.411756707322638e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0003820884739980102</v>
+        <v>1.206179955914877e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>0.000115308299427852</v>
+        <v>9.165159298163417e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>4.819170499104075e-05</v>
+        <v>3.50064643939163e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>9.341885743197054e-06</v>
+        <v>4.443353240901615e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0006508221267722547</v>
+        <v>5.001012937100313e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>8.12406069599092e-05</v>
+        <v>3.634275547170773e-09</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0005285700317472219</v>
+        <v>2.550506916776385e-09</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0007584874401800334</v>
+        <v>8.94787088867588e-09</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0006194090819917619</v>
+        <v>1.499785184932989e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0004693757509812713</v>
+        <v>1.737342358865135e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0004013223224319518</v>
+        <v>1.107510350095708e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>6.257945642573759e-05</v>
+        <v>1.814612460293574e-09</v>
       </c>
       <c r="S6" t="n">
-        <v>1.504036663391162e-05</v>
+        <v>1.968628371429304e-09</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0002003886038437486</v>
+        <v>6.67546329324864e-09</v>
       </c>
       <c r="U6" t="n">
-        <v>4.678014374803752e-05</v>
+        <v>1.701168095280536e-10</v>
       </c>
       <c r="V6" t="n">
-        <v>7.32088228687644e-05</v>
+        <v>7.621134834323584e-09</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0001869661791715771</v>
+        <v>8.647062621491841e-09</v>
       </c>
       <c r="X6" t="n">
-        <v>0.00027480986318551</v>
+        <v>1.095045609744716e-09</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.972480822587386e-05</v>
+        <v>4.303974954211753e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.66669657221064e-05</v>
+        <v>1.148706640918817e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.339555744081736e-05</v>
+        <v>3.088420852392915e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.0001382400805596262</v>
+        <v>1.253118941946241e-09</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.0002336805337108672</v>
+        <v>4.52529214101105e-09</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.0001433784491382539</v>
+        <v>1.015129758030753e-09</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.0002267680101795122</v>
+        <v>3.604187170935802e-09</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.000334081647451967</v>
+        <v>9.161324143747152e-09</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.0002982359146699309</v>
+        <v>6.878777547569825e-09</v>
       </c>
       <c r="AH6" t="n">
-        <v>4.294551035854965e-05</v>
+        <v>3.442857110513842e-10</v>
       </c>
       <c r="AI6" t="n">
-        <v>7.179858948802575e-05</v>
+        <v>6.301784427620305e-09</v>
       </c>
       <c r="AJ6" t="n">
-        <v>3.375170854269527e-05</v>
+        <v>2.670630383505568e-10</v>
       </c>
       <c r="AK6" t="n">
-        <v>3.317108348710462e-05</v>
+        <v>2.926596187613484e-10</v>
       </c>
       <c r="AL6" t="n">
-        <v>7.067090336931869e-05</v>
+        <v>1.970785312721546e-09</v>
       </c>
       <c r="AM6" t="n">
-        <v>4.237685425323434e-05</v>
+        <v>7.246752642409149e-10</v>
       </c>
       <c r="AN6" t="n">
-        <v>5.791462899651378e-05</v>
+        <v>5.984842399442414e-09</v>
       </c>
       <c r="AO6" t="n">
-        <v>5.924774814047851e-05</v>
+        <v>1.470492505539767e-09</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.0001172607881017029</v>
+        <v>2.537471344155051e-10</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.0001954711333382875</v>
+        <v>2.032975121579739e-09</v>
       </c>
       <c r="AR6" t="n">
-        <v>9.839708945946768e-05</v>
+        <v>4.346725757109482e-10</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.240068225655705e-05</v>
+        <v>3.394754033436698e-09</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.0002936387318186462</v>
+        <v>9.241492016087705e-10</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.0008720156038179994</v>
+        <v>8.304872345377134e-09</v>
       </c>
       <c r="AV6" t="n">
-        <v>3.28341375279706e-05</v>
+        <v>2.297452450505943e-09</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.593090852722526e-05</v>
+        <v>2.376673746695701e-09</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.0002081221318803728</v>
+        <v>4.932435349047637e-09</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.0002489006728865206</v>
+        <v>9.40763555945523e-09</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.0003778473183047026</v>
+        <v>5.715160344976766e-09</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.0001314124092459679</v>
+        <v>8.752125246758169e-09</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.982799585675821e-05</v>
+        <v>3.172444307253386e-09</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.787643850548193e-05</v>
+        <v>8.220257807778353e-10</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.0001708419877104461</v>
+        <v>7.73203723269944e-09</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.0001740837615216151</v>
+        <v>2.396457920994521e-09</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.276796633144841e-05</v>
+        <v>1.099627588985186e-08</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.0008120969869196415</v>
+        <v>6.900600979520277e-09</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.0004288081254344434</v>
+        <v>4.365114936177861e-09</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.479124304954894e-05</v>
+        <v>3.087424538250616e-09</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.0004255454987287521</v>
+        <v>9.670860556809657e-09</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.410316872352269e-05</v>
+        <v>4.515498641666227e-09</v>
       </c>
       <c r="BL6" t="n">
-        <v>6.110254616942257e-05</v>
+        <v>2.450705194334546e-09</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.0003145480004604906</v>
+        <v>1.220301637516741e-09</v>
       </c>
       <c r="BN6" t="n">
-        <v>3.866582119371742e-05</v>
+        <v>1.06029252044948e-09</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.0002512756618671119</v>
+        <v>4.025813016284019e-09</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.0003297401708550751</v>
+        <v>2.201478999097617e-09</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.825596963404678e-05</v>
+        <v>5.402640557150562e-10</v>
       </c>
       <c r="BR6" t="n">
-        <v>0.0002493294887244701</v>
+        <v>3.436168904968895e-09</v>
       </c>
       <c r="BS6" t="n">
-        <v>0.0001989140291698277</v>
+        <v>3.856292618564794e-09</v>
       </c>
       <c r="BT6" t="n">
-        <v>6.177081377245486e-05</v>
+        <v>3.066218390301856e-09</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.0001011852145893499</v>
+        <v>6.569980670612097e-11</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.0002972804941236973</v>
+        <v>3.379452717666709e-09</v>
       </c>
       <c r="BW6" t="n">
-        <v>0.0001114935948862694</v>
+        <v>6.286420273227122e-10</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.0001179769315058365</v>
+        <v>1.39143221389304e-08</v>
       </c>
       <c r="BY6" t="n">
-        <v>4.505216929828748e-05</v>
+        <v>7.601467011397744e-09</v>
       </c>
       <c r="BZ6" t="n">
-        <v>8.671955583849922e-05</v>
+        <v>4.770578154733585e-09</v>
       </c>
       <c r="CA6" t="n">
-        <v>8.379165228689089e-05</v>
+        <v>2.327906756249831e-09</v>
       </c>
       <c r="CB6" t="n">
-        <v>0.0001824451901484281</v>
+        <v>4.298148059689311e-09</v>
       </c>
       <c r="CC6" t="n">
-        <v>1.174256067315582e-05</v>
+        <v>4.805789100004176e-09</v>
       </c>
       <c r="CD6" t="n">
-        <v>3.774022843572311e-05</v>
+        <v>2.573636859182216e-10</v>
       </c>
       <c r="CE6" t="n">
-        <v>0.0002019759267568588</v>
+        <v>3.714921981146091e-10</v>
       </c>
       <c r="CF6" t="n">
-        <v>1.071611950465012e-05</v>
+        <v>7.743850005681452e-10</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.0001382287591695786</v>
+        <v>6.149299958124743e-10</v>
       </c>
       <c r="CH6" t="n">
-        <v>3.746666698134504e-05</v>
+        <v>1.698512441805633e-10</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.099982455343707e-05</v>
+        <v>3.120089075991928e-09</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0.0001177827507490292</v>
+        <v>3.054339448027577e-09</v>
       </c>
       <c r="CK6" t="n">
-        <v>6.151489651529118e-05</v>
+        <v>1.794852710901296e-09</v>
       </c>
       <c r="CL6" t="n">
-        <v>3.646289405878633e-05</v>
+        <v>3.08630210277272e-09</v>
       </c>
       <c r="CM6" t="n">
-        <v>0.0003221482911612839</v>
+        <v>2.128458964634206e-09</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.0002785147808026522</v>
+        <v>5.073048647830092e-09</v>
       </c>
       <c r="CO6" t="n">
-        <v>2.543685695854947e-05</v>
+        <v>3.367129686182579e-09</v>
       </c>
       <c r="CP6" t="n">
-        <v>0.0003133346326649189</v>
+        <v>2.990319103446382e-11</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.0001625245931791142</v>
+        <v>1.156126216983466e-08</v>
       </c>
       <c r="CR6" t="n">
-        <v>6.44017054582946e-05</v>
+        <v>8.970759135529249e-10</v>
       </c>
       <c r="CS6" t="n">
-        <v>5.11202379129827e-05</v>
+        <v>9.049570870445223e-09</v>
       </c>
       <c r="CT6" t="n">
-        <v>0.0001475181488785893</v>
+        <v>5.356224797026243e-09</v>
       </c>
       <c r="CU6" t="n">
-        <v>2.524903538869694e-05</v>
+        <v>8.487884839425419e-10</v>
       </c>
       <c r="CV6" t="n">
-        <v>4.078977144672535e-05</v>
+        <v>4.520744889546791e-10</v>
       </c>
       <c r="CW6" t="n">
-        <v>0.0001353688858216628</v>
+        <v>6.162720334046412e-10</v>
       </c>
       <c r="CX6" t="n">
-        <v>3.958163142669946e-05</v>
+        <v>3.62204433113078e-10</v>
       </c>
       <c r="CY6" t="n">
-        <v>0.000183016323717311</v>
+        <v>6.945037323013992e-10</v>
       </c>
       <c r="CZ6" t="n">
-        <v>5.8321744290879e-05</v>
+        <v>2.39040431893045e-09</v>
       </c>
       <c r="DA6" t="n">
-        <v>3.396626198082231e-06</v>
+        <v>3.902739909023012e-09</v>
       </c>
       <c r="DB6" t="n">
-        <v>0.0001004715304588899</v>
+        <v>2.761785466987021e-09</v>
       </c>
       <c r="DC6" t="n">
-        <v>8.188173524104059e-06</v>
+        <v>2.027429557571736e-09</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.091413964284584e-05</v>
+        <v>3.105388834967471e-09</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.0002525491581764072</v>
+        <v>6.916118344690858e-09</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.0003976694133598357</v>
+        <v>1.52539705311483e-08</v>
       </c>
       <c r="DG6" t="n">
-        <v>0.0001249896449735388</v>
+        <v>8.23090040569241e-09</v>
       </c>
       <c r="DH6" t="n">
-        <v>7.132883183658123e-06</v>
+        <v>5.282991821786709e-09</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.0001383521739626303</v>
+        <v>4.080210835866183e-09</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.0001913241867441684</v>
+        <v>1.285807549322726e-08</v>
       </c>
       <c r="DK6" t="n">
-        <v>0.0003633519518189132</v>
+        <v>3.68913966042328e-09</v>
       </c>
       <c r="DL6" t="n">
-        <v>8.335259917657822e-05</v>
+        <v>7.086301767600389e-09</v>
       </c>
       <c r="DM6" t="n">
-        <v>0.0003149803669657558</v>
+        <v>4.072202131055747e-09</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.0001279472053283826</v>
+        <v>3.536112291868676e-09</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.0001625957665964961</v>
+        <v>2.116814057373517e-09</v>
       </c>
       <c r="DP6" t="n">
-        <v>0.0001023298100335523</v>
+        <v>2.701178170028129e-09</v>
       </c>
       <c r="DQ6" t="n">
-        <v>7.570881280116737e-05</v>
+        <v>8.697592868145421e-09</v>
       </c>
       <c r="DR6" t="n">
-        <v>9.17959405342117e-05</v>
+        <v>5.455595530889923e-09</v>
       </c>
       <c r="DS6" t="n">
-        <v>6.95029812050052e-05</v>
+        <v>4.302370959496926e-10</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.0001302207820117474</v>
+        <v>2.745256022507192e-09</v>
       </c>
       <c r="DU6" t="n">
-        <v>2.450463216518983e-05</v>
+        <v>3.580174823269999e-09</v>
       </c>
       <c r="DV6" t="n">
-        <v>0.0001653707440709695</v>
+        <v>2.120086606272054e-10</v>
       </c>
       <c r="DW6" t="n">
-        <v>6.956494326004758e-05</v>
+        <v>3.5866445369237e-09</v>
       </c>
       <c r="DX6" t="n">
-        <v>2.669879677341669e-06</v>
+        <v>7.614599617511431e-09</v>
       </c>
       <c r="DY6" t="n">
-        <v>4.748619176098146e-05</v>
+        <v>1.103588775919206e-09</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.461902088019997e-05</v>
+        <v>6.056601886683666e-09</v>
       </c>
       <c r="EA6" t="n">
-        <v>5.149850403540768e-05</v>
+        <v>4.255099828043285e-09</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.0001040688221110031</v>
+        <v>4.946788756399201e-09</v>
       </c>
       <c r="EC6" t="n">
-        <v>5.672813858836889e-05</v>
+        <v>4.135789044568128e-09</v>
       </c>
       <c r="ED6" t="n">
-        <v>0.0001898626796901226</v>
+        <v>5.332474017905042e-09</v>
       </c>
       <c r="EE6" t="n">
-        <v>3.058208676520735e-05</v>
+        <v>1.303222640913759e-09</v>
       </c>
       <c r="EF6" t="n">
-        <v>8.518638787791133e-05</v>
+        <v>1.899238100122602e-09</v>
       </c>
       <c r="EG6" t="n">
-        <v>3.308892701170407e-05</v>
+        <v>1.689921202974176e-09</v>
       </c>
       <c r="EH6" t="n">
-        <v>5.949103069724515e-05</v>
+        <v>1.177222541670631e-09</v>
       </c>
       <c r="EI6" t="n">
-        <v>8.04005831014365e-05</v>
+        <v>4.882926063487503e-09</v>
       </c>
       <c r="EJ6" t="n">
-        <v>2.187947757192887e-05</v>
+        <v>3.308471274721114e-09</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.0001177133090095595</v>
+        <v>2.783488772806209e-09</v>
       </c>
       <c r="EL6" t="n">
-        <v>0.0002737849135883152</v>
+        <v>1.730990351056505e-11</v>
       </c>
       <c r="EM6" t="n">
-        <v>2.898161801567767e-05</v>
+        <v>1.752977762947694e-10</v>
       </c>
       <c r="EN6" t="n">
-        <v>2.472388223395683e-05</v>
+        <v>5.88192916595176e-09</v>
       </c>
       <c r="EO6" t="n">
-        <v>0.0002197330031776801</v>
+        <v>1.477144517814111e-09</v>
       </c>
       <c r="EP6" t="n">
-        <v>2.641647006385028e-05</v>
+        <v>4.362020522563625e-09</v>
       </c>
       <c r="EQ6" t="n">
-        <v>9.935265552485362e-05</v>
+        <v>6.980732658590227e-10</v>
       </c>
       <c r="ER6" t="n">
-        <v>0.0001674416416790336</v>
+        <v>2.557673628444945e-09</v>
       </c>
       <c r="ES6" t="n">
-        <v>2.831252277246676e-05</v>
+        <v>8.831692710487005e-09</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.0001761706807883456</v>
+        <v>1.424153572848752e-09</v>
       </c>
       <c r="EU6" t="n">
-        <v>8.107619942165911e-05</v>
+        <v>1.458452025815404e-09</v>
       </c>
       <c r="EV6" t="n">
-        <v>0.0001262652804143727</v>
+        <v>1.253762316189011e-09</v>
       </c>
       <c r="EW6" t="n">
-        <v>6.766319711459801e-05</v>
+        <v>2.318178982108066e-10</v>
       </c>
       <c r="EX6" t="n">
-        <v>3.842363366857171e-05</v>
+        <v>7.655664435723963e-10</v>
       </c>
       <c r="EY6" t="n">
-        <v>0.0001296061527682468</v>
+        <v>5.803037217422258e-11</v>
       </c>
       <c r="EZ6" t="n">
-        <v>9.076816240849439e-07</v>
+        <v>3.02454117306894e-10</v>
       </c>
       <c r="FA6" t="n">
-        <v>0.0001194104552268982</v>
+        <v>1.144293548804853e-10</v>
       </c>
       <c r="FB6" t="n">
-        <v>7.229224138427526e-05</v>
+        <v>1.201548638363192e-09</v>
       </c>
       <c r="FC6" t="n">
-        <v>5.873192276339978e-05</v>
+        <v>3.329992281919658e-09</v>
       </c>
       <c r="FD6" t="n">
-        <v>0.0001079167195712216</v>
+        <v>3.293392669689865e-09</v>
       </c>
       <c r="FE6" t="n">
-        <v>3.591035056160763e-05</v>
+        <v>1.302685403992143e-09</v>
       </c>
       <c r="FF6" t="n">
-        <v>1.557141513330862e-05</v>
+        <v>2.290759582024293e-09</v>
       </c>
       <c r="FG6" t="n">
-        <v>0.0001530262816231698</v>
+        <v>8.678061824696215e-09</v>
       </c>
       <c r="FH6" t="n">
-        <v>5.669271922670305e-05</v>
+        <v>4.061158520585195e-09</v>
       </c>
       <c r="FI6" t="n">
-        <v>1.251624416909181e-05</v>
+        <v>2.141028243585197e-09</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0.0001708188792690635</v>
+        <v>1.729854148813104e-09</v>
       </c>
       <c r="FK6" t="n">
-        <v>0.0001989964075619355</v>
+        <v>3.38866001925453e-09</v>
       </c>
       <c r="FL6" t="n">
-        <v>2.053693606285378e-06</v>
+        <v>2.728484105318785e-11</v>
       </c>
       <c r="FM6" t="n">
-        <v>4.997439100407064e-05</v>
+        <v>3.022476491310044e-09</v>
       </c>
       <c r="FN6" t="n">
-        <v>0.000166623736731708</v>
+        <v>5.47159695329924e-09</v>
       </c>
       <c r="FO6" t="n">
-        <v>0.0001611793850315735</v>
+        <v>3.211039656392245e-09</v>
       </c>
       <c r="FP6" t="n">
-        <v>0.0003398028493393213</v>
+        <v>1.185837428252512e-09</v>
       </c>
       <c r="FQ6" t="n">
-        <v>8.983315638033673e-05</v>
+        <v>9.097928632684216e-09</v>
       </c>
       <c r="FR6" t="n">
-        <v>8.79786821315065e-05</v>
+        <v>8.744471813315613e-09</v>
       </c>
       <c r="FS6" t="n">
-        <v>0.000252400990575552</v>
+        <v>1.124328075086112e-09</v>
       </c>
       <c r="FT6" t="n">
-        <v>0.0002110933419317007</v>
+        <v>7.901132192955629e-09</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.0002560852735769004</v>
+        <v>1.682566308502942e-09</v>
       </c>
       <c r="FV6" t="n">
-        <v>3.843160811811686e-05</v>
+        <v>1.194274368288006e-08</v>
       </c>
       <c r="FW6" t="n">
-        <v>0.0001074625906767324</v>
+        <v>2.566814982785104e-09</v>
       </c>
       <c r="FX6" t="n">
-        <v>4.245919262757525e-05</v>
+        <v>1.18621379385786e-09</v>
       </c>
       <c r="FY6" t="n">
-        <v>0.000108945656393189</v>
+        <v>2.565032186652161e-09</v>
       </c>
       <c r="FZ6" t="n">
-        <v>0.000344999018125236</v>
+        <v>4.908045636575764e-10</v>
       </c>
       <c r="GA6" t="n">
-        <v>0.000144198362249881</v>
+        <v>1.807677341147951e-10</v>
       </c>
       <c r="GB6" t="n">
-        <v>0.0001660591660765931</v>
+        <v>2.809835919492798e-09</v>
       </c>
       <c r="GC6" t="n">
-        <v>0.0002287031820742413</v>
+        <v>3.457260921990724e-09</v>
       </c>
       <c r="GD6" t="n">
-        <v>4.469691702979617e-05</v>
+        <v>7.359199916123771e-09</v>
       </c>
       <c r="GE6" t="n">
-        <v>0.000142079486977309</v>
+        <v>2.239295415762399e-10</v>
       </c>
       <c r="GF6" t="n">
-        <v>0.0003327495651319623</v>
+        <v>5.029697103253739e-09</v>
       </c>
       <c r="GG6" t="n">
-        <v>0.0001995154307223856</v>
+        <v>4.224505190109085e-09</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2.15795617486414e-10</v>
+        <v>2.192558018857557e-16</v>
       </c>
       <c r="B7" t="n">
-        <v>5.782826439926225e-10</v>
+        <v>7.760841970428593e-16</v>
       </c>
       <c r="C7" t="n">
-        <v>2.469331128462926e-10</v>
+        <v>8.383369893804325e-16</v>
       </c>
       <c r="D7" t="n">
-        <v>2.561525713762336e-10</v>
+        <v>8.817191052630415e-16</v>
       </c>
       <c r="E7" t="n">
-        <v>3.334177656189041e-10</v>
+        <v>5.163783367609744e-16</v>
       </c>
       <c r="F7" t="n">
-        <v>1.513902614380669e-10</v>
+        <v>2.53489983113842e-15</v>
       </c>
       <c r="G7" t="n">
-        <v>5.577568962245039e-10</v>
+        <v>7.151857045088273e-16</v>
       </c>
       <c r="H7" t="n">
-        <v>2.361256190575034e-10</v>
+        <v>1.099927868546873e-16</v>
       </c>
       <c r="I7" t="n">
-        <v>1.481754163812354e-10</v>
+        <v>3.084550310281813e-15</v>
       </c>
       <c r="J7" t="n">
-        <v>9.800438932616728e-11</v>
+        <v>1.287339731478399e-16</v>
       </c>
       <c r="K7" t="n">
-        <v>9.205319839722392e-11</v>
+        <v>3.703775228679727e-15</v>
       </c>
       <c r="L7" t="n">
-        <v>3.101038037467418e-10</v>
+        <v>6.675496303464295e-16</v>
       </c>
       <c r="M7" t="n">
-        <v>2.648754549028354e-10</v>
+        <v>1.734451578400738e-15</v>
       </c>
       <c r="N7" t="n">
-        <v>1.237432822875917e-09</v>
+        <v>3.651033875185991e-16</v>
       </c>
       <c r="O7" t="n">
-        <v>6.914820105397013e-11</v>
+        <v>2.576665543459872e-15</v>
       </c>
       <c r="P7" t="n">
-        <v>1.724350523479856e-10</v>
+        <v>1.54991740402839e-15</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.580406916446009e-10</v>
+        <v>1.469305701954672e-15</v>
       </c>
       <c r="R7" t="n">
-        <v>1.939519933547018e-10</v>
+        <v>1.780219733156204e-15</v>
       </c>
       <c r="S7" t="n">
-        <v>4.256733507346233e-11</v>
+        <v>7.881590752224429e-16</v>
       </c>
       <c r="T7" t="n">
-        <v>7.045586336573706e-12</v>
+        <v>1.725115793014338e-15</v>
       </c>
       <c r="U7" t="n">
-        <v>9.711793869104923e-11</v>
+        <v>7.432240832497207e-16</v>
       </c>
       <c r="V7" t="n">
-        <v>2.153414946359788e-10</v>
+        <v>2.202864821638866e-15</v>
       </c>
       <c r="W7" t="n">
-        <v>4.792853336432756e-10</v>
+        <v>3.630560665334381e-15</v>
       </c>
       <c r="X7" t="n">
-        <v>4.514473239680683e-10</v>
+        <v>1.641997720449695e-15</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.148850541949798e-10</v>
+        <v>5.854072338579044e-16</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.338956194864906e-11</v>
+        <v>8.29728064141895e-16</v>
       </c>
       <c r="AA7" t="n">
-        <v>7.995973674845835e-12</v>
+        <v>7.89407919424051e-16</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.239953972831387e-11</v>
+        <v>9.749451925641851e-16</v>
       </c>
       <c r="AC7" t="n">
-        <v>7.15296571973667e-11</v>
+        <v>2.954340541042061e-16</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.856088781617473e-10</v>
+        <v>1.253439990621624e-15</v>
       </c>
       <c r="AE7" t="n">
-        <v>5.119424884014734e-10</v>
+        <v>1.504943448540094e-15</v>
       </c>
       <c r="AF7" t="n">
-        <v>3.077946786333996e-10</v>
+        <v>1.599883507010007e-16</v>
       </c>
       <c r="AG7" t="n">
-        <v>3.110620094837202e-10</v>
+        <v>1.071489478496638e-15</v>
       </c>
       <c r="AH7" t="n">
-        <v>3.507409640501891e-12</v>
+        <v>6.338694827812304e-16</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.213984052172989e-10</v>
+        <v>2.156463086238855e-15</v>
       </c>
       <c r="AJ7" t="n">
-        <v>3.415563942787969e-10</v>
+        <v>5.910845780659948e-16</v>
       </c>
       <c r="AK7" t="n">
-        <v>8.926218791893703e-11</v>
+        <v>8.706390143404488e-16</v>
       </c>
       <c r="AL7" t="n">
-        <v>2.336002918879032e-12</v>
+        <v>7.605445305925319e-16</v>
       </c>
       <c r="AM7" t="n">
-        <v>6.88327589370985e-11</v>
+        <v>4.512791960832715e-16</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.707480407064921e-10</v>
+        <v>1.741406248293288e-15</v>
       </c>
       <c r="AO7" t="n">
-        <v>5.14117637351319e-10</v>
+        <v>1.419815896187208e-15</v>
       </c>
       <c r="AP7" t="n">
-        <v>2.520589986731991e-11</v>
+        <v>7.865995287478702e-17</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.257406678778494e-10</v>
+        <v>2.179474271498235e-16</v>
       </c>
       <c r="AR7" t="n">
-        <v>2.637702556373966e-10</v>
+        <v>9.375715578324837e-16</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.01946566308542e-11</v>
+        <v>9.033110868192969e-16</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.399201587926058e-10</v>
+        <v>5.964067507713896e-16</v>
       </c>
       <c r="AU7" t="n">
-        <v>6.607933089597395e-10</v>
+        <v>3.956681055521495e-15</v>
       </c>
       <c r="AV7" t="n">
-        <v>9.572348469433223e-11</v>
+        <v>7.56268655335233e-16</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.424474843636503e-10</v>
+        <v>8.618265894363335e-16</v>
       </c>
       <c r="AX7" t="n">
-        <v>8.828184711040521e-11</v>
+        <v>5.32216847023005e-16</v>
       </c>
       <c r="AY7" t="n">
-        <v>9.363892994329603e-11</v>
+        <v>5.810843879767023e-17</v>
       </c>
       <c r="AZ7" t="n">
-        <v>2.955493905165696e-10</v>
+        <v>6.433655691528983e-16</v>
       </c>
       <c r="BA7" t="n">
-        <v>3.691668359895317e-10</v>
+        <v>1.360544765703089e-15</v>
       </c>
       <c r="BB7" t="n">
-        <v>3.4974237395069e-10</v>
+        <v>1.175242650084936e-15</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.477394496826825e-11</v>
+        <v>1.44394672665396e-16</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.353783751767423e-10</v>
+        <v>9.755291159021986e-16</v>
       </c>
       <c r="BE7" t="n">
-        <v>2.344630600781272e-10</v>
+        <v>5.675332504840626e-16</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.210398170581328e-10</v>
+        <v>1.311193238064264e-15</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.800874892601058e-10</v>
+        <v>7.611996046981147e-16</v>
       </c>
       <c r="BH7" t="n">
-        <v>1.161390428272568e-12</v>
+        <v>1.568897083035754e-15</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.727724907585326e-11</v>
+        <v>1.471648912724133e-15</v>
       </c>
       <c r="BJ7" t="n">
-        <v>1.02619593378428e-10</v>
+        <v>1.293951141269074e-15</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.086460697079076e-10</v>
+        <v>8.517606616494002e-16</v>
       </c>
       <c r="BL7" t="n">
-        <v>2.21511350928516e-11</v>
+        <v>1.452617352948749e-15</v>
       </c>
       <c r="BM7" t="n">
-        <v>3.263002090747591e-10</v>
+        <v>1.368318834092989e-15</v>
       </c>
       <c r="BN7" t="n">
-        <v>7.386740524806257e-11</v>
+        <v>6.685825340860469e-16</v>
       </c>
       <c r="BO7" t="n">
-        <v>2.210414351555556e-10</v>
+        <v>2.901535713016839e-16</v>
       </c>
       <c r="BP7" t="n">
-        <v>9.470467743355471e-10</v>
+        <v>1.399663076547897e-15</v>
       </c>
       <c r="BQ7" t="n">
-        <v>3.201922615936326e-10</v>
+        <v>1.118306683557278e-15</v>
       </c>
       <c r="BR7" t="n">
-        <v>3.073490628668907e-10</v>
+        <v>2.140577195071337e-15</v>
       </c>
       <c r="BS7" t="n">
-        <v>3.400792980556844e-10</v>
+        <v>4.786833059653491e-16</v>
       </c>
       <c r="BT7" t="n">
-        <v>2.590830328053073e-11</v>
+        <v>2.503870420242094e-16</v>
       </c>
       <c r="BU7" t="n">
-        <v>9.987181220916241e-12</v>
+        <v>5.512216193814313e-16</v>
       </c>
       <c r="BV7" t="n">
-        <v>3.942703663550873e-10</v>
+        <v>7.490610931683685e-16</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.270551025500666e-10</v>
+        <v>1.306304799167423e-15</v>
       </c>
       <c r="BX7" t="n">
-        <v>2.430686207866017e-10</v>
+        <v>2.5847434849196e-15</v>
       </c>
       <c r="BY7" t="n">
-        <v>5.192090646310987e-10</v>
+        <v>2.13503717607982e-15</v>
       </c>
       <c r="BZ7" t="n">
-        <v>6.693520043787871e-11</v>
+        <v>1.942176244319489e-15</v>
       </c>
       <c r="CA7" t="n">
-        <v>6.734303392708085e-11</v>
+        <v>1.004585310608336e-16</v>
       </c>
       <c r="CB7" t="n">
-        <v>1.655121179000574e-10</v>
+        <v>1.509814205624162e-15</v>
       </c>
       <c r="CC7" t="n">
-        <v>2.184943892480362e-10</v>
+        <v>1.895553221562007e-15</v>
       </c>
       <c r="CD7" t="n">
-        <v>1.149835435199087e-11</v>
+        <v>6.179051881265326e-16</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.433420396268481e-11</v>
+        <v>9.360471102856627e-17</v>
       </c>
       <c r="CF7" t="n">
-        <v>8.805352280649714e-12</v>
+        <v>9.578804432923264e-18</v>
       </c>
       <c r="CG7" t="n">
-        <v>7.578640492944544e-11</v>
+        <v>5.845332017354564e-16</v>
       </c>
       <c r="CH7" t="n">
-        <v>2.294843481909226e-11</v>
+        <v>6.166224493721445e-17</v>
       </c>
       <c r="CI7" t="n">
-        <v>4.764877381546739e-11</v>
+        <v>4.514369030301385e-16</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.116823161728675e-10</v>
+        <v>3.286260195242111e-16</v>
       </c>
       <c r="CK7" t="n">
-        <v>2.12467508864389e-11</v>
+        <v>2.168193248478685e-16</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.32512806283458e-10</v>
+        <v>8.439850580122833e-16</v>
       </c>
       <c r="CM7" t="n">
-        <v>1.75014738812429e-10</v>
+        <v>6.084049724692467e-16</v>
       </c>
       <c r="CN7" t="n">
-        <v>2.848837832303275e-10</v>
+        <v>1.34797712610644e-15</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.799868448726372e-10</v>
+        <v>4.501995996524367e-17</v>
       </c>
       <c r="CP7" t="n">
-        <v>7.903766530148459e-11</v>
+        <v>2.408602242384239e-16</v>
       </c>
       <c r="CQ7" t="n">
-        <v>5.904208233431518e-10</v>
+        <v>1.020032756346532e-15</v>
       </c>
       <c r="CR7" t="n">
-        <v>2.978034485678904e-12</v>
+        <v>9.918354530489095e-16</v>
       </c>
       <c r="CS7" t="n">
-        <v>4.221915872459903e-10</v>
+        <v>5.860792486224323e-16</v>
       </c>
       <c r="CT7" t="n">
-        <v>4.336491998824243e-10</v>
+        <v>4.711441833391938e-16</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.300122232095191e-10</v>
+        <v>1.344274639214873e-15</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.209460916834493e-11</v>
+        <v>7.517375055234553e-16</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.795658413628054e-11</v>
+        <v>1.835503191343328e-16</v>
       </c>
       <c r="CX7" t="n">
-        <v>6.717012362988939e-12</v>
+        <v>7.600532514831244e-19</v>
       </c>
       <c r="CY7" t="n">
-        <v>3.615014537716732e-11</v>
+        <v>6.626978256245569e-16</v>
       </c>
       <c r="CZ7" t="n">
-        <v>1.695833404258273e-11</v>
+        <v>1.988529751781066e-16</v>
       </c>
       <c r="DA7" t="n">
-        <v>4.078447995992107e-11</v>
+        <v>5.149897850626286e-16</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.318580522546853e-10</v>
+        <v>2.11629778973168e-16</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.768309539935565e-11</v>
+        <v>5.469044247981741e-17</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.36820397961457e-11</v>
+        <v>7.537734021517402e-16</v>
       </c>
       <c r="DE7" t="n">
-        <v>2.671212417926228e-10</v>
+        <v>1.516383131418576e-16</v>
       </c>
       <c r="DF7" t="n">
-        <v>5.702373018223739e-10</v>
+        <v>1.213825953744435e-15</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.297018881185608e-10</v>
+        <v>1.219566296027977e-15</v>
       </c>
       <c r="DH7" t="n">
-        <v>1.006296934669137e-09</v>
+        <v>8.55373839504591e-16</v>
       </c>
       <c r="DI7" t="n">
-        <v>4.831927080672926e-10</v>
+        <v>2.90485978793922e-16</v>
       </c>
       <c r="DJ7" t="n">
-        <v>4.074082737837159e-10</v>
+        <v>1.436891868645618e-15</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.823281136128287e-10</v>
+        <v>4.553994290365125e-16</v>
       </c>
       <c r="DL7" t="n">
-        <v>4.793595520524718e-10</v>
+        <v>6.651387628203069e-16</v>
       </c>
       <c r="DM7" t="n">
-        <v>1.002803118321793e-10</v>
+        <v>3.644024677547462e-16</v>
       </c>
       <c r="DN7" t="n">
-        <v>3.474632040423309e-11</v>
+        <v>5.565507801086409e-16</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.493875995128846e-10</v>
+        <v>1.534462123235433e-16</v>
       </c>
       <c r="DP7" t="n">
-        <v>1.460311316314744e-10</v>
+        <v>4.575235759099894e-16</v>
       </c>
       <c r="DQ7" t="n">
-        <v>5.420683346635258e-11</v>
+        <v>1.98148111417093e-15</v>
       </c>
       <c r="DR7" t="n">
-        <v>1.66802543999367e-10</v>
+        <v>1.017490175197111e-15</v>
       </c>
       <c r="DS7" t="n">
-        <v>1.135925936646132e-10</v>
+        <v>1.272299285071359e-15</v>
       </c>
       <c r="DT7" t="n">
-        <v>4.370168393830198e-10</v>
+        <v>9.11402474927062e-16</v>
       </c>
       <c r="DU7" t="n">
-        <v>1.707844005105486e-10</v>
+        <v>4.671618049981185e-16</v>
       </c>
       <c r="DV7" t="n">
-        <v>2.038685192884415e-12</v>
+        <v>3.779030082636772e-16</v>
       </c>
       <c r="DW7" t="n">
-        <v>4.633973066381358e-11</v>
+        <v>9.964615234903389e-16</v>
       </c>
       <c r="DX7" t="n">
-        <v>1.432434587611553e-10</v>
+        <v>1.285508684474451e-16</v>
       </c>
       <c r="DY7" t="n">
-        <v>1.981912967075061e-10</v>
+        <v>5.287847224602898e-16</v>
       </c>
       <c r="DZ7" t="n">
-        <v>2.253706110622034e-10</v>
+        <v>8.571066042168773e-16</v>
       </c>
       <c r="EA7" t="n">
-        <v>1.68883934614783e-10</v>
+        <v>8.534126935339013e-17</v>
       </c>
       <c r="EB7" t="n">
-        <v>5.856842788531935e-11</v>
+        <v>1.058856723242169e-15</v>
       </c>
       <c r="EC7" t="n">
-        <v>4.894269364785764e-11</v>
+        <v>1.105895956814108e-15</v>
       </c>
       <c r="ED7" t="n">
-        <v>3.263116443719127e-10</v>
+        <v>3.977359406165019e-16</v>
       </c>
       <c r="EE7" t="n">
-        <v>1.357852164041162e-10</v>
+        <v>8.654689369886454e-16</v>
       </c>
       <c r="EF7" t="n">
-        <v>7.243645353677275e-12</v>
+        <v>6.328897832986124e-16</v>
       </c>
       <c r="EG7" t="n">
-        <v>4.579504137014467e-11</v>
+        <v>4.352424007022447e-16</v>
       </c>
       <c r="EH7" t="n">
-        <v>1.011383338189731e-10</v>
+        <v>8.680066741683989e-17</v>
       </c>
       <c r="EI7" t="n">
-        <v>2.10318096272033e-10</v>
+        <v>1.208541950461226e-15</v>
       </c>
       <c r="EJ7" t="n">
-        <v>1.033609170475458e-10</v>
+        <v>6.959513332821358e-16</v>
       </c>
       <c r="EK7" t="n">
-        <v>1.304086699738249e-10</v>
+        <v>9.845204897513112e-17</v>
       </c>
       <c r="EL7" t="n">
-        <v>2.074380944794285e-11</v>
+        <v>2.86048690820612e-16</v>
       </c>
       <c r="EM7" t="n">
-        <v>8.31451851812659e-11</v>
+        <v>3.591470518335069e-16</v>
       </c>
       <c r="EN7" t="n">
-        <v>6.618221248810841e-11</v>
+        <v>1.054826540479133e-15</v>
       </c>
       <c r="EO7" t="n">
-        <v>2.936968723776801e-11</v>
+        <v>1.976442723972645e-16</v>
       </c>
       <c r="EP7" t="n">
-        <v>2.05608030601212e-11</v>
+        <v>7.960169998741211e-16</v>
       </c>
       <c r="EQ7" t="n">
-        <v>8.30721082201169e-12</v>
+        <v>1.100693374572954e-15</v>
       </c>
       <c r="ER7" t="n">
-        <v>2.654891584352725e-10</v>
+        <v>1.560423153673185e-16</v>
       </c>
       <c r="ES7" t="n">
-        <v>2.497985152061233e-11</v>
+        <v>1.228000573660703e-16</v>
       </c>
       <c r="ET7" t="n">
-        <v>1.311829950223498e-10</v>
+        <v>1.360593258339319e-15</v>
       </c>
       <c r="EU7" t="n">
-        <v>6.699207161231513e-11</v>
+        <v>1.055915930728421e-15</v>
       </c>
       <c r="EV7" t="n">
-        <v>1.353432088624373e-10</v>
+        <v>7.502883380298216e-16</v>
       </c>
       <c r="EW7" t="n">
-        <v>1.004522229286486e-10</v>
+        <v>7.424765766737688e-16</v>
       </c>
       <c r="EX7" t="n">
-        <v>1.394635101847896e-11</v>
+        <v>9.520049992536969e-16</v>
       </c>
       <c r="EY7" t="n">
-        <v>8.636494297498132e-11</v>
+        <v>2.658836686129045e-16</v>
       </c>
       <c r="EZ7" t="n">
-        <v>1.462473545044141e-11</v>
+        <v>2.137008804083232e-16</v>
       </c>
       <c r="FA7" t="n">
-        <v>3.381854518647032e-11</v>
+        <v>5.138084917385641e-16</v>
       </c>
       <c r="FB7" t="n">
-        <v>2.430161280542187e-11</v>
+        <v>8.359766526635696e-17</v>
       </c>
       <c r="FC7" t="n">
-        <v>1.558945333934858e-10</v>
+        <v>5.342239445310832e-16</v>
       </c>
       <c r="FD7" t="n">
-        <v>1.265489102397765e-10</v>
+        <v>5.312127953431534e-16</v>
       </c>
       <c r="FE7" t="n">
-        <v>3.993851777073232e-11</v>
+        <v>2.150208224379414e-16</v>
       </c>
       <c r="FF7" t="n">
-        <v>8.838756115903124e-12</v>
+        <v>8.841307139429929e-16</v>
       </c>
       <c r="FG7" t="n">
-        <v>5.698982605273351e-11</v>
+        <v>1.917678780935473e-15</v>
       </c>
       <c r="FH7" t="n">
-        <v>1.067810839749939e-10</v>
+        <v>7.471377989825092e-16</v>
       </c>
       <c r="FI7" t="n">
-        <v>3.779743532050794e-11</v>
+        <v>7.271106578567469e-16</v>
       </c>
       <c r="FJ7" t="n">
-        <v>7.740040552928207e-11</v>
+        <v>4.757650657038212e-16</v>
       </c>
       <c r="FK7" t="n">
-        <v>9.983933124679822e-11</v>
+        <v>5.77854029309001e-16</v>
       </c>
       <c r="FL7" t="n">
-        <v>4.962587285550768e-11</v>
+        <v>1.628854098448913e-15</v>
       </c>
       <c r="FM7" t="n">
-        <v>3.976588502929701e-11</v>
+        <v>1.256932095704917e-15</v>
       </c>
       <c r="FN7" t="n">
-        <v>1.118807615996253e-10</v>
+        <v>1.290398579209171e-16</v>
       </c>
       <c r="FO7" t="n">
-        <v>2.614981564619256e-10</v>
+        <v>1.108661519386893e-15</v>
       </c>
       <c r="FP7" t="n">
-        <v>1.39662781339922e-10</v>
+        <v>5.40334757849931e-16</v>
       </c>
       <c r="FQ7" t="n">
-        <v>5.002380176755139e-10</v>
+        <v>1.620581339411317e-15</v>
       </c>
       <c r="FR7" t="n">
-        <v>9.056090599646183e-11</v>
+        <v>1.369518656262774e-15</v>
       </c>
       <c r="FS7" t="n">
-        <v>1.357124135292764e-11</v>
+        <v>1.444565351873032e-15</v>
       </c>
       <c r="FT7" t="n">
-        <v>4.381078000381677e-10</v>
+        <v>3.399077042882503e-16</v>
       </c>
       <c r="FU7" t="n">
-        <v>2.617780436864336e-10</v>
+        <v>1.019781346379875e-16</v>
       </c>
       <c r="FV7" t="n">
-        <v>5.743239217537166e-12</v>
+        <v>1.816514247913103e-15</v>
       </c>
       <c r="FW7" t="n">
-        <v>1.589567505400069e-10</v>
+        <v>5.866137264121498e-16</v>
       </c>
       <c r="FX7" t="n">
-        <v>4.552209997843448e-11</v>
+        <v>8.499817865810478e-16</v>
       </c>
       <c r="FY7" t="n">
-        <v>1.211387379296269e-10</v>
+        <v>8.05352732320962e-16</v>
       </c>
       <c r="FZ7" t="n">
-        <v>1.725748433045737e-10</v>
+        <v>8.906845784328139e-16</v>
       </c>
       <c r="GA7" t="n">
-        <v>3.324956421302261e-10</v>
+        <v>3.323540497530937e-16</v>
       </c>
       <c r="GB7" t="n">
-        <v>1.364528282032929e-12</v>
+        <v>9.797307169579351e-17</v>
       </c>
       <c r="GC7" t="n">
-        <v>1.2107959079799e-10</v>
+        <v>2.115945476965182e-16</v>
       </c>
       <c r="GD7" t="n">
-        <v>4.428126754163486e-10</v>
+        <v>1.440262000984506e-15</v>
       </c>
       <c r="GE7" t="n">
-        <v>2.180173264143548e-10</v>
+        <v>2.117086059768219e-16</v>
       </c>
       <c r="GF7" t="n">
-        <v>1.089107623530872e-11</v>
+        <v>6.401751136779466e-16</v>
       </c>
       <c r="GG7" t="n">
-        <v>2.103222734861632e-10</v>
+        <v>9.033562972028566e-16</v>
       </c>
     </row>
     <row r="8">
@@ -4982,3416 +4982,3416 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.0005574516835622489</v>
+        <v>0.00702365580946207</v>
       </c>
       <c r="B9" t="n">
-        <v>0.007174636702984571</v>
+        <v>0.073737733066082</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001093513681553304</v>
+        <v>0.00275023840367794</v>
       </c>
       <c r="D9" t="n">
-        <v>0.003830263158306479</v>
+        <v>0.1273183077573776</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0003868161584250629</v>
+        <v>0.01002899836748838</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001343348063528538</v>
+        <v>0.0633816197514534</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0004472366417758167</v>
+        <v>0.06204156205058098</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0009061763412319124</v>
+        <v>0.0471557155251503</v>
       </c>
       <c r="I9" t="n">
-        <v>3.305068457848392e-05</v>
+        <v>0.004311207216233015</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001111212070100009</v>
+        <v>0.01048599556088448</v>
       </c>
       <c r="K9" t="n">
-        <v>0.005202196538448334</v>
+        <v>0.06955133378505707</v>
       </c>
       <c r="L9" t="n">
-        <v>1.379921377520077e-05</v>
+        <v>0.01785701140761375</v>
       </c>
       <c r="M9" t="n">
-        <v>0.003547691740095615</v>
+        <v>0.193936824798584</v>
       </c>
       <c r="N9" t="n">
-        <v>0.001391806872561574</v>
+        <v>0.01356503460556269</v>
       </c>
       <c r="O9" t="n">
-        <v>0.001992725767195225</v>
+        <v>0.08017537742853165</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0001895226305350661</v>
+        <v>0.07037246227264404</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.0001302102027693763</v>
+        <v>0.007756787817925215</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0009879849385470152</v>
+        <v>0.006417693570256233</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0001847629609983414</v>
+        <v>0.002157068811357021</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0009796321392059326</v>
+        <v>0.005686072632670403</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0002033395139733329</v>
+        <v>0.01496396586298943</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0008658269071020186</v>
+        <v>0.02341582998633385</v>
       </c>
       <c r="W9" t="n">
-        <v>0.0001225884043378755</v>
+        <v>0.04028962180018425</v>
       </c>
       <c r="X9" t="n">
-        <v>0.0007212707423605025</v>
+        <v>0.04093721508979797</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.0006639697821810842</v>
+        <v>0.001346583478152752</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.0003281138488091528</v>
+        <v>0.01943132281303406</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.000480298709589988</v>
+        <v>0.01060368679463863</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.00057966448366642</v>
+        <v>0.0135603416711092</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.001715661026537418</v>
+        <v>0.03337477892637253</v>
       </c>
       <c r="AD9" t="n">
-        <v>8.775282367423642e-06</v>
+        <v>0.01409002579748631</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.000362497114110738</v>
+        <v>0.01302332431077957</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.0006710905581712723</v>
+        <v>0.003901692340150476</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.0001217727040057071</v>
+        <v>0.02931618317961693</v>
       </c>
       <c r="AH9" t="n">
-        <v>6.614759331569076e-05</v>
+        <v>0.006564215756952763</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.0001925018150359392</v>
+        <v>0.03420909866690636</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.0003273730399087071</v>
+        <v>0.04065867140889168</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.0002574756217654794</v>
+        <v>0.005170959047973156</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.0008205785416066647</v>
+        <v>0.03362860530614853</v>
       </c>
       <c r="AM9" t="n">
-        <v>5.592976958723739e-05</v>
+        <v>0.02646428719162941</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.0004262652655597776</v>
+        <v>0.03850428760051727</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.000613466661889106</v>
+        <v>0.0131547823548317</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.000969098589848727</v>
+        <v>0.0290142297744751</v>
       </c>
       <c r="AQ9" t="n">
-        <v>9.218836203217506e-05</v>
+        <v>0.01522891409695148</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.583115226821974e-05</v>
+        <v>0.02283676713705063</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.0004528605786617845</v>
+        <v>0.0135828098282218</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.000776240136474371</v>
+        <v>0.01191687025129795</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.005360424518585205</v>
+        <v>0.07871808111667633</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.0002046011941274628</v>
+        <v>0.03002080507576466</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.000802309368737042</v>
+        <v>0.08080059289932251</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.0008301499765366316</v>
+        <v>0.09378061443567276</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.272525696549565e-05</v>
+        <v>0.04655056819319725</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.0001677201071288437</v>
+        <v>0.006921793799847364</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.0001748247159412131</v>
+        <v>0.004836083855479956</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.0004151488828938454</v>
+        <v>0.02362414076924324</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.0001493451272835955</v>
+        <v>0.01677888445556164</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.001129459124058485</v>
+        <v>0.009070815518498421</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.001471110386773944</v>
+        <v>0.006910534575581551</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.0002016777580138296</v>
+        <v>0.01826474256813526</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.002630450297147036</v>
+        <v>0.05652634799480438</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.001334871398285031</v>
+        <v>0.02105546183884144</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.001037264824844897</v>
+        <v>0.009478333406150341</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.0007183342822827399</v>
+        <v>0.02530322968959808</v>
       </c>
       <c r="BK9" t="n">
-        <v>2.654724085005e-07</v>
+        <v>0.04051064699888229</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.0008552641957066953</v>
+        <v>0.008406135253608227</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.0009777621598914266</v>
+        <v>0.01411537267267704</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.0006794952787458897</v>
+        <v>0.007831284776329994</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.0002534330706112087</v>
+        <v>0.001665322110056877</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.0008051593904383481</v>
+        <v>0.01424253359436989</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.0004728608764708042</v>
+        <v>0.02295242249965668</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.0005668941885232925</v>
+        <v>0.04321659356355667</v>
       </c>
       <c r="BS9" t="n">
-        <v>0.0002932001661974937</v>
+        <v>0.005456122104078531</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.0006039589061401784</v>
+        <v>0.01475618779659271</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.0005366202676668763</v>
+        <v>0.003294656751677394</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.002370430156588554</v>
+        <v>0.04463969171047211</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.0007392219267785549</v>
+        <v>0.02191831171512604</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.000732913613319397</v>
+        <v>0.08654125034809113</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.0006568919634446502</v>
+        <v>0.03306914120912552</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.001021687872707844</v>
+        <v>0.04049127921462059</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.0002582438755780458</v>
+        <v>0.01142912730574608</v>
       </c>
       <c r="CB9" t="n">
-        <v>9.960179158952087e-05</v>
+        <v>0.004985812120139599</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.0006929275114089251</v>
+        <v>0.01325848232954741</v>
       </c>
       <c r="CD9" t="n">
-        <v>0.0003158061881549656</v>
+        <v>0.01179844327270985</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.001305330777540803</v>
+        <v>0.02572926320135593</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.0004326476191636175</v>
+        <v>0.004470454063266516</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.0004728595376946032</v>
+        <v>0.04474169760942459</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.0003978358581662178</v>
+        <v>0.003015610156580806</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.0002172583626816049</v>
+        <v>0.0005072832573205233</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.0001757557911332697</v>
+        <v>0.01344660110771656</v>
       </c>
       <c r="CK9" t="n">
-        <v>0.0001252140500582755</v>
+        <v>0.01652416586875916</v>
       </c>
       <c r="CL9" t="n">
-        <v>0.0002619771403260529</v>
+        <v>0.00244108447805047</v>
       </c>
       <c r="CM9" t="n">
-        <v>0.001145182177424431</v>
+        <v>0.01843016594648361</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.0007049518753774464</v>
+        <v>0.0240236334502697</v>
       </c>
       <c r="CO9" t="n">
-        <v>0.0003509061352815479</v>
+        <v>0.05109160766005516</v>
       </c>
       <c r="CP9" t="n">
-        <v>0.001623396412469447</v>
+        <v>0.09497157484292984</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.0001080235379049554</v>
+        <v>0.00202425941824913</v>
       </c>
       <c r="CR9" t="n">
-        <v>0.0008454229682683945</v>
+        <v>0.005639964714646339</v>
       </c>
       <c r="CS9" t="n">
-        <v>0.0004473040753509849</v>
+        <v>0.01342451479285955</v>
       </c>
       <c r="CT9" t="n">
-        <v>0.001157761202193797</v>
+        <v>0.02580063976347446</v>
       </c>
       <c r="CU9" t="n">
-        <v>0.0001874490699265152</v>
+        <v>0.01887837797403336</v>
       </c>
       <c r="CV9" t="n">
-        <v>0.0003036534762941301</v>
+        <v>0.01236545853316784</v>
       </c>
       <c r="CW9" t="n">
-        <v>0.001045687939040363</v>
+        <v>0.02273100987076759</v>
       </c>
       <c r="CX9" t="n">
-        <v>0.0005682987393811345</v>
+        <v>0.002032759133726358</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.0007198808598332107</v>
+        <v>0.05121432244777679</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.0002224912168458104</v>
+        <v>0.002031598007306457</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.0002441766555421054</v>
+        <v>0.001017269678413868</v>
       </c>
       <c r="DB9" t="n">
-        <v>0.0002885996946133673</v>
+        <v>0.01419857330620289</v>
       </c>
       <c r="DC9" t="n">
-        <v>0.0002404695260338485</v>
+        <v>0.0157591849565506</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.0001686964824330062</v>
+        <v>0.005676791537553072</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.0004189728642813861</v>
+        <v>0.009355207905173302</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.0009406215976923704</v>
+        <v>0.007596042938530445</v>
       </c>
       <c r="DG9" t="n">
-        <v>0.0004096133052371442</v>
+        <v>0.01792439818382263</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.001267514424398541</v>
+        <v>0.02810060605406761</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.0007684509619139135</v>
+        <v>0.001572237000800669</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.0009020764846354723</v>
+        <v>0.0270496029406786</v>
       </c>
       <c r="DK9" t="n">
-        <v>0.0006625670357607305</v>
+        <v>0.003578769043087959</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.0003580207703635097</v>
+        <v>0.08146591484546661</v>
       </c>
       <c r="DM9" t="n">
-        <v>7.748238567728549e-05</v>
+        <v>0.02947905473411083</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.0005470247706398368</v>
+        <v>0.009210341610014439</v>
       </c>
       <c r="DO9" t="n">
-        <v>0.0001225269079441205</v>
+        <v>0.01687111705541611</v>
       </c>
       <c r="DP9" t="n">
-        <v>0.0003616210306063294</v>
+        <v>0.01074858568608761</v>
       </c>
       <c r="DQ9" t="n">
-        <v>2.400896119070239e-05</v>
+        <v>0.004491094499826431</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.0007281236466951668</v>
+        <v>0.005856812000274658</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.0004175641806796193</v>
+        <v>0.000999669311568141</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.0003709435113705695</v>
+        <v>0.0119055463001132</v>
       </c>
       <c r="DU9" t="n">
-        <v>3.252361784689128e-05</v>
+        <v>0.03355712443590164</v>
       </c>
       <c r="DV9" t="n">
-        <v>0.0006658379570581019</v>
+        <v>0.03908697515726089</v>
       </c>
       <c r="DW9" t="n">
-        <v>2.099344965245109e-05</v>
+        <v>0.005381783004850149</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.0001948312565218657</v>
+        <v>0.005016823299229145</v>
       </c>
       <c r="DY9" t="n">
-        <v>0.0009739820961840451</v>
+        <v>0.03151633590459824</v>
       </c>
       <c r="DZ9" t="n">
-        <v>8.105461893137544e-05</v>
+        <v>0.03849560767412186</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.001299268682487309</v>
+        <v>8.490681648254395e-05</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.0007530990405939519</v>
+        <v>0.01576060615479946</v>
       </c>
       <c r="EC9" t="n">
-        <v>0.0001420722983311862</v>
+        <v>0.009064980782568455</v>
       </c>
       <c r="ED9" t="n">
-        <v>0.0001894893503049389</v>
+        <v>0.06175659969449043</v>
       </c>
       <c r="EE9" t="n">
-        <v>0.0002020169049501419</v>
+        <v>0.04733986780047417</v>
       </c>
       <c r="EF9" t="n">
-        <v>7.753675163257867e-05</v>
+        <v>0.03036939725279808</v>
       </c>
       <c r="EG9" t="n">
-        <v>0.0007958514615893364</v>
+        <v>0.004672443028539419</v>
       </c>
       <c r="EH9" t="n">
-        <v>0.0002969252236653119</v>
+        <v>0.02284921705722809</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.0004831530386582017</v>
+        <v>0.03437724336981773</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.0005252890987321734</v>
+        <v>0.001444080378860235</v>
       </c>
       <c r="EK9" t="n">
-        <v>0.0002290210832143202</v>
+        <v>0.004633105825632811</v>
       </c>
       <c r="EL9" t="n">
-        <v>0.0004073724849149585</v>
+        <v>0.007153254933655262</v>
       </c>
       <c r="EM9" t="n">
-        <v>0.0002690734399948269</v>
+        <v>0.006673204712569714</v>
       </c>
       <c r="EN9" t="n">
-        <v>4.62470852653496e-05</v>
+        <v>0.0057453284971416</v>
       </c>
       <c r="EO9" t="n">
-        <v>0.0003371701459400356</v>
+        <v>0.004707688931375742</v>
       </c>
       <c r="EP9" t="n">
-        <v>0.001251683686859906</v>
+        <v>0.02617691271007061</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0.0002784064272418618</v>
+        <v>0.003012863919138908</v>
       </c>
       <c r="ER9" t="n">
-        <v>0.0006734332419000566</v>
+        <v>0.03681027516722679</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.0004019586776848882</v>
+        <v>0.008532572537660599</v>
       </c>
       <c r="ET9" t="n">
-        <v>0.000808530836366117</v>
+        <v>0.0190041046589613</v>
       </c>
       <c r="EU9" t="n">
-        <v>0.0007676248205825686</v>
+        <v>0.024825818836689</v>
       </c>
       <c r="EV9" t="n">
-        <v>0.0003214679600205272</v>
+        <v>0.01258267741650343</v>
       </c>
       <c r="EW9" t="n">
-        <v>0.0003068499790970236</v>
+        <v>0.03243289887905121</v>
       </c>
       <c r="EX9" t="n">
-        <v>0.0001227208558702841</v>
+        <v>0.01152576692402363</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.001130201388150454</v>
+        <v>0.02574954181909561</v>
       </c>
       <c r="EZ9" t="n">
-        <v>0.0002591218799352646</v>
+        <v>0.00292606744915247</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.0006235883920453489</v>
+        <v>0.05738453567028046</v>
       </c>
       <c r="FB9" t="n">
-        <v>0.0001654498046264052</v>
+        <v>0.003956626635044813</v>
       </c>
       <c r="FC9" t="n">
-        <v>0.0003788160975091159</v>
+        <v>0.0011497592786327</v>
       </c>
       <c r="FD9" t="n">
-        <v>0.0003624655364546925</v>
+        <v>0.01918764412403107</v>
       </c>
       <c r="FE9" t="n">
-        <v>0.0001665427116677165</v>
+        <v>0.02231546118855476</v>
       </c>
       <c r="FF9" t="n">
-        <v>0.0002951495116576552</v>
+        <v>0.0003662935923784971</v>
       </c>
       <c r="FG9" t="n">
-        <v>4.031886055599898e-05</v>
+        <v>0.005402454640716314</v>
       </c>
       <c r="FH9" t="n">
-        <v>0.0002873086195904762</v>
+        <v>0.01711049489676952</v>
       </c>
       <c r="FI9" t="n">
-        <v>0.0003989891265518963</v>
+        <v>0.003946037497371435</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.0005801459192298353</v>
+        <v>0.02416513115167618</v>
       </c>
       <c r="FK9" t="n">
-        <v>0.000728642859030515</v>
+        <v>0.02183350548148155</v>
       </c>
       <c r="FL9" t="n">
-        <v>0.0008570532081648707</v>
+        <v>0.009054029360413551</v>
       </c>
       <c r="FM9" t="n">
-        <v>6.483068136731163e-05</v>
+        <v>0.01061260513961315</v>
       </c>
       <c r="FN9" t="n">
-        <v>5.961622082395479e-05</v>
+        <v>0.01683574356138706</v>
       </c>
       <c r="FO9" t="n">
-        <v>0.0005412393948063254</v>
+        <v>0.01155564002692699</v>
       </c>
       <c r="FP9" t="n">
-        <v>0.0003082216717302799</v>
+        <v>0.03683418408036232</v>
       </c>
       <c r="FQ9" t="n">
-        <v>0.0003033992252312601</v>
+        <v>0.06451904028654099</v>
       </c>
       <c r="FR9" t="n">
-        <v>0.0004612152697518468</v>
+        <v>0.0411004051566124</v>
       </c>
       <c r="FS9" t="n">
-        <v>0.0006425884203054011</v>
+        <v>0.07719850540161133</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.0009935819543898106</v>
+        <v>0.01681341417133808</v>
       </c>
       <c r="FU9" t="n">
-        <v>0.0002044975990429521</v>
+        <v>0.02769900858402252</v>
       </c>
       <c r="FV9" t="n">
-        <v>0.000215125794056803</v>
+        <v>0.002127803862094879</v>
       </c>
       <c r="FW9" t="n">
-        <v>0.0008126296452246606</v>
+        <v>0.05888801440596581</v>
       </c>
       <c r="FX9" t="n">
-        <v>0.0004111093294341117</v>
+        <v>0.01760274358093739</v>
       </c>
       <c r="FY9" t="n">
-        <v>0.0008492318447679281</v>
+        <v>0.008122830651700497</v>
       </c>
       <c r="FZ9" t="n">
-        <v>0.0005367668927647173</v>
+        <v>0.02189169451594353</v>
       </c>
       <c r="GA9" t="n">
-        <v>0.0003381696296855807</v>
+        <v>0.01267795637249947</v>
       </c>
       <c r="GB9" t="n">
-        <v>0.000333788339048624</v>
+        <v>0.05009192228317261</v>
       </c>
       <c r="GC9" t="n">
-        <v>0.0007425820804201066</v>
+        <v>0.007907895371317863</v>
       </c>
       <c r="GD9" t="n">
-        <v>0.0009264652035199106</v>
+        <v>0.01154272351413965</v>
       </c>
       <c r="GE9" t="n">
-        <v>0.001794241718016565</v>
+        <v>0.05513203144073486</v>
       </c>
       <c r="GF9" t="n">
-        <v>0.0003147659881506115</v>
+        <v>0.01059762388467789</v>
       </c>
       <c r="GG9" t="n">
-        <v>0.0003809766203630716</v>
+        <v>0.00518878037109971</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.007674574851989746</v>
+        <v>0.1158408597111702</v>
       </c>
       <c r="B10" t="n">
-        <v>0.0514502190053463</v>
+        <v>0.1092938184738159</v>
       </c>
       <c r="C10" t="n">
-        <v>0.004728741478174925</v>
+        <v>0.00112435594201088</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0197239276021719</v>
+        <v>0.4734638929367065</v>
       </c>
       <c r="E10" t="n">
-        <v>0.001227324828505516</v>
+        <v>0.1028001010417938</v>
       </c>
       <c r="F10" t="n">
-        <v>0.007207505870610476</v>
+        <v>0.03178735077381134</v>
       </c>
       <c r="G10" t="n">
-        <v>0.005452743731439114</v>
+        <v>0.3271169364452362</v>
       </c>
       <c r="H10" t="n">
-        <v>0.003505546599626541</v>
+        <v>0.3025287985801697</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0006368590984493494</v>
+        <v>0.1777191460132599</v>
       </c>
       <c r="J10" t="n">
-        <v>0.008464469574391842</v>
+        <v>0.09541112184524536</v>
       </c>
       <c r="K10" t="n">
-        <v>0.03317788988351822</v>
+        <v>0.1412498354911804</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0008902302943170071</v>
+        <v>0.0007712189108133316</v>
       </c>
       <c r="M10" t="n">
-        <v>0.02532978728413582</v>
+        <v>0.7611310482025146</v>
       </c>
       <c r="N10" t="n">
-        <v>0.01047265436500311</v>
+        <v>0.3018062710762024</v>
       </c>
       <c r="O10" t="n">
-        <v>0.01462677866220474</v>
+        <v>0.01686163619160652</v>
       </c>
       <c r="P10" t="n">
-        <v>0.003412113757804036</v>
+        <v>0.4035113453865051</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.002303733490407467</v>
+        <v>0.1985356509685516</v>
       </c>
       <c r="R10" t="n">
-        <v>0.0007302294834516943</v>
+        <v>0.2134918868541718</v>
       </c>
       <c r="S10" t="n">
-        <v>0.00180873810313642</v>
+        <v>0.01670815236866474</v>
       </c>
       <c r="T10" t="n">
-        <v>0.009354280307888985</v>
+        <v>0.01515615917742252</v>
       </c>
       <c r="U10" t="n">
-        <v>0.00504590105265379</v>
+        <v>0.04490602761507034</v>
       </c>
       <c r="V10" t="n">
-        <v>0.005273872520774603</v>
+        <v>0.07397665828466415</v>
       </c>
       <c r="W10" t="n">
-        <v>0.0009974308777600527</v>
+        <v>0.06636832654476166</v>
       </c>
       <c r="X10" t="n">
-        <v>0.007292462512850761</v>
+        <v>0.01163109205663204</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.00210333545692265</v>
+        <v>0.009862389415502548</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.002871146658435464</v>
+        <v>0.04771450534462929</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.002510059857740998</v>
+        <v>0.03133530542254448</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.005056667141616344</v>
+        <v>0.02019656263291836</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.007917057722806931</v>
+        <v>0.004000891000032425</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.001768226968124509</v>
+        <v>0.01094521768391132</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.0001412805868312716</v>
+        <v>0.04037284106016159</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.00206784438341856</v>
+        <v>0.0006489474326372147</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.0006096058059483767</v>
+        <v>0.05550341680645943</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.004154577851295471</v>
+        <v>0.08050620555877686</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.0009176790481433272</v>
+        <v>0.05461695790290833</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.0007991478778421879</v>
+        <v>0.04839848726987839</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.006840662099421024</v>
+        <v>0.0512516163289547</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.003900561016052961</v>
+        <v>0.1743365526199341</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.003730435855686665</v>
+        <v>0.03220819309353828</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.004226669669151306</v>
+        <v>0.09559369087219238</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.002796793123707175</v>
+        <v>0.08275119960308075</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.003412758465856314</v>
+        <v>0.0133447889238596</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.001954163424670696</v>
+        <v>0.13601353764534</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.003686413634568453</v>
+        <v>0.05832927674055099</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.001882359851151705</v>
+        <v>0.01692077703773975</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.002087074564769864</v>
+        <v>0.1960824280977249</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.04177901521325111</v>
+        <v>0.08217944949865341</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.002500751987099648</v>
+        <v>0.1410092115402222</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.0002871805336326361</v>
+        <v>0.1577790975570679</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.01016939803957939</v>
+        <v>0.5040638446807861</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.003528742585331202</v>
+        <v>0.1134216487407684</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.001184291206300259</v>
+        <v>0.02185499295592308</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.002584781032055616</v>
+        <v>0.04020453989505768</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.001365406671538949</v>
+        <v>0.114257350564003</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.0008635006379336119</v>
+        <v>0.04342842102050781</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.009266677312552929</v>
+        <v>0.01844566687941551</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.006702866405248642</v>
+        <v>0.08071462064981461</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.004316193517297506</v>
+        <v>0.008162453770637512</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.01628921926021576</v>
+        <v>0.0805077999830246</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.006929569412022829</v>
+        <v>0.0412394143640995</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.002662384184077382</v>
+        <v>0.1308721899986267</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.003477000864222646</v>
+        <v>0.0895581841468811</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.0004633669450413436</v>
+        <v>0.05624549463391304</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.01111617870628834</v>
+        <v>0.02808791399002075</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.009688952937722206</v>
+        <v>0.03157142177224159</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.004196477122604847</v>
+        <v>0.001296842936426401</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.005064765922725201</v>
+        <v>0.105631411075592</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.005598694551736116</v>
+        <v>0.1477365642786026</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.002395951887592673</v>
+        <v>0.1377161145210266</v>
       </c>
       <c r="BR10" t="n">
-        <v>0.0003685004776343703</v>
+        <v>0.01968646235764027</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.001661622663959861</v>
+        <v>0.0789877325296402</v>
       </c>
       <c r="BT10" t="n">
-        <v>0.002175344387069345</v>
+        <v>0.02388232946395874</v>
       </c>
       <c r="BU10" t="n">
-        <v>0.002462123055011034</v>
+        <v>0.007704365998506546</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.02027681283652782</v>
+        <v>0.07030097395181656</v>
       </c>
       <c r="BW10" t="n">
-        <v>0.000535531435161829</v>
+        <v>0.1058486849069595</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.001184546272270381</v>
+        <v>0.3020806312561035</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.006177582312375307</v>
+        <v>0.1614035069942474</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.009860033169388771</v>
+        <v>0.01032973080873489</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.00321478396654129</v>
+        <v>0.0759313777089119</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.000621383311226964</v>
+        <v>0.06903014332056046</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.002224010648205876</v>
+        <v>0.06686495989561081</v>
       </c>
       <c r="CD10" t="n">
-        <v>0.002967129228636622</v>
+        <v>0.05242825299501419</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.008978037163615227</v>
+        <v>0.008731668815016747</v>
       </c>
       <c r="CF10" t="n">
-        <v>0.001464233733713627</v>
+        <v>0.01784240640699863</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.0004625302099157125</v>
+        <v>0.1801311373710632</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.004143890924751759</v>
+        <v>0.04411062225699425</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.001307006110437214</v>
+        <v>0.03773590177297592</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0.001437910832464695</v>
+        <v>0.02270438149571419</v>
       </c>
       <c r="CK10" t="n">
-        <v>7.111793820513412e-05</v>
+        <v>0.07405251264572144</v>
       </c>
       <c r="CL10" t="n">
-        <v>0.0008477543597109616</v>
+        <v>0.02445959486067295</v>
       </c>
       <c r="CM10" t="n">
-        <v>0.00881533045321703</v>
+        <v>0.1063656955957413</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.01092857215553522</v>
+        <v>0.07306578755378723</v>
       </c>
       <c r="CO10" t="n">
-        <v>0.004080269485712051</v>
+        <v>0.1117822974920273</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.01218236330896616</v>
+        <v>0.2904691696166992</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.006740988232195377</v>
+        <v>0.2877670526504517</v>
       </c>
       <c r="CR10" t="n">
-        <v>0.008330906741321087</v>
+        <v>0.05133805423974991</v>
       </c>
       <c r="CS10" t="n">
-        <v>0.004336277954280376</v>
+        <v>0.1226814091205597</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.004720069468021393</v>
+        <v>0.01636066474020481</v>
       </c>
       <c r="CU10" t="n">
-        <v>0.001353271305561066</v>
+        <v>0.04966304078698158</v>
       </c>
       <c r="CV10" t="n">
-        <v>0.003064042422920465</v>
+        <v>0.04822345823049545</v>
       </c>
       <c r="CW10" t="n">
-        <v>0.007577118929475546</v>
+        <v>0.002397407777607441</v>
       </c>
       <c r="CX10" t="n">
-        <v>0.001840736251324415</v>
+        <v>0.02617126330733299</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.002782061696052551</v>
+        <v>0.1948622465133667</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.005051167216151953</v>
+        <v>0.06378073990345001</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.002228191588073969</v>
+        <v>0.02205494791269302</v>
       </c>
       <c r="DB10" t="n">
-        <v>0.001152629964053631</v>
+        <v>0.003387232776731253</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.0006103251362219453</v>
+        <v>0.0529642179608345</v>
       </c>
       <c r="DD10" t="n">
-        <v>0.0004304893955122679</v>
+        <v>0.03458094969391823</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.001898683258332312</v>
+        <v>0.1624053567647934</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.006105538923293352</v>
+        <v>0.0206574834883213</v>
       </c>
       <c r="DG10" t="n">
-        <v>0.001172232674434781</v>
+        <v>0.2357791364192963</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.005023368634283543</v>
+        <v>0.2762403190135956</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.001463364344090223</v>
+        <v>0.07723350077867508</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.003510419046506286</v>
+        <v>0.2122743278741837</v>
       </c>
       <c r="DK10" t="n">
-        <v>0.003941294271498919</v>
+        <v>0.01033495739102364</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.0007894147420302033</v>
+        <v>0.177672952413559</v>
       </c>
       <c r="DM10" t="n">
-        <v>2.057480742223561e-05</v>
+        <v>0.001209758222103119</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.006683086510747671</v>
+        <v>0.04561771079897881</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.001653862651437521</v>
+        <v>0.006594959646463394</v>
       </c>
       <c r="DP10" t="n">
-        <v>0.004297899082303047</v>
+        <v>0.1034287586808205</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.001494626048952341</v>
+        <v>0.05008645728230476</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.003084808588027954</v>
+        <v>0.02677454240620136</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.00386646599508822</v>
+        <v>0.007639257237315178</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.0005661588511429727</v>
+        <v>0.01818221807479858</v>
       </c>
       <c r="DU10" t="n">
-        <v>0.001826005987823009</v>
+        <v>0.07104408740997314</v>
       </c>
       <c r="DV10" t="n">
-        <v>0.000533382932189852</v>
+        <v>0.153348833322525</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.002515392145141959</v>
+        <v>0.06166017800569534</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.0004007722600363195</v>
+        <v>0.0011119544506073</v>
       </c>
       <c r="DY10" t="n">
-        <v>0.007436575368046761</v>
+        <v>0.2024784982204437</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.001287482446059585</v>
+        <v>0.09006442874670029</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.006947370711714029</v>
+        <v>0.007655763067305088</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.001915159169584513</v>
+        <v>0.1235106214880943</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.0002230752434115857</v>
+        <v>0.004924014210700989</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.0004709229397121817</v>
+        <v>0.1246224120259285</v>
       </c>
       <c r="EE10" t="n">
-        <v>0.0004290298093110323</v>
+        <v>0.01055589318275452</v>
       </c>
       <c r="EF10" t="n">
-        <v>0.002921260893344879</v>
+        <v>0.161374568939209</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.008258775807917118</v>
+        <v>0.02486849948763847</v>
       </c>
       <c r="EH10" t="n">
-        <v>0.002644602907821536</v>
+        <v>0.04495849832892418</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.0020984155125916</v>
+        <v>0.1990643888711929</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.001140288659371436</v>
+        <v>0.01324986666440964</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.0006714083719998598</v>
+        <v>0.01689372397959232</v>
       </c>
       <c r="EL10" t="n">
-        <v>0.0006130038527771831</v>
+        <v>0.04773884639143944</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.0009863524464890361</v>
+        <v>0.03363229334354401</v>
       </c>
       <c r="EN10" t="n">
-        <v>0.001086289645172656</v>
+        <v>0.07110961526632309</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.002916774246841669</v>
+        <v>0.007062040269374847</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.006556634791195393</v>
+        <v>0.06418678909540176</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0.002716815331950784</v>
+        <v>0.005225805565714836</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.004396701697260141</v>
+        <v>0.2244685888290405</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.006253323517739773</v>
+        <v>0.1043701991438866</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.008390545845031738</v>
+        <v>0.09887542575597763</v>
       </c>
       <c r="EU10" t="n">
-        <v>0.003063087584450841</v>
+        <v>0.03536255657672882</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.002758678514510393</v>
+        <v>0.05677907913923264</v>
       </c>
       <c r="EW10" t="n">
-        <v>0.001868155668489635</v>
+        <v>0.1268247365951538</v>
       </c>
       <c r="EX10" t="n">
-        <v>0.002068412490189075</v>
+        <v>0.05368936806917191</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.008508332073688507</v>
+        <v>0.004293342120945454</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0.0003861411823891103</v>
+        <v>0.01589276269078255</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.001250198460184038</v>
+        <v>0.2137851715087891</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.002925064414739609</v>
+        <v>0.06692272424697876</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.002332105534151196</v>
+        <v>0.01881094090640545</v>
       </c>
       <c r="FD10" t="n">
-        <v>0.001661451533436775</v>
+        <v>0.004140631295740604</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.0001204178988700733</v>
+        <v>0.07007810473442078</v>
       </c>
       <c r="FF10" t="n">
-        <v>0.0009434670209884644</v>
+        <v>0.02821078151464462</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.003271860536187887</v>
+        <v>0.02449695765972137</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.002956032287329435</v>
+        <v>0.01152807846665382</v>
       </c>
       <c r="FI10" t="n">
-        <v>0.0002845377312041819</v>
+        <v>0.01647195778787136</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.00294953235425055</v>
+        <v>0.1178001090884209</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.00428975373506546</v>
+        <v>0.03208507969975471</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.0004031342105008662</v>
+        <v>0.05470530688762665</v>
       </c>
       <c r="FM10" t="n">
-        <v>0.001651472528465092</v>
+        <v>0.05408310145139694</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.0006839048583060503</v>
+        <v>0.07480387389659882</v>
       </c>
       <c r="FO10" t="n">
-        <v>0.001837309915572405</v>
+        <v>0.08334943652153015</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.001716176979243755</v>
+        <v>0.09710686653852463</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.006142753642052412</v>
+        <v>0.3471631407737732</v>
       </c>
       <c r="FR10" t="n">
-        <v>0.001189705450087786</v>
+        <v>0.006284452974796295</v>
       </c>
       <c r="FS10" t="n">
-        <v>0.007347163744270802</v>
+        <v>0.04058857634663582</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.007010029628872871</v>
+        <v>0.2689686417579651</v>
       </c>
       <c r="FU10" t="n">
-        <v>0.001439493964426219</v>
+        <v>0.09161354601383209</v>
       </c>
       <c r="FV10" t="n">
-        <v>0.00332227093167603</v>
+        <v>0.1204522848129272</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.002699117176234722</v>
+        <v>0.2193494141101837</v>
       </c>
       <c r="FX10" t="n">
-        <v>0.0006421773578040302</v>
+        <v>0.02435937151312828</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.00578731345012784</v>
+        <v>0.008669988252222538</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.005749688483774662</v>
+        <v>0.04539455100893974</v>
       </c>
       <c r="GA10" t="n">
-        <v>0.001652746694162488</v>
+        <v>0.1572174280881882</v>
       </c>
       <c r="GB10" t="n">
-        <v>0.0006809160695411265</v>
+        <v>0.1838418841362</v>
       </c>
       <c r="GC10" t="n">
-        <v>0.0008881638641469181</v>
+        <v>0.04941176250576973</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.004556110594421625</v>
+        <v>0.02244917303323746</v>
       </c>
       <c r="GE10" t="n">
-        <v>0.00790958758443594</v>
+        <v>0.02895365282893181</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.002882032888010144</v>
+        <v>0.01763667352497578</v>
       </c>
       <c r="GG10" t="n">
-        <v>0.001459401100873947</v>
+        <v>0.07336250692605972</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.0009823718573898077</v>
+        <v>0.00919321458786726</v>
       </c>
       <c r="B11" t="n">
-        <v>0.04466086998581886</v>
+        <v>0.02443988621234894</v>
       </c>
       <c r="C11" t="n">
-        <v>0.003515479387715459</v>
+        <v>0.00530294282361865</v>
       </c>
       <c r="D11" t="n">
-        <v>0.01644807867705822</v>
+        <v>0.00959798414260149</v>
       </c>
       <c r="E11" t="n">
-        <v>0.006263350136578083</v>
+        <v>0.001434810925275087</v>
       </c>
       <c r="F11" t="n">
-        <v>0.03475905954837799</v>
+        <v>0.03052883595228195</v>
       </c>
       <c r="G11" t="n">
-        <v>0.002283141249790788</v>
+        <v>0.00512954406440258</v>
       </c>
       <c r="H11" t="n">
-        <v>0.01843822933733463</v>
+        <v>0.0137452632188797</v>
       </c>
       <c r="I11" t="n">
-        <v>0.002263189293444157</v>
+        <v>0.0008886581053957343</v>
       </c>
       <c r="J11" t="n">
-        <v>0.006616956554353237</v>
+        <v>0.005423339083790779</v>
       </c>
       <c r="K11" t="n">
-        <v>0.03915110975503922</v>
+        <v>0.03028135187923908</v>
       </c>
       <c r="L11" t="n">
-        <v>0.001258694566786289</v>
+        <v>0.008981877937912941</v>
       </c>
       <c r="M11" t="n">
-        <v>0.01190534140914679</v>
+        <v>0.0007188478484749794</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0003792187198996544</v>
+        <v>0.01409945450723171</v>
       </c>
       <c r="O11" t="n">
-        <v>0.03119133040308952</v>
+        <v>0.03397148102521896</v>
       </c>
       <c r="P11" t="n">
-        <v>0.002758806105703115</v>
+        <v>0.002845981623977423</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.004020505119115114</v>
+        <v>0.005051316227763891</v>
       </c>
       <c r="R11" t="n">
-        <v>0.00460001127794385</v>
+        <v>0.004658407997339964</v>
       </c>
       <c r="S11" t="n">
-        <v>0.001912339124828577</v>
+        <v>0.0006508788792416453</v>
       </c>
       <c r="T11" t="n">
-        <v>0.003043489996343851</v>
+        <v>0.004916440695524216</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0009830155177041888</v>
+        <v>0.004297791514545679</v>
       </c>
       <c r="V11" t="n">
-        <v>0.004693375434726477</v>
+        <v>0.007225631270557642</v>
       </c>
       <c r="W11" t="n">
-        <v>0.009142655879259109</v>
+        <v>0.008226297795772552</v>
       </c>
       <c r="X11" t="n">
-        <v>0.003707782365381718</v>
+        <v>0.004033484496176243</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.003497312776744366</v>
+        <v>0.0009404305019415915</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.00523864571005106</v>
+        <v>0.001816552132368088</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.005036837421357632</v>
+        <v>0.003155640093609691</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.0001130395103245974</v>
+        <v>0.0009230214636772871</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.003523677820339799</v>
+        <v>0.003881106385961175</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.0004223575233481824</v>
+        <v>0.001260406104847789</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.001105326926335692</v>
+        <v>0.005170226097106934</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.003496297169476748</v>
+        <v>0.009409906342625618</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.001855561044067144</v>
+        <v>0.00649670884013176</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.001411704579368234</v>
+        <v>0.004005082882940769</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.002044110093265772</v>
+        <v>0.01511832140386105</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.0006429433124139905</v>
+        <v>0.003184811677783728</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.00596765847876668</v>
+        <v>0.0001242850557900965</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.005545796826481819</v>
+        <v>0.00740627758204937</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.001322061172686517</v>
+        <v>0.005798350088298321</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.001864543068222702</v>
+        <v>0.003442427841946483</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.001718710642307997</v>
+        <v>0.0005332573782652617</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.008056217804551125</v>
+        <v>0.003389397636055946</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.001216088770888746</v>
+        <v>0.0005633065011352301</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.003753571771085262</v>
+        <v>0.004495278000831604</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.003495347918942571</v>
+        <v>0.001406132476404309</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.002086298074573278</v>
+        <v>0.003432898316532373</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.03035757504403591</v>
+        <v>0.02982061728835106</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.000734990113414824</v>
+        <v>0.008349098265171051</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.004532956052571535</v>
+        <v>0.000250206037890166</v>
       </c>
       <c r="AX11" t="n">
-        <v>3.991939593106508e-05</v>
+        <v>0.009995779022574425</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.02076854929327965</v>
+        <v>0.01748027838766575</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.00649078655987978</v>
+        <v>0.001389514305628836</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.004607755225151777</v>
+        <v>0.0050068199634552</v>
       </c>
       <c r="BB11" t="n">
-        <v>0.005727990064769983</v>
+        <v>0.001767102628946304</v>
       </c>
       <c r="BC11" t="n">
-        <v>7.225223816931248e-05</v>
+        <v>0.001092968159355223</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.01438774541020393</v>
+        <v>0.004550236277282238</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.0108901634812355</v>
+        <v>0.005512507632374763</v>
       </c>
       <c r="BF11" t="n">
-        <v>0.0002466526057105511</v>
+        <v>0.007356851827353239</v>
       </c>
       <c r="BG11" t="n">
-        <v>0.005194114055484533</v>
+        <v>0.000151132931932807</v>
       </c>
       <c r="BH11" t="n">
-        <v>0.01103658229112625</v>
+        <v>0.002710832515731454</v>
       </c>
       <c r="BI11" t="n">
-        <v>0.004391963593661785</v>
+        <v>0.0002000338863581419</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.004375271964818239</v>
+        <v>0.009207822382450104</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.003948495723307133</v>
+        <v>0.004200343508273363</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.003926122095435858</v>
+        <v>0.0008547598263248801</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.0127804446965456</v>
+        <v>0.008356001228094101</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.003887517843395472</v>
+        <v>0.0002866740105673671</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.0005181536544114351</v>
+        <v>0.0005162761081010103</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.004428843501955271</v>
+        <v>0.005942050833255053</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.0008497723611071706</v>
+        <v>0.007166125811636448</v>
       </c>
       <c r="BR11" t="n">
-        <v>0.001201831735670567</v>
+        <v>0.009592789225280285</v>
       </c>
       <c r="BS11" t="n">
-        <v>0.003973053768277168</v>
+        <v>0.001875343499705195</v>
       </c>
       <c r="BT11" t="n">
-        <v>0.0006242255913093686</v>
+        <v>0.006960866041481495</v>
       </c>
       <c r="BU11" t="n">
-        <v>0.002530808327719569</v>
+        <v>0.001041899900883436</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.01617548801004887</v>
+        <v>0.01905765198171139</v>
       </c>
       <c r="BW11" t="n">
-        <v>0.003381146350875497</v>
+        <v>0.003964626230299473</v>
       </c>
       <c r="BX11" t="n">
-        <v>0.003339724149554968</v>
+        <v>0.00908513180911541</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.0009254695032723248</v>
+        <v>0.005016248673200607</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0.006808126345276833</v>
+        <v>0.01112811360508204</v>
       </c>
       <c r="CA11" t="n">
-        <v>0.0007109149009920657</v>
+        <v>0.002212357940152287</v>
       </c>
       <c r="CB11" t="n">
-        <v>0.002217743545770645</v>
+        <v>0.0008329558186233044</v>
       </c>
       <c r="CC11" t="n">
-        <v>0.004320446867495775</v>
+        <v>0.004541288129985332</v>
       </c>
       <c r="CD11" t="n">
-        <v>5.40488981641829e-05</v>
+        <v>0.003040199168026447</v>
       </c>
       <c r="CE11" t="n">
-        <v>0.006603694520890713</v>
+        <v>0.008528904989361763</v>
       </c>
       <c r="CF11" t="n">
-        <v>0.003557434305548668</v>
+        <v>0.0001268366468138993</v>
       </c>
       <c r="CG11" t="n">
-        <v>0.002977576572448015</v>
+        <v>0.001061094691976905</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.0003191625291947275</v>
+        <v>0.0009833239018917084</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.00512135773897171</v>
+        <v>0.007350178435444832</v>
       </c>
       <c r="CJ11" t="n">
-        <v>0.003253479022532701</v>
+        <v>0.002583532594144344</v>
       </c>
       <c r="CK11" t="n">
-        <v>0.004226953722536564</v>
+        <v>0.001494886470027268</v>
       </c>
       <c r="CL11" t="n">
-        <v>0.003101442940533161</v>
+        <v>0.001367785967886448</v>
       </c>
       <c r="CM11" t="n">
-        <v>0.008167543448507786</v>
+        <v>0.003317746100947261</v>
       </c>
       <c r="CN11" t="n">
-        <v>0.006645416840910912</v>
+        <v>0.01218102034181356</v>
       </c>
       <c r="CO11" t="n">
-        <v>0.001045655459165573</v>
+        <v>0.009780369699001312</v>
       </c>
       <c r="CP11" t="n">
-        <v>0.007779540494084358</v>
+        <v>0.01179128605872393</v>
       </c>
       <c r="CQ11" t="n">
-        <v>0.004933440126478672</v>
+        <v>0.003527052234858274</v>
       </c>
       <c r="CR11" t="n">
-        <v>0.002085589338093996</v>
+        <v>0.001594582688994706</v>
       </c>
       <c r="CS11" t="n">
-        <v>0.006693204864859581</v>
+        <v>0.003736102022230625</v>
       </c>
       <c r="CT11" t="n">
-        <v>0.006942763924598694</v>
+        <v>0.003675445448607206</v>
       </c>
       <c r="CU11" t="n">
-        <v>0.000555308535695076</v>
+        <v>9.737373329699039e-05</v>
       </c>
       <c r="CV11" t="n">
-        <v>0.0002060069818980992</v>
+        <v>0.001250430708751082</v>
       </c>
       <c r="CW11" t="n">
-        <v>0.005410604644566774</v>
+        <v>0.006945398636162281</v>
       </c>
       <c r="CX11" t="n">
-        <v>0.00349327689036727</v>
+        <v>0.001083284732885659</v>
       </c>
       <c r="CY11" t="n">
-        <v>0.004688424523919821</v>
+        <v>0.0001464553643018007</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.001160304993391037</v>
+        <v>0.0003222411032766104</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.004861917346715927</v>
+        <v>0.007890211418271065</v>
       </c>
       <c r="DB11" t="n">
-        <v>0.002859982894733548</v>
+        <v>0.001209429930895567</v>
       </c>
       <c r="DC11" t="n">
-        <v>0.006180346012115479</v>
+        <v>0.00147266045678407</v>
       </c>
       <c r="DD11" t="n">
-        <v>0.001466575893573463</v>
+        <v>0.00072012486634776</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.003310577245429158</v>
+        <v>0.0006747802253812551</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.005637920461595058</v>
+        <v>0.005911983549594879</v>
       </c>
       <c r="DG11" t="n">
-        <v>0.001313480781391263</v>
+        <v>0.00231995084322989</v>
       </c>
       <c r="DH11" t="n">
-        <v>0.01962032727897167</v>
+        <v>0.0006577558815479279</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.008208285085856915</v>
+        <v>0.002916124183684587</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.006286503747105598</v>
+        <v>0.002274146070703864</v>
       </c>
       <c r="DK11" t="n">
-        <v>0.008093620650470257</v>
+        <v>0.001781747210770845</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.009938947856426239</v>
+        <v>0.01095916796475649</v>
       </c>
       <c r="DM11" t="n">
-        <v>0.01025056652724743</v>
+        <v>0.01216656528413296</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.0001910746941575781</v>
+        <v>0.0001988078001886606</v>
       </c>
       <c r="DO11" t="n">
-        <v>0.002117140684276819</v>
+        <v>0.003617967246100307</v>
       </c>
       <c r="DP11" t="n">
-        <v>0.004174238070845604</v>
+        <v>0.003117067739367485</v>
       </c>
       <c r="DQ11" t="n">
-        <v>0.001257563126273453</v>
+        <v>0.003891316009685397</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.003344160970300436</v>
+        <v>0.0003407505573704839</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.002075479831546545</v>
+        <v>0.00222355080768466</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.0009673734311945736</v>
+        <v>7.185561116784811e-05</v>
       </c>
       <c r="DU11" t="n">
-        <v>0.001238440629094839</v>
+        <v>0.006181492935866117</v>
       </c>
       <c r="DV11" t="n">
-        <v>0.0004872388672083616</v>
+        <v>0.003311078296974301</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.0002931717317551374</v>
+        <v>0.002608671085909009</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.000225450232392177</v>
+        <v>0.001826928230002522</v>
       </c>
       <c r="DY11" t="n">
-        <v>0.001079966546967626</v>
+        <v>0.00571047980338335</v>
       </c>
       <c r="DZ11" t="n">
-        <v>0.0007088547572493553</v>
+        <v>0.003739028237760067</v>
       </c>
       <c r="EA11" t="n">
-        <v>0.0003521800972521305</v>
+        <v>0.002689575077965856</v>
       </c>
       <c r="EB11" t="n">
-        <v>0.002224750118330121</v>
+        <v>0.005269030574709177</v>
       </c>
       <c r="EC11" t="n">
-        <v>0.000665773986838758</v>
+        <v>0.001370372134260833</v>
       </c>
       <c r="ED11" t="n">
-        <v>0.0002135788090527058</v>
+        <v>0.001354693900793791</v>
       </c>
       <c r="EE11" t="n">
-        <v>0.005163223948329687</v>
+        <v>0.009553762152791023</v>
       </c>
       <c r="EF11" t="n">
-        <v>0.001094036735594273</v>
+        <v>0.001623511896468699</v>
       </c>
       <c r="EG11" t="n">
-        <v>0.005355942063033581</v>
+        <v>2.739275805652142e-05</v>
       </c>
       <c r="EH11" t="n">
-        <v>0.002468867460265756</v>
+        <v>0.003562834113836288</v>
       </c>
       <c r="EI11" t="n">
-        <v>0.001412643701769412</v>
+        <v>0.001736584352329373</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.00145775789860636</v>
+        <v>0.00419731019064784</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.002575784688815475</v>
+        <v>0.004376964643597603</v>
       </c>
       <c r="EL11" t="n">
-        <v>0.002928935922682285</v>
+        <v>0.0003134744765702635</v>
       </c>
       <c r="EM11" t="n">
-        <v>0.001945028081536293</v>
+        <v>0.0006710857851430774</v>
       </c>
       <c r="EN11" t="n">
-        <v>0.0009623387013562024</v>
+        <v>0.0001257130061276257</v>
       </c>
       <c r="EO11" t="n">
-        <v>0.001557738287374377</v>
+        <v>0.002785765565931797</v>
       </c>
       <c r="EP11" t="n">
-        <v>0.002198531292378902</v>
+        <v>0.006030931137502193</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0.00331405270844698</v>
+        <v>0.0002097896067425609</v>
       </c>
       <c r="ER11" t="n">
-        <v>0.003633967600762844</v>
+        <v>0.002639602404087782</v>
       </c>
       <c r="ES11" t="n">
-        <v>0.00135824887547642</v>
+        <v>0.007005384191870689</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.00493323989212513</v>
+        <v>0.005000276491045952</v>
       </c>
       <c r="EU11" t="n">
-        <v>0.005013062618672848</v>
+        <v>0.0009880110155791044</v>
       </c>
       <c r="EV11" t="n">
-        <v>0.01322829909622669</v>
+        <v>0.003705273615196347</v>
       </c>
       <c r="EW11" t="n">
-        <v>3.510297392494977e-05</v>
+        <v>0.001953029073774815</v>
       </c>
       <c r="EX11" t="n">
-        <v>0.0005668324884027243</v>
+        <v>0.002890534000471234</v>
       </c>
       <c r="EY11" t="n">
-        <v>0.004747451283037663</v>
+        <v>0.009136831387877464</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0.002301204949617386</v>
+        <v>0.0005645250203087926</v>
       </c>
       <c r="FA11" t="n">
-        <v>0.00306744291447103</v>
+        <v>0.0004364121705293655</v>
       </c>
       <c r="FB11" t="n">
-        <v>4.146393621340394e-05</v>
+        <v>0.001052482519298792</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.004468474537134171</v>
+        <v>0.007035100366920233</v>
       </c>
       <c r="FD11" t="n">
-        <v>0.004804325290024281</v>
+        <v>0.003229315858334303</v>
       </c>
       <c r="FE11" t="n">
-        <v>0.005042115692049265</v>
+        <v>0.001432781806215644</v>
       </c>
       <c r="FF11" t="n">
-        <v>0.003057046793401241</v>
+        <v>0.002001085784286261</v>
       </c>
       <c r="FG11" t="n">
-        <v>0.0003483470936771482</v>
+        <v>0.0006901274900883436</v>
       </c>
       <c r="FH11" t="n">
-        <v>0.002438662573695183</v>
+        <v>0.007206200156360865</v>
       </c>
       <c r="FI11" t="n">
-        <v>0.001241606893017888</v>
+        <v>0.004733596928417683</v>
       </c>
       <c r="FJ11" t="n">
-        <v>0.00736683513969183</v>
+        <v>0.00500190258026123</v>
       </c>
       <c r="FK11" t="n">
-        <v>0.001188969938084483</v>
+        <v>0.004781781230121851</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.002782085444778204</v>
+        <v>0.009221663698554039</v>
       </c>
       <c r="FM11" t="n">
-        <v>0.003530731191858649</v>
+        <v>0.004284084774553776</v>
       </c>
       <c r="FN11" t="n">
-        <v>0.0005720630288124084</v>
+        <v>0.0159065555781126</v>
       </c>
       <c r="FO11" t="n">
-        <v>0.001734194927848876</v>
+        <v>0.009195553138852119</v>
       </c>
       <c r="FP11" t="n">
-        <v>0.00522454921156168</v>
+        <v>0.0007743741734884679</v>
       </c>
       <c r="FQ11" t="n">
-        <v>0.005051069427281618</v>
+        <v>0.009062773548066616</v>
       </c>
       <c r="FR11" t="n">
-        <v>0.003885835176333785</v>
+        <v>0.007552758790552616</v>
       </c>
       <c r="FS11" t="n">
-        <v>0.001589900348335505</v>
+        <v>0.009388014674186707</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.008662219159305096</v>
+        <v>0.004493081010878086</v>
       </c>
       <c r="FU11" t="n">
-        <v>0.00566277839243412</v>
+        <v>0.005707774311304092</v>
       </c>
       <c r="FV11" t="n">
-        <v>0.003989316523075104</v>
+        <v>0.0006141198100522161</v>
       </c>
       <c r="FW11" t="n">
-        <v>0.001121761742979288</v>
+        <v>0.019049271941185</v>
       </c>
       <c r="FX11" t="n">
-        <v>0.0002876194193959236</v>
+        <v>0.004977318923920393</v>
       </c>
       <c r="FY11" t="n">
-        <v>0.006718738004565239</v>
+        <v>0.004399450030177832</v>
       </c>
       <c r="FZ11" t="n">
-        <v>0.0008527797181159258</v>
+        <v>0.001024960307404399</v>
       </c>
       <c r="GA11" t="n">
-        <v>0.0008149947389028966</v>
+        <v>0.006941848900169134</v>
       </c>
       <c r="GB11" t="n">
-        <v>5.322194192558527e-05</v>
+        <v>3.091210965067148e-05</v>
       </c>
       <c r="GC11" t="n">
-        <v>0.003758735023438931</v>
+        <v>0.008683568798005581</v>
       </c>
       <c r="GD11" t="n">
-        <v>0.007052295841276646</v>
+        <v>0.007942194119095802</v>
       </c>
       <c r="GE11" t="n">
-        <v>0.0136449821293354</v>
+        <v>0.001565039972774684</v>
       </c>
       <c r="GF11" t="n">
-        <v>0.001493894262239337</v>
+        <v>6.496888818219304e-05</v>
       </c>
       <c r="GG11" t="n">
-        <v>8.581543806940317e-05</v>
+        <v>0.004437107127159834</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>3.873959212796763e-05</v>
+        <v>0.0001831243425840512</v>
       </c>
       <c r="B12" t="n">
-        <v>0.0007118219509720802</v>
+        <v>0.007599782198667526</v>
       </c>
       <c r="C12" t="n">
-        <v>5.971807331661694e-05</v>
+        <v>0.002048637019470334</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0004599877574946731</v>
+        <v>0.01167897693812847</v>
       </c>
       <c r="E12" t="n">
-        <v>4.565145718515851e-05</v>
+        <v>0.004314735531806946</v>
       </c>
       <c r="F12" t="n">
-        <v>5.702471025870182e-05</v>
+        <v>0.006857620552182198</v>
       </c>
       <c r="G12" t="n">
-        <v>6.910783849889413e-05</v>
+        <v>0.009258163161575794</v>
       </c>
       <c r="H12" t="n">
-        <v>8.333437290275469e-05</v>
+        <v>0.007578922901302576</v>
       </c>
       <c r="I12" t="n">
-        <v>2.471804509696085e-05</v>
+        <v>0.00316293747164309</v>
       </c>
       <c r="J12" t="n">
-        <v>9.718490764498711e-05</v>
+        <v>0.0001470735878683627</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0005101463757455349</v>
+        <v>0.004091409500688314</v>
       </c>
       <c r="L12" t="n">
-        <v>1.619487011339515e-05</v>
+        <v>0.002406789921224117</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0004395788128022105</v>
+        <v>0.01686125621199608</v>
       </c>
       <c r="N12" t="n">
-        <v>0.0001750793162500486</v>
+        <v>0.01006288360804319</v>
       </c>
       <c r="O12" t="n">
-        <v>0.0001758097496349365</v>
+        <v>0.00585140148177743</v>
       </c>
       <c r="P12" t="n">
-        <v>1.953396349563263e-05</v>
+        <v>0.01032030954957008</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.024394340580329e-05</v>
+        <v>0.006288109347224236</v>
       </c>
       <c r="R12" t="n">
-        <v>4.91360951855313e-05</v>
+        <v>0.001909304060973227</v>
       </c>
       <c r="S12" t="n">
-        <v>2.149976171494927e-05</v>
+        <v>0.000986829400062561</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0001207035529660061</v>
+        <v>1.25170627143234e-05</v>
       </c>
       <c r="U12" t="n">
-        <v>2.191200110246427e-05</v>
+        <v>0.002205800265073776</v>
       </c>
       <c r="V12" t="n">
-        <v>6.397430115612224e-05</v>
+        <v>0.001421522116288543</v>
       </c>
       <c r="W12" t="n">
-        <v>6.652876436419319e-06</v>
+        <v>0.002241213107481599</v>
       </c>
       <c r="X12" t="n">
-        <v>6.888064672239125e-05</v>
+        <v>0.001733635552227497</v>
       </c>
       <c r="Y12" t="n">
-        <v>7.468694093404338e-05</v>
+        <v>0.0004022529465146363</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.291048026061617e-05</v>
+        <v>0.001015017740428448</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.530458292923868e-05</v>
+        <v>0.0002542130532674491</v>
       </c>
       <c r="AB12" t="n">
-        <v>6.32398878224194e-05</v>
+        <v>0.0009275685297325253</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.0001458090700907633</v>
+        <v>0.001348510151728988</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.634678255868494e-06</v>
+        <v>0.001988462405279279</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.110747507482301e-05</v>
+        <v>0.001053759944625199</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.945929372799583e-05</v>
+        <v>0.001152629032731056</v>
       </c>
       <c r="AG12" t="n">
-        <v>9.996401786338538e-06</v>
+        <v>0.004874009639024734</v>
       </c>
       <c r="AH12" t="n">
-        <v>3.094286512350664e-05</v>
+        <v>0.002488537458702922</v>
       </c>
       <c r="AI12" t="n">
-        <v>9.078790753846988e-06</v>
+        <v>0.003040411043912172</v>
       </c>
       <c r="AJ12" t="n">
-        <v>7.055800324451411e-06</v>
+        <v>0.001100489986129105</v>
       </c>
       <c r="AK12" t="n">
-        <v>4.054068267578259e-05</v>
+        <v>0.001067674602381885</v>
       </c>
       <c r="AL12" t="n">
-        <v>6.459847645601258e-05</v>
+        <v>0.004451419226825237</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.924228672578465e-05</v>
+        <v>0.002540376735851169</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.823973434511572e-05</v>
+        <v>0.002069950103759766</v>
       </c>
       <c r="AO12" t="n">
-        <v>7.9302531958092e-05</v>
+        <v>0.0005091021303087473</v>
       </c>
       <c r="AP12" t="n">
-        <v>7.647562597412616e-05</v>
+        <v>0.002127550775185227</v>
       </c>
       <c r="AQ12" t="n">
-        <v>3.141092747682706e-05</v>
+        <v>0.002885900437831879</v>
       </c>
       <c r="AR12" t="n">
-        <v>4.201558840577491e-05</v>
+        <v>0.001652274164371192</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.058525933534838e-05</v>
+        <v>7.733932579867542e-05</v>
       </c>
       <c r="AT12" t="n">
-        <v>6.078987280488946e-05</v>
+        <v>0.004843645263463259</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.0005009315791539848</v>
+        <v>0.00461601372808218</v>
       </c>
       <c r="AV12" t="n">
-        <v>9.42764017963782e-06</v>
+        <v>0.004967165179550648</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.000102168633020483</v>
+        <v>0.001639914698898792</v>
       </c>
       <c r="AX12" t="n">
-        <v>2.00393969862489e-05</v>
+        <v>0.01038352400064468</v>
       </c>
       <c r="AY12" t="n">
-        <v>3.649305654107593e-06</v>
+        <v>0.006450580433011055</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.371123835269827e-05</v>
+        <v>0.001220555393956602</v>
       </c>
       <c r="BA12" t="n">
-        <v>5.091380444355309e-06</v>
+        <v>0.0008845347329042852</v>
       </c>
       <c r="BB12" t="n">
-        <v>9.89046020549722e-06</v>
+        <v>0.001899967435747385</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.213493280578405e-05</v>
+        <v>0.0005322095821611583</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.0001407576346537098</v>
+        <v>0.0009511281969025731</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.0001261145953321829</v>
+        <v>0.0004192166961729527</v>
       </c>
       <c r="BF12" t="n">
-        <v>9.36411670409143e-05</v>
+        <v>0.002258365973830223</v>
       </c>
       <c r="BG12" t="n">
-        <v>0.0001861139753600582</v>
+        <v>0.004386196378618479</v>
       </c>
       <c r="BH12" t="n">
-        <v>3.422314330236986e-05</v>
+        <v>0.0004000411427114159</v>
       </c>
       <c r="BI12" t="n">
-        <v>8.042803528951481e-05</v>
+        <v>0.003235969925299287</v>
       </c>
       <c r="BJ12" t="n">
-        <v>6.400972051778808e-05</v>
+        <v>0.002208560472354293</v>
       </c>
       <c r="BK12" t="n">
-        <v>4.481031282921322e-05</v>
+        <v>0.001440999796614051</v>
       </c>
       <c r="BL12" t="n">
-        <v>9.671056614024565e-05</v>
+        <v>0.001215846044942737</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.0001215472948388197</v>
+        <v>0.002262586262077093</v>
       </c>
       <c r="BN12" t="n">
-        <v>7.281135185621679e-05</v>
+        <v>0.0013961938675493</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.367211461911211e-05</v>
+        <v>0.003410723060369492</v>
       </c>
       <c r="BP12" t="n">
-        <v>6.427298649214208e-05</v>
+        <v>0.001263201236724854</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.568270378513262e-05</v>
+        <v>0.0003859737189486623</v>
       </c>
       <c r="BR12" t="n">
-        <v>1.133208661485696e-05</v>
+        <v>0.001006203005090356</v>
       </c>
       <c r="BS12" t="n">
-        <v>3.611421561799943e-06</v>
+        <v>0.000715909933205694</v>
       </c>
       <c r="BT12" t="n">
-        <v>1.70977546076756e-05</v>
+        <v>0.000542738358490169</v>
       </c>
       <c r="BU12" t="n">
-        <v>4.957635974278674e-05</v>
+        <v>0.001412879093550146</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.0002524876035749912</v>
+        <v>0.004450565669685602</v>
       </c>
       <c r="BW12" t="n">
-        <v>5.819808211526833e-05</v>
+        <v>0.002408267930150032</v>
       </c>
       <c r="BX12" t="n">
-        <v>7.326243940042332e-05</v>
+        <v>0.004757765680551529</v>
       </c>
       <c r="BY12" t="n">
-        <v>3.102574919466861e-05</v>
+        <v>0.002928080968558788</v>
       </c>
       <c r="BZ12" t="n">
-        <v>6.979708268772811e-05</v>
+        <v>0.003652147483080626</v>
       </c>
       <c r="CA12" t="n">
-        <v>2.81898828689009e-05</v>
+        <v>0.001835232134908438</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.081358954659663e-05</v>
+        <v>0.0004423061618581414</v>
       </c>
       <c r="CC12" t="n">
-        <v>4.705345054389909e-05</v>
+        <v>0.0002246733492938802</v>
       </c>
       <c r="CD12" t="n">
-        <v>2.950973066617735e-05</v>
+        <v>2.60050073848106e-05</v>
       </c>
       <c r="CE12" t="n">
-        <v>0.0001236946845892817</v>
+        <v>0.001666812575422227</v>
       </c>
       <c r="CF12" t="n">
-        <v>4.068862108397298e-05</v>
+        <v>0.0005163747118785977</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.958558590966277e-05</v>
+        <v>0.00404617004096508</v>
       </c>
       <c r="CH12" t="n">
-        <v>3.569812906789593e-05</v>
+        <v>0.0006853688391856849</v>
       </c>
       <c r="CI12" t="n">
-        <v>7.476319751731353e-06</v>
+        <v>0.001654306543059647</v>
       </c>
       <c r="CJ12" t="n">
-        <v>2.461455551383551e-05</v>
+        <v>0.0002571214572526515</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.386396434099879e-05</v>
+        <v>0.001608642283827066</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.082173523376696e-05</v>
+        <v>0.0008164505125023425</v>
       </c>
       <c r="CM12" t="n">
-        <v>0.0001346478093182668</v>
+        <v>0.002220893278717995</v>
       </c>
       <c r="CN12" t="n">
-        <v>8.470241300528869e-05</v>
+        <v>0.001171670388430357</v>
       </c>
       <c r="CO12" t="n">
-        <v>3.88189364457503e-05</v>
+        <v>0.003236460033804178</v>
       </c>
       <c r="CP12" t="n">
-        <v>0.0001340863527730107</v>
+        <v>0.004645855166018009</v>
       </c>
       <c r="CQ12" t="n">
-        <v>5.809570575365797e-05</v>
+        <v>0.0002038430975517258</v>
       </c>
       <c r="CR12" t="n">
-        <v>9.780182153917849e-05</v>
+        <v>0.00112482812255621</v>
       </c>
       <c r="CS12" t="n">
-        <v>8.547035395167768e-05</v>
+        <v>0.003897866001352668</v>
       </c>
       <c r="CT12" t="n">
-        <v>0.0001456870813854039</v>
+        <v>0.0003081016766373068</v>
       </c>
       <c r="CU12" t="n">
-        <v>2.098981894960161e-06</v>
+        <v>0.0014076828956604</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.937770477728918e-05</v>
+        <v>2.214070991612971e-05</v>
       </c>
       <c r="CW12" t="n">
-        <v>9.943743498297408e-05</v>
+        <v>0.001264185993932188</v>
       </c>
       <c r="CX12" t="n">
-        <v>5.602520104730502e-05</v>
+        <v>0.000577816681470722</v>
       </c>
       <c r="CY12" t="n">
-        <v>7.03231489751488e-05</v>
+        <v>0.004429422318935394</v>
       </c>
       <c r="CZ12" t="n">
-        <v>4.277424886822701e-05</v>
+        <v>0.002008342882618308</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.497363336966373e-05</v>
+        <v>0.001828495180234313</v>
       </c>
       <c r="DB12" t="n">
-        <v>2.457107439113315e-05</v>
+        <v>9.132208651863039e-05</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.259800021420233e-05</v>
+        <v>0.001756378100253642</v>
       </c>
       <c r="DD12" t="n">
-        <v>9.058662726602051e-06</v>
+        <v>0.001265014871023595</v>
       </c>
       <c r="DE12" t="n">
-        <v>3.719333108165301e-05</v>
+        <v>0.003725118469446898</v>
       </c>
       <c r="DF12" t="n">
-        <v>0.0001248469343408942</v>
+        <v>0.001783750485628843</v>
       </c>
       <c r="DG12" t="n">
-        <v>1.214786607306451e-05</v>
+        <v>0.002812901977449656</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.0001698613341432065</v>
+        <v>0.005194993689656258</v>
       </c>
       <c r="DI12" t="n">
-        <v>2.099773155350704e-06</v>
+        <v>0.0008053646888583899</v>
       </c>
       <c r="DJ12" t="n">
-        <v>3.869740612572059e-05</v>
+        <v>0.008048364892601967</v>
       </c>
       <c r="DK12" t="n">
-        <v>8.65921174408868e-05</v>
+        <v>0.0007897434988990426</v>
       </c>
       <c r="DL12" t="n">
-        <v>3.157453465973958e-05</v>
+        <v>0.00514625757932663</v>
       </c>
       <c r="DM12" t="n">
-        <v>5.574322130996734e-06</v>
+        <v>0.002463990822434425</v>
       </c>
       <c r="DN12" t="n">
-        <v>5.028459054301493e-05</v>
+        <v>0.00177219114266336</v>
       </c>
       <c r="DO12" t="n">
-        <v>4.021386848762631e-05</v>
+        <v>0.002374644158408046</v>
       </c>
       <c r="DP12" t="n">
-        <v>6.01084393565543e-05</v>
+        <v>0.0006372163770720363</v>
       </c>
       <c r="DQ12" t="n">
-        <v>9.104107448365539e-06</v>
+        <v>0.0002507616300135851</v>
       </c>
       <c r="DR12" t="n">
-        <v>8.382355736102909e-05</v>
+        <v>0.0005032883491367102</v>
       </c>
       <c r="DS12" t="n">
-        <v>5.752580545959063e-05</v>
+        <v>0.001297085895203054</v>
       </c>
       <c r="DT12" t="n">
-        <v>4.842589987674728e-06</v>
+        <v>0.0002764763776212931</v>
       </c>
       <c r="DU12" t="n">
-        <v>2.449860221531708e-05</v>
+        <v>0.003433308564126492</v>
       </c>
       <c r="DV12" t="n">
-        <v>4.078926940564997e-05</v>
+        <v>0.004503675270825624</v>
       </c>
       <c r="DW12" t="n">
-        <v>1.812278696888825e-06</v>
+        <v>0.001219776342622936</v>
       </c>
       <c r="DX12" t="n">
-        <v>3.420856955926865e-05</v>
+        <v>0.001226061023771763</v>
       </c>
       <c r="DY12" t="n">
-        <v>6.609357660636306e-05</v>
+        <v>0.004720409400761127</v>
       </c>
       <c r="DZ12" t="n">
-        <v>7.299349817913026e-07</v>
+        <v>0.001872224034741521</v>
       </c>
       <c r="EA12" t="n">
-        <v>7.451794226653874e-05</v>
+        <v>0.0006872187368571758</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.909321872517467e-05</v>
+        <v>0.002875268459320068</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.477715861459728e-05</v>
+        <v>0.0007971150917001069</v>
       </c>
       <c r="ED12" t="n">
-        <v>7.931708751129918e-06</v>
+        <v>0.004151876084506512</v>
       </c>
       <c r="EE12" t="n">
-        <v>1.145937312685419e-05</v>
+        <v>0.001778172212652862</v>
       </c>
       <c r="EF12" t="n">
-        <v>1.216958662553225e-05</v>
+        <v>0.001521806116215885</v>
       </c>
       <c r="EG12" t="n">
-        <v>6.153702997835353e-05</v>
+        <v>0.0008442368125542998</v>
       </c>
       <c r="EH12" t="n">
-        <v>3.604670200729743e-05</v>
+        <v>0.001957802567631006</v>
       </c>
       <c r="EI12" t="n">
-        <v>6.688517169095576e-05</v>
+        <v>0.00496651092544198</v>
       </c>
       <c r="EJ12" t="n">
-        <v>4.127605279791169e-05</v>
+        <v>0.0005920479889027774</v>
       </c>
       <c r="EK12" t="n">
-        <v>2.36013420362724e-05</v>
+        <v>0.001724993693642318</v>
       </c>
       <c r="EL12" t="n">
-        <v>2.540509558457416e-05</v>
+        <v>0.000475333770737052</v>
       </c>
       <c r="EM12" t="n">
-        <v>5.662238436343614e-06</v>
+        <v>0.0008346433169208467</v>
       </c>
       <c r="EN12" t="n">
-        <v>9.763225534697995e-06</v>
+        <v>0.0006824221927672625</v>
       </c>
       <c r="EO12" t="n">
-        <v>3.263403414166532e-05</v>
+        <v>0.001261040335521102</v>
       </c>
       <c r="EP12" t="n">
-        <v>9.07648864085786e-05</v>
+        <v>0.002516648964956403</v>
       </c>
       <c r="EQ12" t="n">
-        <v>3.967151496908627e-05</v>
+        <v>0.0002112264337483793</v>
       </c>
       <c r="ER12" t="n">
-        <v>7.217001257231459e-05</v>
+        <v>0.005259463097900152</v>
       </c>
       <c r="ES12" t="n">
-        <v>3.84370687243063e-05</v>
+        <v>0.0008432486793026328</v>
       </c>
       <c r="ET12" t="n">
-        <v>5.99610066274181e-05</v>
+        <v>0.0007717684493400156</v>
       </c>
       <c r="EU12" t="n">
-        <v>6.962133193155751e-05</v>
+        <v>0.001144592650234699</v>
       </c>
       <c r="EV12" t="n">
-        <v>3.957704029744491e-05</v>
+        <v>0.001915983157232404</v>
       </c>
       <c r="EW12" t="n">
-        <v>4.970577720087022e-06</v>
+        <v>0.003466552356258035</v>
       </c>
       <c r="EX12" t="n">
-        <v>1.051904837368056e-05</v>
+        <v>9.518166189081967e-05</v>
       </c>
       <c r="EY12" t="n">
-        <v>0.0001067225457518362</v>
+        <v>0.002282305154949427</v>
       </c>
       <c r="EZ12" t="n">
-        <v>3.521196413203143e-05</v>
+        <v>0.0002336083562113345</v>
       </c>
       <c r="FA12" t="n">
-        <v>6.210704304976389e-05</v>
+        <v>0.004457793198525906</v>
       </c>
       <c r="FB12" t="n">
-        <v>2.893480632337742e-05</v>
+        <v>0.001074672793038189</v>
       </c>
       <c r="FC12" t="n">
-        <v>2.705023507587612e-05</v>
+        <v>0.002009008079767227</v>
       </c>
       <c r="FD12" t="n">
-        <v>3.501485480228439e-05</v>
+        <v>0.0001389882090734318</v>
       </c>
       <c r="FE12" t="n">
-        <v>1.74809611053206e-05</v>
+        <v>0.00169150996953249</v>
       </c>
       <c r="FF12" t="n">
-        <v>2.272024539706763e-05</v>
+        <v>0.0005131788202561438</v>
       </c>
       <c r="FG12" t="n">
-        <v>8.219893970817793e-06</v>
+        <v>0.002086687600240111</v>
       </c>
       <c r="FH12" t="n">
-        <v>2.262034831801429e-05</v>
+        <v>0.000185612152563408</v>
       </c>
       <c r="FI12" t="n">
-        <v>4.6534463763237e-05</v>
+        <v>0.001551169669255614</v>
       </c>
       <c r="FJ12" t="n">
-        <v>6.484537880169228e-05</v>
+        <v>0.0005821349332109094</v>
       </c>
       <c r="FK12" t="n">
-        <v>4.4791118853027e-05</v>
+        <v>0.0001465509849367663</v>
       </c>
       <c r="FL12" t="n">
-        <v>4.067455847689416e-06</v>
+        <v>0.0008406633278355002</v>
       </c>
       <c r="FM12" t="n">
-        <v>1.085735311789904e-05</v>
+        <v>0.002651270478963852</v>
       </c>
       <c r="FN12" t="n">
-        <v>7.471420303772902e-06</v>
+        <v>0.002972427988424897</v>
       </c>
       <c r="FO12" t="n">
-        <v>1.531231464468874e-05</v>
+        <v>0.000644576852209866</v>
       </c>
       <c r="FP12" t="n">
-        <v>3.460812877165154e-05</v>
+        <v>0.002136174589395523</v>
       </c>
       <c r="FQ12" t="n">
-        <v>1.187929592560977e-05</v>
+        <v>0.001870701438747346</v>
       </c>
       <c r="FR12" t="n">
-        <v>5.148971104063094e-05</v>
+        <v>0.005110885482281446</v>
       </c>
       <c r="FS12" t="n">
-        <v>3.546383231878281e-05</v>
+        <v>0.0009559561731293797</v>
       </c>
       <c r="FT12" t="n">
-        <v>3.313831621198915e-05</v>
+        <v>0.006395850796252489</v>
       </c>
       <c r="FU12" t="n">
-        <v>1.205833632411668e-05</v>
+        <v>2.436533395666629e-05</v>
       </c>
       <c r="FV12" t="n">
-        <v>3.241961530875415e-05</v>
+        <v>0.004418979398906231</v>
       </c>
       <c r="FW12" t="n">
-        <v>1.033296939567663e-05</v>
+        <v>0.007494022604078054</v>
       </c>
       <c r="FX12" t="n">
-        <v>1.847130624810234e-05</v>
+        <v>0.002129675121977925</v>
       </c>
       <c r="FY12" t="n">
-        <v>9.728159784572199e-05</v>
+        <v>0.0009049235377460718</v>
       </c>
       <c r="FZ12" t="n">
-        <v>3.148427276755683e-05</v>
+        <v>0.0008329377742484212</v>
       </c>
       <c r="GA12" t="n">
-        <v>5.185292593523627e-06</v>
+        <v>0.003433859441429377</v>
       </c>
       <c r="GB12" t="n">
-        <v>1.556001370772719e-05</v>
+        <v>0.003507749643176794</v>
       </c>
       <c r="GC12" t="n">
-        <v>1.88202247954905e-05</v>
+        <v>0.001604542718268931</v>
       </c>
       <c r="GD12" t="n">
-        <v>9.558454621583223e-05</v>
+        <v>0.00531482370570302</v>
       </c>
       <c r="GE12" t="n">
-        <v>0.0001638650282984599</v>
+        <v>0.001801879378035665</v>
       </c>
       <c r="GF12" t="n">
-        <v>2.532869984861463e-05</v>
+        <v>0.001206045038998127</v>
       </c>
       <c r="GG12" t="n">
-        <v>1.670361780270468e-05</v>
+        <v>0.001743706758134067</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.003304256591945887</v>
+        <v>0.003731715492904186</v>
       </c>
       <c r="B13" t="n">
-        <v>0.008225835859775543</v>
+        <v>0.07609032094478607</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0004422013298608363</v>
+        <v>0.01084287837147713</v>
       </c>
       <c r="D13" t="n">
-        <v>0.007477168459445238</v>
+        <v>0.01903029903769493</v>
       </c>
       <c r="E13" t="n">
-        <v>0.009568837471306324</v>
+        <v>0.03760984539985657</v>
       </c>
       <c r="F13" t="n">
-        <v>0.01864826306700706</v>
+        <v>0.07371418178081512</v>
       </c>
       <c r="G13" t="n">
-        <v>0.002930265385657549</v>
+        <v>0.01511706784367561</v>
       </c>
       <c r="H13" t="n">
-        <v>0.01112681068480015</v>
+        <v>0.05158870294690132</v>
       </c>
       <c r="I13" t="n">
-        <v>0.002195741981267929</v>
+        <v>0.0191295500844717</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0001651276834309101</v>
+        <v>0.01777480356395245</v>
       </c>
       <c r="K13" t="n">
-        <v>0.008862252347171307</v>
+        <v>0.1079176142811775</v>
       </c>
       <c r="L13" t="n">
-        <v>0.001996238483116031</v>
+        <v>0.003832846414297819</v>
       </c>
       <c r="M13" t="n">
-        <v>0.003694410668686032</v>
+        <v>0.04452557116746902</v>
       </c>
       <c r="N13" t="n">
-        <v>0.004110649693757296</v>
+        <v>0.0259533915668726</v>
       </c>
       <c r="O13" t="n">
-        <v>0.01560508087277412</v>
+        <v>0.08220361173152924</v>
       </c>
       <c r="P13" t="n">
-        <v>0.0002667047083377838</v>
+        <v>0.03968891501426697</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.009035287424921989</v>
+        <v>0.007345064077526331</v>
       </c>
       <c r="R13" t="n">
-        <v>0.0002038899692706764</v>
+        <v>0.01438948884606361</v>
       </c>
       <c r="S13" t="n">
-        <v>0.001171492505818605</v>
+        <v>0.01351570524275303</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0004947331035509706</v>
+        <v>0.0201578214764595</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0002330886200070381</v>
+        <v>0.01279421336948872</v>
       </c>
       <c r="V13" t="n">
-        <v>0.001391091616824269</v>
+        <v>0.04595665261149406</v>
       </c>
       <c r="W13" t="n">
-        <v>0.007266318891197443</v>
+        <v>0.04510679468512535</v>
       </c>
       <c r="X13" t="n">
-        <v>0.001941498485393822</v>
+        <v>0.01660569198429585</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.001617263187654316</v>
+        <v>0.007884008809924126</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.001465173554606736</v>
+        <v>0.01455525681376457</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.0003855509567074478</v>
+        <v>0.007428525015711784</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.0003190990537405014</v>
+        <v>0.0007427557138726115</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.00109111936762929</v>
+        <v>0.02604319900274277</v>
       </c>
       <c r="AD13" t="n">
-        <v>4.841561894863844e-05</v>
+        <v>0.01036680862307549</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.00137886987067759</v>
+        <v>0.05714546144008636</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.001781675731763244</v>
+        <v>0.07042084634304047</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.0007609822205267847</v>
+        <v>0.04095042496919632</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.001429503434337676</v>
+        <v>0.01054560579359531</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.003024056553840637</v>
+        <v>0.02503145486116409</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.001078846747986972</v>
+        <v>0.009774479083716869</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.0001805320207495242</v>
+        <v>0.003872253000736237</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.001154858851805329</v>
+        <v>0.02806126698851585</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.0007961951196193695</v>
+        <v>0.006389816757291555</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.0009187629912048578</v>
+        <v>0.02370814979076385</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.0003284183330833912</v>
+        <v>0.01676563173532486</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.001145041547715664</v>
+        <v>0.01743541471660137</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.0003517856821417809</v>
+        <v>0.02587256021797657</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.002327430993318558</v>
+        <v>0.03990642726421356</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.0003625077952165157</v>
+        <v>0.01412266120314598</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.001701844041235745</v>
+        <v>0.01693748310208321</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.001440476393327117</v>
+        <v>0.1801928281784058</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.0009349884930998087</v>
+        <v>0.005232426337897778</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.00772668793797493</v>
+        <v>0.03129550069570541</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.009823549538850784</v>
+        <v>0.004964022431522608</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.01096460036933422</v>
+        <v>0.04870492219924927</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.003878479823470116</v>
+        <v>0.01173610705882311</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.001829717890359461</v>
+        <v>0.01562080811709166</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.0005665664211846888</v>
+        <v>0.003114305436611176</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.003084840020164847</v>
+        <v>0.03199988231062889</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.003591655753552914</v>
+        <v>0.0427144281566143</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.001781991100870073</v>
+        <v>0.004594228230416775</v>
       </c>
       <c r="BF13" t="n">
-        <v>0.003290998283773661</v>
+        <v>0.004647385329008102</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.0006095252465456724</v>
+        <v>0.01181428879499435</v>
       </c>
       <c r="BH13" t="n">
-        <v>0.003168400377035141</v>
+        <v>0.01560148503631353</v>
       </c>
       <c r="BI13" t="n">
-        <v>0.001653911545872688</v>
+        <v>0.04822384938597679</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.004253380000591278</v>
+        <v>0.01658660173416138</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.0008579370332881808</v>
+        <v>0.01232164353132248</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.0003024544566869736</v>
+        <v>0.02361304312944412</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.0003621765645220876</v>
+        <v>0.0155341662466526</v>
       </c>
       <c r="BN13" t="n">
-        <v>0.0006311036413535476</v>
+        <v>0.005815622862428427</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.005908272229135036</v>
+        <v>0.02437199465930462</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.002940671052783728</v>
+        <v>0.001470571151003242</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.0003952481492888182</v>
+        <v>0.000547120172996074</v>
       </c>
       <c r="BR13" t="n">
-        <v>0.0003086857032030821</v>
+        <v>0.04931778460741043</v>
       </c>
       <c r="BS13" t="n">
-        <v>0.0044566560536623</v>
+        <v>0.02543352916836739</v>
       </c>
       <c r="BT13" t="n">
-        <v>0.001176042482256889</v>
+        <v>0.007995722815394402</v>
       </c>
       <c r="BU13" t="n">
-        <v>4.957639612257481e-05</v>
+        <v>0.02510695531964302</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.002456480637192726</v>
+        <v>0.08440049737691879</v>
       </c>
       <c r="BW13" t="n">
-        <v>0.0003609325503930449</v>
+        <v>0.01689723134040833</v>
       </c>
       <c r="BX13" t="n">
-        <v>0.005225180648267269</v>
+        <v>0.03918459638953209</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.004879103507846594</v>
+        <v>0.0173029787838459</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.008899452164769173</v>
+        <v>0.05851058661937714</v>
       </c>
       <c r="CA13" t="n">
-        <v>0.002995043061673641</v>
+        <v>0.008985958993434906</v>
       </c>
       <c r="CB13" t="n">
-        <v>0.0003092483384534717</v>
+        <v>0.004375032614916563</v>
       </c>
       <c r="CC13" t="n">
-        <v>0.0009355922811664641</v>
+        <v>0.01422069407999516</v>
       </c>
       <c r="CD13" t="n">
-        <v>0.0003215633041691035</v>
+        <v>0.010351805947721</v>
       </c>
       <c r="CE13" t="n">
-        <v>0.0004955071490257978</v>
+        <v>0.02534971013665199</v>
       </c>
       <c r="CF13" t="n">
-        <v>0.0004875649465247989</v>
+        <v>0.006577994674444199</v>
       </c>
       <c r="CG13" t="n">
-        <v>0.0004257078107912093</v>
+        <v>0.009897190146148205</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.002170945052057505</v>
+        <v>0.006256125867366791</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.00310239102691412</v>
+        <v>0.02192019112408161</v>
       </c>
       <c r="CJ13" t="n">
-        <v>0.001441081869415939</v>
+        <v>0.01220990344882011</v>
       </c>
       <c r="CK13" t="n">
-        <v>0.002206332981586456</v>
+        <v>0.0174226425588131</v>
       </c>
       <c r="CL13" t="n">
-        <v>6.508955266326666e-06</v>
+        <v>0.005950585938990116</v>
       </c>
       <c r="CM13" t="n">
-        <v>0.0005040868418291211</v>
+        <v>0.02968163229525089</v>
       </c>
       <c r="CN13" t="n">
-        <v>0.002767229685559869</v>
+        <v>0.0884053036570549</v>
       </c>
       <c r="CO13" t="n">
-        <v>0.001248763757757843</v>
+        <v>0.0007188671734184027</v>
       </c>
       <c r="CP13" t="n">
-        <v>0.003559258300811052</v>
+        <v>0.005494474899023771</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.004691385664045811</v>
+        <v>0.04654065519571304</v>
       </c>
       <c r="CR13" t="n">
-        <v>0.001801780425012112</v>
+        <v>0.03426074236631393</v>
       </c>
       <c r="CS13" t="n">
-        <v>0.00301946559920907</v>
+        <v>0.01506613194942474</v>
       </c>
       <c r="CT13" t="n">
-        <v>0.004325468093156815</v>
+        <v>0.01800801046192646</v>
       </c>
       <c r="CU13" t="n">
-        <v>0.000419583055190742</v>
+        <v>0.02150899171829224</v>
       </c>
       <c r="CV13" t="n">
-        <v>0.0003848850610665977</v>
+        <v>0.01792280748486519</v>
       </c>
       <c r="CW13" t="n">
-        <v>0.0006217061309143901</v>
+        <v>0.02349614538252354</v>
       </c>
       <c r="CX13" t="n">
-        <v>0.0004068774287588894</v>
+        <v>0.003248973283916712</v>
       </c>
       <c r="CY13" t="n">
-        <v>0.000356742471922189</v>
+        <v>0.007118906825780869</v>
       </c>
       <c r="CZ13" t="n">
-        <v>0.001797832548618317</v>
+        <v>0.01113474927842617</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.003340683877468109</v>
+        <v>0.01772501692175865</v>
       </c>
       <c r="DB13" t="n">
-        <v>0.0007309416541829705</v>
+        <v>0.006383929867297411</v>
       </c>
       <c r="DC13" t="n">
-        <v>0.001742503140121698</v>
+        <v>0.01505292486399412</v>
       </c>
       <c r="DD13" t="n">
-        <v>0.0007676837267354131</v>
+        <v>0.007425403688102961</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.004154548980295658</v>
+        <v>0.01607643999159336</v>
       </c>
       <c r="DF13" t="n">
-        <v>0.00167109677568078</v>
+        <v>0.01501887664198875</v>
       </c>
       <c r="DG13" t="n">
-        <v>0.000540147302672267</v>
+        <v>0.0173213854432106</v>
       </c>
       <c r="DH13" t="n">
-        <v>0.008776279166340828</v>
+        <v>0.02678173407912254</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.001265867496840656</v>
+        <v>0.03513201698660851</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.001378917368128896</v>
+        <v>0.009794145822525024</v>
       </c>
       <c r="DK13" t="n">
-        <v>0.003359625348821282</v>
+        <v>0.006290327291935682</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.001737899845466018</v>
+        <v>0.01882564276456833</v>
       </c>
       <c r="DM13" t="n">
-        <v>0.002919677877798676</v>
+        <v>0.01623041555285454</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.002626290777698159</v>
+        <v>0.005200423300266266</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.001894570305012167</v>
+        <v>0.01503117382526398</v>
       </c>
       <c r="DP13" t="n">
-        <v>0.0003210068389307708</v>
+        <v>0.0004096453776583076</v>
       </c>
       <c r="DQ13" t="n">
-        <v>0.000793362851254642</v>
+        <v>0.05146171152591705</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.00239104381762445</v>
+        <v>0.01753222569823265</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.003749404335394502</v>
+        <v>0.03097868338227272</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.003430884797126055</v>
+        <v>0.002704485785216093</v>
       </c>
       <c r="DU13" t="n">
-        <v>0.0007873704889789224</v>
+        <v>0.008042294532060623</v>
       </c>
       <c r="DV13" t="n">
-        <v>0.001016385154798627</v>
+        <v>0.01814631000161171</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.0003283055848442018</v>
+        <v>0.0006465800106525421</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.002498681424185634</v>
+        <v>0.009057081304490566</v>
       </c>
       <c r="DY13" t="n">
-        <v>0.001320286770351231</v>
+        <v>0.004914452321827412</v>
       </c>
       <c r="DZ13" t="n">
-        <v>0.002722640056163073</v>
+        <v>0.01532015018165112</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.003318168688565493</v>
+        <v>0.003743339329957962</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.002035726793110371</v>
+        <v>0.02099683694541454</v>
       </c>
       <c r="EC13" t="n">
-        <v>0.001140853855758905</v>
+        <v>0.01276576239615679</v>
       </c>
       <c r="ED13" t="n">
-        <v>0.001078030560165644</v>
+        <v>0.00988303404301405</v>
       </c>
       <c r="EE13" t="n">
-        <v>0.001616742694750428</v>
+        <v>0.02514082938432693</v>
       </c>
       <c r="EF13" t="n">
-        <v>0.0002798485802486539</v>
+        <v>0.008061372675001621</v>
       </c>
       <c r="EG13" t="n">
-        <v>0.002145606558769941</v>
+        <v>0.004451807588338852</v>
       </c>
       <c r="EH13" t="n">
-        <v>0.001217359094880521</v>
+        <v>0.006697779055684805</v>
       </c>
       <c r="EI13" t="n">
-        <v>0.002481857547536492</v>
+        <v>0.02893118001520634</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.002132435794919729</v>
+        <v>0.01892033964395523</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.002741968492045999</v>
+        <v>0.002203879179432988</v>
       </c>
       <c r="EL13" t="n">
-        <v>0.0004605466965585947</v>
+        <v>0.00681514386087656</v>
       </c>
       <c r="EM13" t="n">
-        <v>0.00141018268186599</v>
+        <v>0.00911280233412981</v>
       </c>
       <c r="EN13" t="n">
-        <v>0.0006559816538356245</v>
+        <v>0.006848103366792202</v>
       </c>
       <c r="EO13" t="n">
-        <v>0.001692342455498874</v>
+        <v>0.01813823357224464</v>
       </c>
       <c r="EP13" t="n">
-        <v>0.0002929114561993629</v>
+        <v>0.00567399337887764</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0.0004470011917874217</v>
+        <v>0.02517747320234776</v>
       </c>
       <c r="ER13" t="n">
-        <v>0.001147666713222861</v>
+        <v>0.003222827101126313</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.00278529804199934</v>
+        <v>0.006863124668598175</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.0003808563342317939</v>
+        <v>0.01325027644634247</v>
       </c>
       <c r="EU13" t="n">
-        <v>0.0003848494088742882</v>
+        <v>0.01847624406218529</v>
       </c>
       <c r="EV13" t="n">
-        <v>0.007628145627677441</v>
+        <v>0.01805463619530201</v>
       </c>
       <c r="EW13" t="n">
-        <v>0.001231290865689516</v>
+        <v>0.0119083859026432</v>
       </c>
       <c r="EX13" t="n">
-        <v>0.0007784813642501831</v>
+        <v>0.01566217094659805</v>
       </c>
       <c r="EY13" t="n">
-        <v>0.0007507812697440386</v>
+        <v>0.0301582608371973</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0.0001284368336200714</v>
+        <v>0.01057651452720165</v>
       </c>
       <c r="FA13" t="n">
-        <v>0.0006287219002842903</v>
+        <v>0.009385333396494389</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.002472428372129798</v>
+        <v>0.01052908413112164</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.002952511422336102</v>
+        <v>0.02062245830893517</v>
       </c>
       <c r="FD13" t="n">
-        <v>0.001591120613738894</v>
+        <v>0.01341067813336849</v>
       </c>
       <c r="FE13" t="n">
-        <v>0.00243644998408854</v>
+        <v>0.01710973493754864</v>
       </c>
       <c r="FF13" t="n">
-        <v>0.0004456232709344476</v>
+        <v>0.009589288383722305</v>
       </c>
       <c r="FG13" t="n">
-        <v>0.001917911460623145</v>
+        <v>0.02292876690626144</v>
       </c>
       <c r="FH13" t="n">
-        <v>0.0002320393396075815</v>
+        <v>0.04522819072008133</v>
       </c>
       <c r="FI13" t="n">
-        <v>0.0003803706495091319</v>
+        <v>0.007059061899781227</v>
       </c>
       <c r="FJ13" t="n">
-        <v>0.005398181732743979</v>
+        <v>0.02361872047185898</v>
       </c>
       <c r="FK13" t="n">
-        <v>0.002452782588079572</v>
+        <v>0.01941931620240211</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.0001044059754349291</v>
+        <v>0.02464061789214611</v>
       </c>
       <c r="FM13" t="n">
-        <v>0.0006523575866594911</v>
+        <v>0.0246433075517416</v>
       </c>
       <c r="FN13" t="n">
-        <v>0.0008330760174430907</v>
+        <v>0.02487070485949516</v>
       </c>
       <c r="FO13" t="n">
-        <v>0.0008909823372960091</v>
+        <v>0.0009812242351472378</v>
       </c>
       <c r="FP13" t="n">
-        <v>0.001558482879772782</v>
+        <v>0.01860920712351799</v>
       </c>
       <c r="FQ13" t="n">
-        <v>0.005943167489022017</v>
+        <v>0.07548698782920837</v>
       </c>
       <c r="FR13" t="n">
-        <v>0.001062605297192931</v>
+        <v>0.01832264102995396</v>
       </c>
       <c r="FS13" t="n">
-        <v>0.001536511583253741</v>
+        <v>0.009034335613250732</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.01066538318991661</v>
+        <v>0.008865063078701496</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.00264659128151834</v>
+        <v>0.01216129772365093</v>
       </c>
       <c r="FV13" t="n">
-        <v>0.003002924844622612</v>
+        <v>0.02041611634194851</v>
       </c>
       <c r="FW13" t="n">
-        <v>0.00719540286809206</v>
+        <v>0.01022617798298597</v>
       </c>
       <c r="FX13" t="n">
-        <v>0.002449315972626209</v>
+        <v>0.01129463873803616</v>
       </c>
       <c r="FY13" t="n">
-        <v>0.001828416949138045</v>
+        <v>0.004837851040065289</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0.002778585534542799</v>
+        <v>0.006591103971004486</v>
       </c>
       <c r="GA13" t="n">
-        <v>0.000491214741487056</v>
+        <v>0.01462111994624138</v>
       </c>
       <c r="GB13" t="n">
-        <v>0.001814607880078256</v>
+        <v>0.02304783090949059</v>
       </c>
       <c r="GC13" t="n">
-        <v>0.003830120898783207</v>
+        <v>0.003599273506551981</v>
       </c>
       <c r="GD13" t="n">
-        <v>0.0001583174453116953</v>
+        <v>0.003806234803050756</v>
       </c>
       <c r="GE13" t="n">
-        <v>0.002892931457608938</v>
+        <v>0.01076122373342514</v>
       </c>
       <c r="GF13" t="n">
-        <v>0.002199415117502213</v>
+        <v>0.01257359981536865</v>
       </c>
       <c r="GG13" t="n">
-        <v>0.0009605659288354218</v>
+        <v>0.0149196945130825</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.008726856671273708</v>
+        <v>0.02608283795416355</v>
       </c>
       <c r="B14" t="n">
-        <v>0.0007500459905713797</v>
+        <v>0.0004859310574829578</v>
       </c>
       <c r="C14" t="n">
-        <v>0.001812145696021616</v>
+        <v>0.002927261404693127</v>
       </c>
       <c r="D14" t="n">
-        <v>0.004704102408140898</v>
+        <v>0.08622892200946808</v>
       </c>
       <c r="E14" t="n">
-        <v>0.001440699561499059</v>
+        <v>0.04119898751378059</v>
       </c>
       <c r="F14" t="n">
-        <v>0.001835231902077794</v>
+        <v>0.01006969157606363</v>
       </c>
       <c r="G14" t="n">
-        <v>0.001328688696958125</v>
+        <v>0.03697944432497025</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0005293807480484247</v>
+        <v>0.01873747073113918</v>
       </c>
       <c r="I14" t="n">
-        <v>7.642584387212992e-05</v>
+        <v>0.009527783840894699</v>
       </c>
       <c r="J14" t="n">
-        <v>0.007619220763444901</v>
+        <v>0.009910533204674721</v>
       </c>
       <c r="K14" t="n">
-        <v>4.432047717273235e-06</v>
+        <v>0.0201445147395134</v>
       </c>
       <c r="L14" t="n">
-        <v>0.002400007331743836</v>
+        <v>0.0150747150182724</v>
       </c>
       <c r="M14" t="n">
-        <v>0.001263385638594627</v>
+        <v>0.1173533126711845</v>
       </c>
       <c r="N14" t="n">
-        <v>0.001834360882639885</v>
+        <v>0.01755219697952271</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0006364407599903643</v>
+        <v>0.008739707991480827</v>
       </c>
       <c r="P14" t="n">
-        <v>0.0007380162714980543</v>
+        <v>0.0228772796690464</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.001241132500581443</v>
+        <v>0.04627420753240585</v>
       </c>
       <c r="R14" t="n">
-        <v>0.0005122117581777275</v>
+        <v>0.006631973665207624</v>
       </c>
       <c r="S14" t="n">
-        <v>0.001160299172624946</v>
+        <v>0.001000334974378347</v>
       </c>
       <c r="T14" t="n">
-        <v>0.001797402743250132</v>
+        <v>0.01140394899994135</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0005871693138033152</v>
+        <v>0.005982669536024332</v>
       </c>
       <c r="V14" t="n">
-        <v>1.857396273408085e-05</v>
+        <v>0.01303523685783148</v>
       </c>
       <c r="W14" t="n">
-        <v>0.0008790027350187302</v>
+        <v>0.002710101194679737</v>
       </c>
       <c r="X14" t="n">
-        <v>0.0002585913171060383</v>
+        <v>0.02738828025758266</v>
       </c>
       <c r="Y14" t="n">
-        <v>3.825494786724448e-05</v>
+        <v>0.002551327226683497</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.001637427601963282</v>
+        <v>0.005064106546342373</v>
       </c>
       <c r="AA14" t="n">
-        <v>5.103412695461884e-05</v>
+        <v>0.0008543664589524269</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.0007116590859368443</v>
+        <v>0.00463828444480896</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.001770806033164263</v>
+        <v>0.003428466618061066</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.000380910380044952</v>
+        <v>0.001706567592918873</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.0006065571797080338</v>
+        <v>0.01041563227772713</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.0005110189085826278</v>
+        <v>0.03773555904626846</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.0001325238845311105</v>
+        <v>0.02099801599979401</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.0003288221196271479</v>
+        <v>0.0136471213772893</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.001072112005203962</v>
+        <v>0.02673163823783398</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.0006703610997647047</v>
+        <v>0.02498762123286724</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.0009924373589456081</v>
+        <v>0.007462161593139172</v>
       </c>
       <c r="AL14" t="n">
-        <v>5.006638821214437e-05</v>
+        <v>0.02459579519927502</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.0003156501334160566</v>
+        <v>0.01670796051621437</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.0009740975801832974</v>
+        <v>0.02110623195767403</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.001122292480431497</v>
+        <v>0.02581717073917389</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.0002637735742609948</v>
+        <v>0.01276499032974243</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.0009190941927954555</v>
+        <v>0.02141348458826542</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.001269996631890535</v>
+        <v>0.00352849205955863</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.0003681523085106164</v>
+        <v>0.007265193853527308</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.005151258315891027</v>
+        <v>0.01428412646055222</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.00190118548925966</v>
+        <v>0.00827447883784771</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.001959798391908407</v>
+        <v>0.006137856747955084</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.003128346987068653</v>
+        <v>0.05525501817464828</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.002139674965292215</v>
+        <v>0.01719208806753159</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.0003031369997188449</v>
+        <v>0.01806704886257648</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.0007349535007961094</v>
+        <v>0.01193704456090927</v>
       </c>
       <c r="BA14" t="n">
-        <v>0.002538570901378989</v>
+        <v>0.01189206074923277</v>
       </c>
       <c r="BB14" t="n">
-        <v>0.0005447471630759537</v>
+        <v>0.0113714188337326</v>
       </c>
       <c r="BC14" t="n">
-        <v>0.003492813091725111</v>
+        <v>0.03172097355127335</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.003955780528485775</v>
+        <v>0.02231689915060997</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.0003138154279440641</v>
+        <v>0.001334665808826685</v>
       </c>
       <c r="BF14" t="n">
-        <v>0.0004518122877925634</v>
+        <v>0.02835692465305328</v>
       </c>
       <c r="BG14" t="n">
-        <v>0.00160653458442539</v>
+        <v>0.02588178217411041</v>
       </c>
       <c r="BH14" t="n">
-        <v>0.0002209188824053854</v>
+        <v>0.01744368672370911</v>
       </c>
       <c r="BI14" t="n">
-        <v>0.0003270573215559125</v>
+        <v>0.02682063542306423</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.002045932458713651</v>
+        <v>0.01861710660159588</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.001378066837787628</v>
+        <v>0.04648781940340996</v>
       </c>
       <c r="BL14" t="n">
-        <v>3.955031934310682e-05</v>
+        <v>0.002926846733316779</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.001748946728184819</v>
+        <v>0.02650260366499424</v>
       </c>
       <c r="BN14" t="n">
-        <v>0.0004503377713263035</v>
+        <v>0.01639846153557301</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.0002562919107731432</v>
+        <v>0.01216851733624935</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.0001264166203327477</v>
+        <v>0.01906261034309864</v>
       </c>
       <c r="BQ14" t="n">
-        <v>0.000683635997120291</v>
+        <v>0.002315925434231758</v>
       </c>
       <c r="BR14" t="n">
-        <v>0.0008189999498426914</v>
+        <v>0.002053327392786741</v>
       </c>
       <c r="BS14" t="n">
-        <v>0.0004972250899299979</v>
+        <v>0.01179521344602108</v>
       </c>
       <c r="BT14" t="n">
-        <v>0.0006685149855911732</v>
+        <v>0.01277282647788525</v>
       </c>
       <c r="BU14" t="n">
-        <v>0.002496735192835331</v>
+        <v>0.004620431922376156</v>
       </c>
       <c r="BV14" t="n">
-        <v>5.386452539823949e-05</v>
+        <v>0.008669537492096424</v>
       </c>
       <c r="BW14" t="n">
-        <v>0.0005572762456722558</v>
+        <v>0.008216500282287598</v>
       </c>
       <c r="BX14" t="n">
-        <v>0.0009582052007317543</v>
+        <v>0.05481363087892532</v>
       </c>
       <c r="BY14" t="n">
-        <v>7.913532317616045e-05</v>
+        <v>0.00189998943824321</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0.0003198863996658474</v>
+        <v>0.009578497149050236</v>
       </c>
       <c r="CA14" t="n">
-        <v>0.0002617320569697767</v>
+        <v>0.005073871463537216</v>
       </c>
       <c r="CB14" t="n">
-        <v>0.001697497675195336</v>
+        <v>0.001892053987830877</v>
       </c>
       <c r="CC14" t="n">
-        <v>0.0005423069233074784</v>
+        <v>0.009750085882842541</v>
       </c>
       <c r="CD14" t="n">
-        <v>0.001628236495889723</v>
+        <v>0.006112352944910526</v>
       </c>
       <c r="CE14" t="n">
-        <v>0.001196420518681407</v>
+        <v>0.00650513032451272</v>
       </c>
       <c r="CF14" t="n">
-        <v>0.0001269789063371718</v>
+        <v>0.001916148466989398</v>
       </c>
       <c r="CG14" t="n">
-        <v>0.0002652278344612569</v>
+        <v>0.02939322963356972</v>
       </c>
       <c r="CH14" t="n">
-        <v>4.805551725439727e-07</v>
+        <v>0.008777240291237831</v>
       </c>
       <c r="CI14" t="n">
-        <v>0.0009884724859148264</v>
+        <v>0.01369531452655792</v>
       </c>
       <c r="CJ14" t="n">
-        <v>8.577987318858504e-05</v>
+        <v>0.002067976631224155</v>
       </c>
       <c r="CK14" t="n">
-        <v>0.001084575313143432</v>
+        <v>0.008879994042217731</v>
       </c>
       <c r="CL14" t="n">
-        <v>0.0001397948217345402</v>
+        <v>0.006638386286795139</v>
       </c>
       <c r="CM14" t="n">
-        <v>0.00220827478915453</v>
+        <v>0.005268779583275318</v>
       </c>
       <c r="CN14" t="n">
-        <v>0.001115894177928567</v>
+        <v>0.03142803162336349</v>
       </c>
       <c r="CO14" t="n">
-        <v>0.0002949742774944752</v>
+        <v>0.009539227932691574</v>
       </c>
       <c r="CP14" t="n">
-        <v>0.001450961921364069</v>
+        <v>0.03414325416088104</v>
       </c>
       <c r="CQ14" t="n">
-        <v>0.002415457041934133</v>
+        <v>0.02069349959492683</v>
       </c>
       <c r="CR14" t="n">
-        <v>0.0008666393696330488</v>
+        <v>0.003277778392657638</v>
       </c>
       <c r="CS14" t="n">
-        <v>0.001456712139770389</v>
+        <v>0.01376781426370144</v>
       </c>
       <c r="CT14" t="n">
-        <v>0.002994580892845988</v>
+        <v>0.00715307891368866</v>
       </c>
       <c r="CU14" t="n">
-        <v>0.0002926065644714981</v>
+        <v>0.03716147318482399</v>
       </c>
       <c r="CV14" t="n">
-        <v>0.00139485823456198</v>
+        <v>0.00576223898679018</v>
       </c>
       <c r="CW14" t="n">
-        <v>0.001343815238215029</v>
+        <v>0.006516627967357635</v>
       </c>
       <c r="CX14" t="n">
-        <v>0.0003262392419856042</v>
+        <v>0.0003824041050393134</v>
       </c>
       <c r="CY14" t="n">
-        <v>0.0004822007613256574</v>
+        <v>0.02955700643360615</v>
       </c>
       <c r="CZ14" t="n">
-        <v>0.0001956386840902269</v>
+        <v>0.004985494539141655</v>
       </c>
       <c r="DA14" t="n">
-        <v>0.0007599495584145188</v>
+        <v>0.01000936608761549</v>
       </c>
       <c r="DB14" t="n">
-        <v>0.0002268810203531757</v>
+        <v>0.0004646212328225374</v>
       </c>
       <c r="DC14" t="n">
-        <v>0.000814201426692307</v>
+        <v>0.009841190651059151</v>
       </c>
       <c r="DD14" t="n">
-        <v>0.000135658192448318</v>
+        <v>0.002697381190955639</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.000667214160785079</v>
+        <v>0.003420452587306499</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.001375581137835979</v>
+        <v>0.001409582328051329</v>
       </c>
       <c r="DG14" t="n">
-        <v>0.00128968118224293</v>
+        <v>0.02474677003920078</v>
       </c>
       <c r="DH14" t="n">
-        <v>0.003180108498781919</v>
+        <v>0.02367779985070229</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.001634118147194386</v>
+        <v>0.002271431032568216</v>
       </c>
       <c r="DJ14" t="n">
-        <v>0.0008170779328793287</v>
+        <v>0.008865751326084137</v>
       </c>
       <c r="DK14" t="n">
-        <v>0.001216930104419589</v>
+        <v>0.008695190772414207</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.003259417833760381</v>
+        <v>0.06405239552259445</v>
       </c>
       <c r="DM14" t="n">
-        <v>0.0003812187351286411</v>
+        <v>0.004153469577431679</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.0008750594570301473</v>
+        <v>0.01549771521240473</v>
       </c>
       <c r="DO14" t="n">
-        <v>0.0002882290282286704</v>
+        <v>0.01122725382447243</v>
       </c>
       <c r="DP14" t="n">
-        <v>0.0003560747718438506</v>
+        <v>0.02098549902439117</v>
       </c>
       <c r="DQ14" t="n">
-        <v>0.001532663009129465</v>
+        <v>0.003637801855802536</v>
       </c>
       <c r="DR14" t="n">
-        <v>0.001753511256538332</v>
+        <v>0.001904991921037436</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.0008192601962946355</v>
+        <v>0.005605170968919992</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.000668939552269876</v>
+        <v>0.0002391992602497339</v>
       </c>
       <c r="DU14" t="n">
-        <v>0.0003564610378816724</v>
+        <v>0.003737360937520862</v>
       </c>
       <c r="DV14" t="n">
-        <v>0.0007668957696296275</v>
+        <v>0.03356481716036797</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.001341854920610785</v>
+        <v>0.003034832887351513</v>
       </c>
       <c r="DX14" t="n">
-        <v>0.00075909512815997</v>
+        <v>0.01150675397366285</v>
       </c>
       <c r="DY14" t="n">
-        <v>0.0003273108741268516</v>
+        <v>0.04247286170721054</v>
       </c>
       <c r="DZ14" t="n">
-        <v>0.0005229930975474417</v>
+        <v>0.0003064991906285286</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.001154043362475932</v>
+        <v>0.01056264061480761</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.46292459248798e-05</v>
+        <v>0.01493279170244932</v>
       </c>
       <c r="EC14" t="n">
-        <v>0.0006394729716703296</v>
+        <v>0.008086128160357475</v>
       </c>
       <c r="ED14" t="n">
-        <v>0.0002274363359902054</v>
+        <v>0.03124650754034519</v>
       </c>
       <c r="EE14" t="n">
-        <v>0.0003085503994952887</v>
+        <v>0.01908943057060242</v>
       </c>
       <c r="EF14" t="n">
-        <v>0.00188871962018311</v>
+        <v>0.01305955555289984</v>
       </c>
       <c r="EG14" t="n">
-        <v>0.002045644912868738</v>
+        <v>0.006325798109173775</v>
       </c>
       <c r="EH14" t="n">
-        <v>0.001499520149081945</v>
+        <v>0.002473726402968168</v>
       </c>
       <c r="EI14" t="n">
-        <v>0.001923573785461485</v>
+        <v>0.03206436336040497</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.001894310698844492</v>
+        <v>0.00823478028178215</v>
       </c>
       <c r="EK14" t="n">
-        <v>0.0002465613069944084</v>
+        <v>0.01390303112566471</v>
       </c>
       <c r="EL14" t="n">
-        <v>0.000244155089603737</v>
+        <v>0.003530497197061777</v>
       </c>
       <c r="EM14" t="n">
-        <v>0.0002953885996248573</v>
+        <v>0.007856898009777069</v>
       </c>
       <c r="EN14" t="n">
-        <v>0.0001652294595260173</v>
+        <v>0.005868527106940746</v>
       </c>
       <c r="EO14" t="n">
-        <v>0.0002150131622329354</v>
+        <v>0.007475239224731922</v>
       </c>
       <c r="EP14" t="n">
-        <v>0.002595276804640889</v>
+        <v>0.00216606492176652</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0.0004162008117418736</v>
+        <v>0.01454220712184906</v>
       </c>
       <c r="ER14" t="n">
-        <v>8.298899047076702e-06</v>
+        <v>0.04076985269784927</v>
       </c>
       <c r="ES14" t="n">
-        <v>6.135129660833627e-05</v>
+        <v>0.0003907494246959686</v>
       </c>
       <c r="ET14" t="n">
-        <v>0.001086076721549034</v>
+        <v>0.03584231808781624</v>
       </c>
       <c r="EU14" t="n">
-        <v>0.0008002237300388515</v>
+        <v>0.008513491600751877</v>
       </c>
       <c r="EV14" t="n">
-        <v>0.0005495070945471525</v>
+        <v>0.008719218894839287</v>
       </c>
       <c r="EW14" t="n">
-        <v>0.001357631175778806</v>
+        <v>0.01585543900728226</v>
       </c>
       <c r="EX14" t="n">
-        <v>0.001452393364161253</v>
+        <v>0.004725066479295492</v>
       </c>
       <c r="EY14" t="n">
-        <v>0.001377551001496613</v>
+        <v>0.001611331710591912</v>
       </c>
       <c r="EZ14" t="n">
-        <v>0.0004224850563332438</v>
+        <v>0.002478738548234105</v>
       </c>
       <c r="FA14" t="n">
-        <v>0.0005031533655710518</v>
+        <v>0.03633590042591095</v>
       </c>
       <c r="FB14" t="n">
-        <v>8.104872540570796e-05</v>
+        <v>0.008514191024005413</v>
       </c>
       <c r="FC14" t="n">
-        <v>0.0008256002911366522</v>
+        <v>0.004224380943924189</v>
       </c>
       <c r="FD14" t="n">
-        <v>0.0001314667024416849</v>
+        <v>0.001112159341573715</v>
       </c>
       <c r="FE14" t="n">
-        <v>0.0009320844546891749</v>
+        <v>0.01089676283299923</v>
       </c>
       <c r="FF14" t="n">
-        <v>0.0001966326963156462</v>
+        <v>0.001355553744360805</v>
       </c>
       <c r="FG14" t="n">
-        <v>0.0001626443699933589</v>
+        <v>0.00507371686398983</v>
       </c>
       <c r="FH14" t="n">
-        <v>0.00165009475313127</v>
+        <v>0.001994245452806354</v>
       </c>
       <c r="FI14" t="n">
-        <v>0.001653300365433097</v>
+        <v>0.00477859890088439</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.0009920739103108644</v>
+        <v>0.01291329227387905</v>
       </c>
       <c r="FK14" t="n">
-        <v>0.0008573575178161263</v>
+        <v>0.0235875565558672</v>
       </c>
       <c r="FL14" t="n">
-        <v>0.00182410329580307</v>
+        <v>0.002447654958814383</v>
       </c>
       <c r="FM14" t="n">
-        <v>0.001404982293024659</v>
+        <v>0.008370492607355118</v>
       </c>
       <c r="FN14" t="n">
-        <v>0.0004490180290304124</v>
+        <v>0.007582373451441526</v>
       </c>
       <c r="FO14" t="n">
-        <v>0.0004624438006430864</v>
+        <v>0.02189726009964943</v>
       </c>
       <c r="FP14" t="n">
-        <v>0.001550506101921201</v>
+        <v>0.008150964044034481</v>
       </c>
       <c r="FQ14" t="n">
-        <v>0.000526453135535121</v>
+        <v>0.008385835215449333</v>
       </c>
       <c r="FR14" t="n">
-        <v>0.001513962866738439</v>
+        <v>0.01336162630468607</v>
       </c>
       <c r="FS14" t="n">
-        <v>0.001019084709696472</v>
+        <v>0.02987473830580711</v>
       </c>
       <c r="FT14" t="n">
-        <v>0.00222277594730258</v>
+        <v>0.029063630849123</v>
       </c>
       <c r="FU14" t="n">
-        <v>0.001911144587211311</v>
+        <v>0.01554378680884838</v>
       </c>
       <c r="FV14" t="n">
-        <v>0.001388458535075188</v>
+        <v>0.007963307201862335</v>
       </c>
       <c r="FW14" t="n">
-        <v>2.463252167217433e-05</v>
+        <v>0.01195401418954134</v>
       </c>
       <c r="FX14" t="n">
-        <v>0.0001053273881552741</v>
+        <v>0.002139607444405556</v>
       </c>
       <c r="FY14" t="n">
-        <v>0.0006813780637457967</v>
+        <v>0.0009579344186931849</v>
       </c>
       <c r="FZ14" t="n">
-        <v>5.613388202618808e-05</v>
+        <v>0.007487102877348661</v>
       </c>
       <c r="GA14" t="n">
-        <v>0.0002394372131675482</v>
+        <v>0.003199364524334669</v>
       </c>
       <c r="GB14" t="n">
-        <v>0.0001796833821572363</v>
+        <v>0.0435350090265274</v>
       </c>
       <c r="GC14" t="n">
-        <v>0.0006687330896966159</v>
+        <v>0.01198379881680012</v>
       </c>
       <c r="GD14" t="n">
-        <v>0.0003028829814866185</v>
+        <v>0.005981271155178547</v>
       </c>
       <c r="GE14" t="n">
-        <v>0.001034660963341594</v>
+        <v>0.02320970222353935</v>
       </c>
       <c r="GF14" t="n">
-        <v>0.000537474756129086</v>
+        <v>0.008495230227708817</v>
       </c>
       <c r="GG14" t="n">
-        <v>0.0004865268711000681</v>
+        <v>0.00810588151216507</v>
       </c>
     </row>
     <row r="15">
@@ -9534,1709 +9534,1709 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>3.938581721740775e-05</v>
+        <v>7.803447488186066e-07</v>
       </c>
       <c r="B17" t="n">
-        <v>0.0003021846059709787</v>
+        <v>2.57437932305038e-06</v>
       </c>
       <c r="C17" t="n">
-        <v>3.120422843494453e-05</v>
+        <v>3.03977060411853e-07</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0002281047927681357</v>
+        <v>1.716203428259178e-06</v>
       </c>
       <c r="E17" t="n">
-        <v>7.93904546299018e-05</v>
+        <v>1.86967412219019e-07</v>
       </c>
       <c r="F17" t="n">
-        <v>3.849655331578106e-05</v>
+        <v>2.086546828650171e-06</v>
       </c>
       <c r="G17" t="n">
-        <v>1.432282715541078e-05</v>
+        <v>1.905593762785429e-07</v>
       </c>
       <c r="H17" t="n">
-        <v>1.789332964108326e-05</v>
+        <v>7.185328172454319e-07</v>
       </c>
       <c r="I17" t="n">
-        <v>3.176266909576952e-05</v>
+        <v>5.713179618282993e-08</v>
       </c>
       <c r="J17" t="n">
-        <v>6.250254227779806e-05</v>
+        <v>1.17615535089044e-07</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0002373135212110355</v>
+        <v>2.965985004266258e-06</v>
       </c>
       <c r="L17" t="n">
-        <v>2.31113335757982e-05</v>
+        <v>4.809699021279812e-07</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0001756221172399819</v>
+        <v>2.111727781084483e-06</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0001168663802673109</v>
+        <v>1.283609549318498e-06</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0001281439472222701</v>
+        <v>2.012830236708396e-06</v>
       </c>
       <c r="P17" t="n">
-        <v>1.851118213380687e-05</v>
+        <v>1.354237895156984e-07</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.765826062997803e-05</v>
+        <v>3.579343399451318e-08</v>
       </c>
       <c r="R17" t="n">
-        <v>2.403919825155754e-05</v>
+        <v>8.977031029644422e-08</v>
       </c>
       <c r="S17" t="n">
-        <v>6.472946552094072e-07</v>
+        <v>2.625495767460961e-07</v>
       </c>
       <c r="T17" t="n">
-        <v>5.370980215957388e-05</v>
+        <v>4.404926983170299e-07</v>
       </c>
       <c r="U17" t="n">
-        <v>8.314951628562994e-06</v>
+        <v>2.247766985874478e-07</v>
       </c>
       <c r="V17" t="n">
-        <v>2.22700837184675e-05</v>
+        <v>3.32081867782108e-07</v>
       </c>
       <c r="W17" t="n">
-        <v>4.622135020326823e-05</v>
+        <v>6.396217600013188e-07</v>
       </c>
       <c r="X17" t="n">
-        <v>4.22601806349121e-05</v>
+        <v>6.629652489209548e-07</v>
       </c>
       <c r="Y17" t="n">
-        <v>5.220797174843028e-05</v>
+        <v>7.438006264237629e-07</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.530331948946696e-05</v>
+        <v>5.716092914553883e-07</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.903340959572233e-05</v>
+        <v>1.06413054368204e-07</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.150895332102664e-05</v>
+        <v>9.083852603453124e-08</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.939806265407242e-05</v>
+        <v>4.982214818483044e-08</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.657141910982318e-05</v>
+        <v>2.17706286775865e-07</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.342184234294109e-05</v>
+        <v>9.407455650034535e-07</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.524795127101243e-05</v>
+        <v>5.580363335866423e-07</v>
       </c>
       <c r="AG17" t="n">
-        <v>3.513919182296377e-07</v>
+        <v>5.656358439409814e-07</v>
       </c>
       <c r="AH17" t="n">
-        <v>3.216517507098615e-05</v>
+        <v>4.445485615178768e-07</v>
       </c>
       <c r="AI17" t="n">
-        <v>7.076017936924472e-06</v>
+        <v>9.632155979488743e-07</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.556539473313023e-06</v>
+        <v>1.442294035314262e-07</v>
       </c>
       <c r="AK17" t="n">
-        <v>3.750983523786999e-05</v>
+        <v>4.281066026123881e-07</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.360714279348031e-05</v>
+        <v>4.215444846522587e-07</v>
       </c>
       <c r="AM17" t="n">
-        <v>9.642541954235639e-06</v>
+        <v>3.2071500299935e-07</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.681501998973545e-05</v>
+        <v>8.903203934096382e-07</v>
       </c>
       <c r="AO17" t="n">
-        <v>2.113126174663194e-05</v>
+        <v>1.087108003616777e-07</v>
       </c>
       <c r="AP17" t="n">
-        <v>6.642022981395712e-06</v>
+        <v>3.285437060185359e-07</v>
       </c>
       <c r="AQ17" t="n">
-        <v>3.010850377904717e-05</v>
+        <v>2.218482961779955e-07</v>
       </c>
       <c r="AR17" t="n">
-        <v>8.517483365722001e-06</v>
+        <v>1.426956686145786e-07</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.767196772561874e-05</v>
+        <v>3.331282414364978e-07</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.236675234395079e-05</v>
+        <v>1.280864694308548e-07</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.0002054830110864714</v>
+        <v>2.159039922844386e-06</v>
       </c>
       <c r="AV17" t="n">
-        <v>2.48846881731879e-05</v>
+        <v>5.685774908670282e-07</v>
       </c>
       <c r="AW17" t="n">
-        <v>4.243108196533285e-05</v>
+        <v>3.182187242600776e-07</v>
       </c>
       <c r="AX17" t="n">
-        <v>6.396988283086102e-06</v>
+        <v>1.485885604779469e-06</v>
       </c>
       <c r="AY17" t="n">
-        <v>7.570442903670482e-06</v>
+        <v>1.258399720427406e-06</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.793693627405446e-06</v>
+        <v>2.835523815747365e-08</v>
       </c>
       <c r="BA17" t="n">
-        <v>6.134917202871293e-05</v>
+        <v>2.531364202695841e-07</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.422684727003798e-05</v>
+        <v>4.293592326121143e-07</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.116007479140535e-05</v>
+        <v>4.880297410636558e-08</v>
       </c>
       <c r="BD17" t="n">
-        <v>2.862866313080303e-05</v>
+        <v>7.388641733996337e-07</v>
       </c>
       <c r="BE17" t="n">
-        <v>9.234408207703382e-05</v>
+        <v>3.489933249056776e-07</v>
       </c>
       <c r="BF17" t="n">
-        <v>5.085505836177617e-05</v>
+        <v>1.838978676005354e-07</v>
       </c>
       <c r="BG17" t="n">
-        <v>0.0001068207275238819</v>
+        <v>9.609877906768816e-07</v>
       </c>
       <c r="BH17" t="n">
-        <v>4.000830085715279e-05</v>
+        <v>1.594083016698278e-07</v>
       </c>
       <c r="BI17" t="n">
-        <v>1.885968049464282e-05</v>
+        <v>4.312236967507488e-08</v>
       </c>
       <c r="BJ17" t="n">
-        <v>6.314777419902384e-05</v>
+        <v>6.724754939568811e-07</v>
       </c>
       <c r="BK17" t="n">
-        <v>2.916161975008436e-06</v>
+        <v>3.779329560416045e-08</v>
       </c>
       <c r="BL17" t="n">
-        <v>5.017024886910804e-05</v>
+        <v>1.082370246763276e-07</v>
       </c>
       <c r="BM17" t="n">
-        <v>4.805466596735641e-05</v>
+        <v>4.73389206945285e-07</v>
       </c>
       <c r="BN17" t="n">
-        <v>3.530626054271124e-05</v>
+        <v>1.411384786820236e-08</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.818376404116862e-05</v>
+        <v>3.411194029467879e-07</v>
       </c>
       <c r="BP17" t="n">
-        <v>7.208785245893523e-05</v>
+        <v>7.50417996187025e-07</v>
       </c>
       <c r="BQ17" t="n">
-        <v>2.829168806783855e-05</v>
+        <v>3.73984676116379e-07</v>
       </c>
       <c r="BR17" t="n">
-        <v>1.764354965416715e-05</v>
+        <v>2.276740929119114e-07</v>
       </c>
       <c r="BS17" t="n">
-        <v>5.628234066534787e-05</v>
+        <v>2.088755053364366e-07</v>
       </c>
       <c r="BT17" t="n">
-        <v>1.339830487268046e-05</v>
+        <v>4.662588182213767e-08</v>
       </c>
       <c r="BU17" t="n">
-        <v>4.202912350592669e-06</v>
+        <v>7.738101004406417e-08</v>
       </c>
       <c r="BV17" t="n">
-        <v>9.436059917788953e-05</v>
+        <v>1.143279632742633e-06</v>
       </c>
       <c r="BW17" t="n">
-        <v>3.5394165024627e-05</v>
+        <v>4.352964992904163e-07</v>
       </c>
       <c r="BX17" t="n">
-        <v>2.306576607224997e-05</v>
+        <v>5.680306003341684e-07</v>
       </c>
       <c r="BY17" t="n">
-        <v>9.065336598723661e-06</v>
+        <v>9.982043280842845e-08</v>
       </c>
       <c r="BZ17" t="n">
-        <v>1.065652941178996e-05</v>
+        <v>1.078528725884098e-06</v>
       </c>
       <c r="CA17" t="n">
-        <v>4.191345578874461e-05</v>
+        <v>7.125876777536178e-07</v>
       </c>
       <c r="CB17" t="n">
-        <v>1.069085647031898e-05</v>
+        <v>3.471947707112122e-08</v>
       </c>
       <c r="CC17" t="n">
-        <v>2.046001645794604e-05</v>
+        <v>1.484197476031568e-08</v>
       </c>
       <c r="CD17" t="n">
-        <v>1.094849608307413e-06</v>
+        <v>1.584506179597156e-07</v>
       </c>
       <c r="CE17" t="n">
-        <v>5.156280531082302e-05</v>
+        <v>7.80264542754594e-07</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.920091901614796e-05</v>
+        <v>6.195380564122388e-08</v>
       </c>
       <c r="CG17" t="n">
-        <v>1.766169225447811e-05</v>
+        <v>4.888134412794898e-07</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.508739296696149e-05</v>
+        <v>1.92351507166677e-07</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.799091114662588e-05</v>
+        <v>4.556466137728421e-07</v>
       </c>
       <c r="CJ17" t="n">
-        <v>8.120558049995452e-06</v>
+        <v>1.477703506225225e-07</v>
       </c>
       <c r="CK17" t="n">
-        <v>4.534784693532856e-06</v>
+        <v>8.673092111166625e-08</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.477704219927546e-05</v>
+        <v>6.183135781157034e-08</v>
       </c>
       <c r="CM17" t="n">
-        <v>5.281115954858251e-05</v>
+        <v>7.203735208349826e-07</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.812483560570399e-06</v>
+        <v>1.335558522441715e-06</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.732317105052061e-05</v>
+        <v>9.63370098361338e-07</v>
       </c>
       <c r="CP17" t="n">
-        <v>9.588697867002338e-05</v>
+        <v>2.038620152688964e-07</v>
       </c>
       <c r="CQ17" t="n">
-        <v>5.871575558558106e-05</v>
+        <v>2.04410611104322e-07</v>
       </c>
       <c r="CR17" t="n">
-        <v>3.84947270504199e-07</v>
+        <v>7.940948876239418e-08</v>
       </c>
       <c r="CS17" t="n">
-        <v>5.36040315637365e-05</v>
+        <v>1.073506439297489e-07</v>
       </c>
       <c r="CT17" t="n">
-        <v>7.296606327145128e-06</v>
+        <v>1.591814395851543e-07</v>
       </c>
       <c r="CU17" t="n">
-        <v>7.286069831025088e-06</v>
+        <v>1.157615940883261e-07</v>
       </c>
       <c r="CV17" t="n">
-        <v>4.157176590524614e-06</v>
+        <v>4.947463239091121e-08</v>
       </c>
       <c r="CW17" t="n">
-        <v>4.649682159652002e-05</v>
+        <v>7.553971954621375e-07</v>
       </c>
       <c r="CX17" t="n">
-        <v>2.754690831352491e-05</v>
+        <v>1.626780914421033e-07</v>
       </c>
       <c r="CY17" t="n">
-        <v>3.47095774486661e-05</v>
+        <v>5.065147661298397e-07</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.058893551293295e-05</v>
+        <v>2.891948440719716e-07</v>
       </c>
       <c r="DA17" t="n">
-        <v>2.224368108727504e-05</v>
+        <v>4.794100618710218e-07</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.887118378363084e-05</v>
+        <v>2.002484507102054e-07</v>
       </c>
       <c r="DC17" t="n">
-        <v>9.470424629398622e-06</v>
+        <v>9.521352239971748e-08</v>
       </c>
       <c r="DD17" t="n">
-        <v>1.835455441323575e-05</v>
+        <v>3.997658737375787e-08</v>
       </c>
       <c r="DE17" t="n">
-        <v>4.448447361937724e-05</v>
+        <v>3.68960343166691e-07</v>
       </c>
       <c r="DF17" t="n">
-        <v>6.820575890742475e-06</v>
+        <v>5.459740464175411e-07</v>
       </c>
       <c r="DG17" t="n">
-        <v>7.211080082925037e-05</v>
+        <v>2.010091293414007e-08</v>
       </c>
       <c r="DH17" t="n">
-        <v>0.0001314687251579016</v>
+        <v>4.256196461938089e-07</v>
       </c>
       <c r="DI17" t="n">
-        <v>6.850632780697197e-05</v>
+        <v>5.377481784307747e-07</v>
       </c>
       <c r="DJ17" t="n">
-        <v>1.85544940904947e-05</v>
+        <v>7.26307575860119e-07</v>
       </c>
       <c r="DK17" t="n">
-        <v>2.215092536062002e-06</v>
+        <v>8.955026942203403e-08</v>
       </c>
       <c r="DL17" t="n">
-        <v>3.739547901204787e-05</v>
+        <v>6.955569915589876e-07</v>
       </c>
       <c r="DM17" t="n">
-        <v>2.724467776715755e-05</v>
+        <v>3.401621597731719e-07</v>
       </c>
       <c r="DN17" t="n">
-        <v>4.781207280757371e-06</v>
+        <v>5.808740155544001e-08</v>
       </c>
       <c r="DO17" t="n">
-        <v>1.457151120121125e-05</v>
+        <v>6.901741471665446e-07</v>
       </c>
       <c r="DP17" t="n">
-        <v>3.035232293768786e-05</v>
+        <v>1.837046994523917e-07</v>
       </c>
       <c r="DQ17" t="n">
-        <v>5.113438419357408e-06</v>
+        <v>1.59671003530093e-07</v>
       </c>
       <c r="DR17" t="n">
-        <v>2.255491563118994e-05</v>
+        <v>4.85502596347942e-07</v>
       </c>
       <c r="DS17" t="n">
-        <v>1.929897371155676e-05</v>
+        <v>3.692731240789726e-07</v>
       </c>
       <c r="DT17" t="n">
-        <v>1.659138797549531e-05</v>
+        <v>7.145250719986507e-07</v>
       </c>
       <c r="DU17" t="n">
-        <v>8.309239092341159e-07</v>
+        <v>2.000387269163184e-07</v>
       </c>
       <c r="DV17" t="n">
-        <v>4.559327135211788e-05</v>
+        <v>7.814585956111841e-08</v>
       </c>
       <c r="DW17" t="n">
-        <v>1.115959275921341e-05</v>
+        <v>2.432184089684597e-07</v>
       </c>
       <c r="DX17" t="n">
-        <v>3.305147038190626e-05</v>
+        <v>2.996930277276988e-07</v>
       </c>
       <c r="DY17" t="n">
-        <v>5.942285497440025e-05</v>
+        <v>4.815503302779689e-07</v>
       </c>
       <c r="DZ17" t="n">
-        <v>1.759248789312551e-06</v>
+        <v>4.646774698358058e-07</v>
       </c>
       <c r="EA17" t="n">
-        <v>5.380758011597209e-06</v>
+        <v>5.700599672309181e-07</v>
       </c>
       <c r="EB17" t="n">
-        <v>4.458111288840882e-05</v>
+        <v>1.787790182561366e-07</v>
       </c>
       <c r="EC17" t="n">
-        <v>8.864086339599453e-06</v>
+        <v>1.565831553307362e-08</v>
       </c>
       <c r="ED17" t="n">
-        <v>3.635093662524014e-06</v>
+        <v>8.094515351331211e-07</v>
       </c>
       <c r="EE17" t="n">
-        <v>5.023921403335407e-06</v>
+        <v>6.514688379866129e-07</v>
       </c>
       <c r="EF17" t="n">
-        <v>1.337105277343653e-05</v>
+        <v>6.38529229490814e-08</v>
       </c>
       <c r="EG17" t="n">
-        <v>3.652596933534369e-05</v>
+        <v>3.452256009950361e-07</v>
       </c>
       <c r="EH17" t="n">
-        <v>1.510737365606474e-05</v>
+        <v>1.064706935949289e-07</v>
       </c>
       <c r="EI17" t="n">
-        <v>1.813996641431004e-05</v>
+        <v>1.670397011821478e-07</v>
       </c>
       <c r="EJ17" t="n">
-        <v>2.397409116383642e-05</v>
+        <v>3.21160939620313e-07</v>
       </c>
       <c r="EK17" t="n">
-        <v>1.783008701750077e-05</v>
+        <v>3.895491431649134e-07</v>
       </c>
       <c r="EL17" t="n">
-        <v>2.733127621468157e-05</v>
+        <v>2.368733902358144e-07</v>
       </c>
       <c r="EM17" t="n">
-        <v>7.140291927498765e-06</v>
+        <v>1.020177577970571e-07</v>
       </c>
       <c r="EN17" t="n">
-        <v>1.295896981901024e-05</v>
+        <v>5.105485101353224e-08</v>
       </c>
       <c r="EO17" t="n">
-        <v>2.202443283749744e-06</v>
+        <v>1.900752693018148e-07</v>
       </c>
       <c r="EP17" t="n">
-        <v>2.332523035875056e-05</v>
+        <v>3.087969844273175e-07</v>
       </c>
       <c r="EQ17" t="n">
-        <v>3.609917257563211e-05</v>
+        <v>2.273912116379506e-07</v>
       </c>
       <c r="ER17" t="n">
-        <v>1.378840124743874e-06</v>
+        <v>3.772454988393292e-07</v>
       </c>
       <c r="ES17" t="n">
-        <v>1.813139169826172e-05</v>
+        <v>4.585074009355594e-07</v>
       </c>
       <c r="ET17" t="n">
-        <v>2.368650257267291e-06</v>
+        <v>1.957411370767659e-07</v>
       </c>
       <c r="EU17" t="n">
-        <v>1.474063901696354e-05</v>
+        <v>2.190939341062403e-07</v>
       </c>
       <c r="EV17" t="n">
-        <v>6.598746404051781e-05</v>
+        <v>2.972777508603031e-07</v>
       </c>
       <c r="EW17" t="n">
-        <v>1.977475039893761e-05</v>
+        <v>1.956790498525152e-07</v>
       </c>
       <c r="EX17" t="n">
-        <v>4.155568603891879e-06</v>
+        <v>8.303830156819458e-08</v>
       </c>
       <c r="EY17" t="n">
-        <v>4.401256956043653e-05</v>
+        <v>8.398427553402144e-07</v>
       </c>
       <c r="EZ17" t="n">
-        <v>2.181389208999462e-05</v>
+        <v>1.100286510791193e-07</v>
       </c>
       <c r="FA17" t="n">
-        <v>2.108387889165897e-05</v>
+        <v>5.333557737685624e-07</v>
       </c>
       <c r="FB17" t="n">
-        <v>9.288055480283219e-06</v>
+        <v>1.345846101230563e-07</v>
       </c>
       <c r="FC17" t="n">
-        <v>2.208079968113452e-05</v>
+        <v>4.719613571069203e-07</v>
       </c>
       <c r="FD17" t="n">
-        <v>1.436944967281306e-05</v>
+        <v>3.442114149265763e-09</v>
       </c>
       <c r="FE17" t="n">
-        <v>3.321556960145244e-06</v>
+        <v>1.709468762101096e-07</v>
       </c>
       <c r="FF17" t="n">
-        <v>2.813496939779725e-05</v>
+        <v>7.325090223275765e-08</v>
       </c>
       <c r="FG17" t="n">
-        <v>2.358167876082007e-05</v>
+        <v>1.102895765825451e-07</v>
       </c>
       <c r="FH17" t="n">
-        <v>1.318724116572412e-06</v>
+        <v>2.962641190151771e-07</v>
       </c>
       <c r="FI17" t="n">
-        <v>6.225890683708712e-05</v>
+        <v>5.164989147488086e-07</v>
       </c>
       <c r="FJ17" t="n">
-        <v>4.586735667544417e-05</v>
+        <v>2.998329478032247e-07</v>
       </c>
       <c r="FK17" t="n">
-        <v>6.813063464505831e-07</v>
+        <v>2.497840796422679e-07</v>
       </c>
       <c r="FL17" t="n">
-        <v>2.988291089423001e-05</v>
+        <v>2.680392583442881e-07</v>
       </c>
       <c r="FM17" t="n">
-        <v>1.414047619618941e-05</v>
+        <v>7.961473613704584e-08</v>
       </c>
       <c r="FN17" t="n">
-        <v>4.590324169839732e-05</v>
+        <v>2.846574602699548e-07</v>
       </c>
       <c r="FO17" t="n">
-        <v>2.452815533615649e-05</v>
+        <v>5.295660798765311e-07</v>
       </c>
       <c r="FP17" t="n">
-        <v>7.47887816032744e-06</v>
+        <v>9.112922043641447e-07</v>
       </c>
       <c r="FQ17" t="n">
-        <v>5.507817149918992e-06</v>
+        <v>3.874995400110492e-07</v>
       </c>
       <c r="FR17" t="n">
-        <v>4.898054612567648e-06</v>
+        <v>2.774416145712166e-07</v>
       </c>
       <c r="FS17" t="n">
-        <v>8.531941602996085e-06</v>
+        <v>2.54032244129121e-07</v>
       </c>
       <c r="FT17" t="n">
-        <v>5.783413871540688e-05</v>
+        <v>1.227338429998781e-06</v>
       </c>
       <c r="FU17" t="n">
-        <v>4.279172571841627e-07</v>
+        <v>2.795661373511393e-07</v>
       </c>
       <c r="FV17" t="n">
-        <v>3.663825191324577e-05</v>
+        <v>3.848538767670107e-07</v>
       </c>
       <c r="FW17" t="n">
-        <v>4.426034502102993e-05</v>
+        <v>3.16736930017214e-07</v>
       </c>
       <c r="FX17" t="n">
-        <v>3.33032148773782e-05</v>
+        <v>9.710538506624289e-08</v>
       </c>
       <c r="FY17" t="n">
-        <v>6.422966544050723e-05</v>
+        <v>3.072618142141437e-07</v>
       </c>
       <c r="FZ17" t="n">
-        <v>2.827833304763772e-05</v>
+        <v>1.819695967242296e-07</v>
       </c>
       <c r="GA17" t="n">
-        <v>5.087421868665842e-06</v>
+        <v>8.184917987819063e-07</v>
       </c>
       <c r="GB17" t="n">
-        <v>5.48431626157253e-06</v>
+        <v>3.749642587536073e-07</v>
       </c>
       <c r="GC17" t="n">
-        <v>7.776456186547875e-05</v>
+        <v>8.43853626975033e-07</v>
       </c>
       <c r="GD17" t="n">
-        <v>4.688126500695944e-05</v>
+        <v>7.319922588067129e-07</v>
       </c>
       <c r="GE17" t="n">
-        <v>9.919614967657253e-05</v>
+        <v>9.044662192536634e-07</v>
       </c>
       <c r="GF17" t="n">
-        <v>1.980873821594287e-05</v>
+        <v>4.292052153687109e-07</v>
       </c>
       <c r="GG17" t="n">
-        <v>4.861117486143485e-05</v>
+        <v>7.557185455198123e-08</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0.0001127168216044083</v>
+        <v>1.793273529671069e-09</v>
       </c>
       <c r="B18" t="n">
-        <v>0.002944689942523837</v>
+        <v>2.384829445034597e-09</v>
       </c>
       <c r="C18" t="n">
-        <v>1.498403435107321e-05</v>
+        <v>1.303877561475986e-09</v>
       </c>
       <c r="D18" t="n">
-        <v>0.00141638983041048</v>
+        <v>1.662524562462409e-10</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0002926437300629914</v>
+        <v>2.861945680443512e-10</v>
       </c>
       <c r="F18" t="n">
-        <v>0.001894774613901973</v>
+        <v>3.454092567523048e-10</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0001137079525506124</v>
+        <v>2.560448741917298e-09</v>
       </c>
       <c r="H18" t="n">
-        <v>0.001147500006482005</v>
+        <v>3.661636327478845e-09</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0001296392147196457</v>
+        <v>2.55418064476487e-09</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0004295097023714334</v>
+        <v>1.706110697163865e-09</v>
       </c>
       <c r="K18" t="n">
-        <v>0.002793787280097604</v>
+        <v>1.924160386579388e-09</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0001663427538005635</v>
+        <v>1.643943647877677e-09</v>
       </c>
       <c r="M18" t="n">
-        <v>0.001011669053696096</v>
+        <v>1.057631870970965e-09</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0001940586953423917</v>
+        <v>5.070421860153829e-10</v>
       </c>
       <c r="O18" t="n">
-        <v>0.001870084088295698</v>
+        <v>1.8498576281889e-10</v>
       </c>
       <c r="P18" t="n">
-        <v>1.324342156294733e-05</v>
+        <v>1.494224854958759e-09</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.0003989445976912975</v>
+        <v>3.294465589220863e-09</v>
       </c>
       <c r="R18" t="n">
-        <v>0.0002862340188585222</v>
+        <v>8.92552864950602e-10</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0001401053159497678</v>
+        <v>2.049045377816583e-09</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0002712109999265522</v>
+        <v>2.45608489102267e-09</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0002490077749826014</v>
+        <v>3.896808153935893e-10</v>
       </c>
       <c r="V18" t="n">
-        <v>0.0002226656652055681</v>
+        <v>8.479972279928916e-10</v>
       </c>
       <c r="W18" t="n">
-        <v>0.0003833667142316699</v>
+        <v>2.71035749399573e-10</v>
       </c>
       <c r="X18" t="n">
-        <v>0.0002230819809483364</v>
+        <v>1.016028372546884e-09</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.0001721523294690996</v>
+        <v>9.022001895564458e-11</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.0004890099517069757</v>
+        <v>1.208126820806399e-09</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.0003892708627972752</v>
+        <v>2.093606621400568e-09</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.0001041484501911327</v>
+        <v>1.966280471776827e-09</v>
       </c>
       <c r="AC18" t="n">
-        <v>5.969993071630597e-05</v>
+        <v>5.62713986518304e-10</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.0001049902566592209</v>
+        <v>8.665859141387955e-10</v>
       </c>
       <c r="AE18" t="n">
-        <v>3.424633541726507e-05</v>
+        <v>1.215877176719005e-09</v>
       </c>
       <c r="AF18" t="n">
-        <v>4.305804031901062e-05</v>
+        <v>8.477281099317224e-10</v>
       </c>
       <c r="AG18" t="n">
-        <v>8.483503188472241e-05</v>
+        <v>1.701233598438989e-09</v>
       </c>
       <c r="AH18" t="n">
-        <v>0.0001538851065561175</v>
+        <v>3.72917058344413e-10</v>
       </c>
       <c r="AI18" t="n">
-        <v>0.0002240717585664243</v>
+        <v>9.075047935347413e-10</v>
       </c>
       <c r="AJ18" t="n">
-        <v>3.239999205106869e-05</v>
+        <v>2.044958424818333e-09</v>
       </c>
       <c r="AK18" t="n">
-        <v>0.0002440833195578307</v>
+        <v>1.717824771318988e-09</v>
       </c>
       <c r="AL18" t="n">
-        <v>0.0005180257139727473</v>
+        <v>1.51272683268644e-09</v>
       </c>
       <c r="AM18" t="n">
-        <v>4.663021900341846e-05</v>
+        <v>1.68453329063567e-09</v>
       </c>
       <c r="AN18" t="n">
-        <v>0.000161785603268072</v>
+        <v>4.287914745493282e-10</v>
       </c>
       <c r="AO18" t="n">
-        <v>4.75545457447879e-05</v>
+        <v>8.128622219771842e-10</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.0003143370558973402</v>
+        <v>6.636355354139312e-11</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.0001357361325062811</v>
+        <v>3.738553910892506e-11</v>
       </c>
       <c r="AR18" t="n">
-        <v>0.0001323686738032848</v>
+        <v>2.639779228541528e-10</v>
       </c>
       <c r="AS18" t="n">
-        <v>0.0003382745489943773</v>
+        <v>1.04737751804862e-09</v>
       </c>
       <c r="AT18" t="n">
-        <v>0.0004163339035585523</v>
+        <v>8.856760880249226e-10</v>
       </c>
       <c r="AU18" t="n">
-        <v>0.001850805361755192</v>
+        <v>1.557784345962432e-09</v>
       </c>
       <c r="AV18" t="n">
-        <v>5.317186878528446e-05</v>
+        <v>1.165657681490018e-09</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.0003933737461920828</v>
+        <v>2.452250069673312e-10</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.0001270701177418232</v>
+        <v>1.125740278773435e-09</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.0009859914425760508</v>
+        <v>1.018508610783897e-09</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.0004804204218089581</v>
+        <v>7.898650622450987e-10</v>
       </c>
       <c r="BA18" t="n">
-        <v>0.0003022818418685347</v>
+        <v>2.7106109024011e-10</v>
       </c>
       <c r="BB18" t="n">
-        <v>0.0006775622605346143</v>
+        <v>1.139261601723618e-11</v>
       </c>
       <c r="BC18" t="n">
-        <v>0.0002184918557759374</v>
+        <v>5.018098825360084e-09</v>
       </c>
       <c r="BD18" t="n">
-        <v>0.0006845276802778244</v>
+        <v>4.121808672152838e-09</v>
       </c>
       <c r="BE18" t="n">
-        <v>0.000470369472168386</v>
+        <v>1.703795771135219e-09</v>
       </c>
       <c r="BF18" t="n">
-        <v>5.690490070264786e-06</v>
+        <v>4.487687998988577e-12</v>
       </c>
       <c r="BG18" t="n">
-        <v>0.000359762052539736</v>
+        <v>3.635886924868714e-09</v>
       </c>
       <c r="BH18" t="n">
-        <v>0.0005288240499794483</v>
+        <v>1.508806191097278e-09</v>
       </c>
       <c r="BI18" t="n">
-        <v>0.0002667436783667654</v>
+        <v>1.217677347842283e-10</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.0002178059366997331</v>
+        <v>4.529757013926883e-09</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.0004607352311722934</v>
+        <v>5.432210681277638e-09</v>
       </c>
       <c r="BL18" t="n">
-        <v>4.027061368105933e-05</v>
+        <v>4.260732600069872e-10</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.0004451006243471056</v>
+        <v>1.068460209197042e-09</v>
       </c>
       <c r="BN18" t="n">
-        <v>0.0002057670790236443</v>
+        <v>1.170253893789663e-10</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.503691601101309e-05</v>
+        <v>1.295218599040027e-09</v>
       </c>
       <c r="BP18" t="n">
-        <v>1.667926335358061e-05</v>
+        <v>3.449593943827267e-10</v>
       </c>
       <c r="BQ18" t="n">
-        <v>0.0001033940789056942</v>
+        <v>1.419144357583946e-09</v>
       </c>
       <c r="BR18" t="n">
-        <v>0.0004019609477836639</v>
+        <v>1.197101306971149e-10</v>
       </c>
       <c r="BS18" t="n">
-        <v>0.0002185769553761929</v>
+        <v>1.452348796782132e-09</v>
       </c>
       <c r="BT18" t="n">
-        <v>0.0002001971151912585</v>
+        <v>1.639242963591414e-09</v>
       </c>
       <c r="BU18" t="n">
-        <v>0.000149001061799936</v>
+        <v>3.07156833301292e-09</v>
       </c>
       <c r="BV18" t="n">
-        <v>0.001013225060887635</v>
+        <v>2.292330547604138e-09</v>
       </c>
       <c r="BW18" t="n">
-        <v>0.0002238885790575296</v>
+        <v>7.451516070844377e-10</v>
       </c>
       <c r="BX18" t="n">
-        <v>0.0001865222293417901</v>
+        <v>8.604048029603462e-10</v>
       </c>
       <c r="BY18" t="n">
-        <v>0.0002044246793957427</v>
+        <v>9.269152806412606e-11</v>
       </c>
       <c r="BZ18" t="n">
-        <v>0.0005086445016786456</v>
+        <v>1.000199256750989e-09</v>
       </c>
       <c r="CA18" t="n">
-        <v>0.0001122864341596141</v>
+        <v>8.322200706345484e-10</v>
       </c>
       <c r="CB18" t="n">
-        <v>6.418143311748281e-05</v>
+        <v>8.594660538818744e-10</v>
       </c>
       <c r="CC18" t="n">
-        <v>0.0004653797950595617</v>
+        <v>6.132375163225845e-10</v>
       </c>
       <c r="CD18" t="n">
-        <v>1.707663614070043e-05</v>
+        <v>3.262913550461377e-11</v>
       </c>
       <c r="CE18" t="n">
-        <v>0.00043781942804344</v>
+        <v>2.527235087868007e-10</v>
       </c>
       <c r="CF18" t="n">
-        <v>0.0002557144034653902</v>
+        <v>2.5991744867504e-10</v>
       </c>
       <c r="CG18" t="n">
-        <v>0.0001521440863143653</v>
+        <v>2.163801637866669e-10</v>
       </c>
       <c r="CH18" t="n">
-        <v>0.0001739964645821601</v>
+        <v>2.100867951826402e-10</v>
       </c>
       <c r="CI18" t="n">
-        <v>0.000231744023039937</v>
+        <v>4.433928779690177e-10</v>
       </c>
       <c r="CJ18" t="n">
-        <v>0.000202635710593313</v>
+        <v>2.345998742492306e-11</v>
       </c>
       <c r="CK18" t="n">
-        <v>0.0001234422670677304</v>
+        <v>2.136627819115944e-10</v>
       </c>
       <c r="CL18" t="n">
-        <v>0.0002393354661762714</v>
+        <v>5.039851314059263e-10</v>
       </c>
       <c r="CM18" t="n">
-        <v>0.0005687858210876584</v>
+        <v>2.829302347961971e-10</v>
       </c>
       <c r="CN18" t="n">
-        <v>0.0001510048459749669</v>
+        <v>7.269402857446039e-10</v>
       </c>
       <c r="CO18" t="n">
-        <v>0.0001173322962131351</v>
+        <v>1.223599443989087e-09</v>
       </c>
       <c r="CP18" t="n">
-        <v>0.0009491594973951578</v>
+        <v>4.792669594522181e-10</v>
       </c>
       <c r="CQ18" t="n">
-        <v>0.0001728001661831513</v>
+        <v>3.689683003571531e-09</v>
       </c>
       <c r="CR18" t="n">
-        <v>0.0003274620103184134</v>
+        <v>1.079455066999024e-10</v>
       </c>
       <c r="CS18" t="n">
-        <v>0.0006054230034351349</v>
+        <v>3.416702698544327e-09</v>
       </c>
       <c r="CT18" t="n">
-        <v>0.0005762487999163568</v>
+        <v>9.302061898530667e-10</v>
       </c>
       <c r="CU18" t="n">
-        <v>0.0001321404415648431</v>
+        <v>1.93804350345772e-09</v>
       </c>
       <c r="CV18" t="n">
-        <v>3.063718031626195e-05</v>
+        <v>4.452579971392367e-10</v>
       </c>
       <c r="CW18" t="n">
-        <v>0.0003894262772519141</v>
+        <v>3.161948480823185e-10</v>
       </c>
       <c r="CX18" t="n">
-        <v>0.0002382185048190877</v>
+        <v>3.469222131791128e-11</v>
       </c>
       <c r="CY18" t="n">
-        <v>0.000313062162604183</v>
+        <v>2.876057725309522e-10</v>
       </c>
       <c r="CZ18" t="n">
-        <v>0.0001894470333354548</v>
+        <v>8.616998781185714e-11</v>
       </c>
       <c r="DA18" t="n">
-        <v>0.0001821069454308599</v>
+        <v>2.142428873197488e-10</v>
       </c>
       <c r="DB18" t="n">
-        <v>0.0002083008730551228</v>
+        <v>1.45756975933331e-10</v>
       </c>
       <c r="DC18" t="n">
-        <v>0.0002793656894937158</v>
+        <v>1.603248228621013e-10</v>
       </c>
       <c r="DD18" t="n">
-        <v>0.0001461643259972334</v>
+        <v>5.465409236293794e-10</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.0001522958918940276</v>
+        <v>8.476194190976116e-10</v>
       </c>
       <c r="DF18" t="n">
-        <v>0.0002213429543189704</v>
+        <v>2.155412071047635e-09</v>
       </c>
       <c r="DG18" t="n">
-        <v>0.0001161384861916304</v>
+        <v>3.32825433879691e-09</v>
       </c>
       <c r="DH18" t="n">
-        <v>0.0007896851166151464</v>
+        <v>2.417081534922261e-10</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.0005905930884182453</v>
+        <v>4.570124001457287e-10</v>
       </c>
       <c r="DJ18" t="n">
-        <v>0.0006126686348579824</v>
+        <v>2.793398845568618e-10</v>
       </c>
       <c r="DK18" t="n">
-        <v>0.000258064828813076</v>
+        <v>2.443036328791948e-10</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.0004960763035342097</v>
+        <v>1.646827896273351e-09</v>
       </c>
       <c r="DM18" t="n">
-        <v>0.0005068129976280034</v>
+        <v>9.730307670707816e-10</v>
       </c>
       <c r="DN18" t="n">
-        <v>2.240287176391575e-05</v>
+        <v>1.464892984692767e-09</v>
       </c>
       <c r="DO18" t="n">
-        <v>7.424500654451549e-05</v>
+        <v>2.112794383890559e-09</v>
       </c>
       <c r="DP18" t="n">
-        <v>0.0002975109382532537</v>
+        <v>1.450001785308075e-10</v>
       </c>
       <c r="DQ18" t="n">
-        <v>3.891338928951882e-05</v>
+        <v>7.009256369761019e-11</v>
       </c>
       <c r="DR18" t="n">
-        <v>0.000106747895188164</v>
+        <v>1.331740051568886e-09</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.0001906333927763626</v>
+        <v>1.270668570363398e-09</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.0003231667797081172</v>
+        <v>4.335802827881707e-10</v>
       </c>
       <c r="DU18" t="n">
-        <v>4.541871385299601e-05</v>
+        <v>2.911623164791877e-10</v>
       </c>
       <c r="DV18" t="n">
-        <v>3.041845047846437e-06</v>
+        <v>7.520452038889403e-10</v>
       </c>
       <c r="DW18" t="n">
-        <v>7.259455742314458e-06</v>
+        <v>9.5758234675003e-10</v>
       </c>
       <c r="DX18" t="n">
-        <v>0.0002921777777373791</v>
+        <v>5.544656400680026e-10</v>
       </c>
       <c r="DY18" t="n">
-        <v>0.0002312680881004781</v>
+        <v>7.897393849987111e-10</v>
       </c>
       <c r="DZ18" t="n">
-        <v>0.0003281287790741771</v>
+        <v>1.080405542808194e-09</v>
       </c>
       <c r="EA18" t="n">
-        <v>0.000149851170135662</v>
+        <v>1.302170815620229e-09</v>
       </c>
       <c r="EB18" t="n">
-        <v>0.0001543551188660786</v>
+        <v>7.872039131662234e-11</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.854301419574767e-05</v>
+        <v>1.976980357198954e-09</v>
       </c>
       <c r="ED18" t="n">
-        <v>6.149060209281743e-05</v>
+        <v>1.764193013897852e-09</v>
       </c>
       <c r="EE18" t="n">
-        <v>0.0002901730185840279</v>
+        <v>2.095981610494846e-09</v>
       </c>
       <c r="EF18" t="n">
-        <v>0.0001870728738140315</v>
+        <v>7.216204300775075e-10</v>
       </c>
       <c r="EG18" t="n">
-        <v>0.0005058028036728501</v>
+        <v>3.792841041239114e-11</v>
       </c>
       <c r="EH18" t="n">
-        <v>0.0001277402916457504</v>
+        <v>3.571218321063441e-10</v>
       </c>
       <c r="EI18" t="n">
-        <v>8.530612831236795e-05</v>
+        <v>6.907149158186243e-11</v>
       </c>
       <c r="EJ18" t="n">
-        <v>8.826842531561852e-06</v>
+        <v>1.077547939765111e-09</v>
       </c>
       <c r="EK18" t="n">
-        <v>9.90509579423815e-05</v>
+        <v>1.429161677890534e-09</v>
       </c>
       <c r="EL18" t="n">
-        <v>0.0002605983172543347</v>
+        <v>1.043560127200749e-09</v>
       </c>
       <c r="EM18" t="n">
-        <v>0.0001059943315340206</v>
+        <v>2.899392184674277e-11</v>
       </c>
       <c r="EN18" t="n">
-        <v>0.0001381750626023859</v>
+        <v>8.779066917874445e-10</v>
       </c>
       <c r="EO18" t="n">
-        <v>7.965932309161872e-05</v>
+        <v>3.661548286792993e-10</v>
       </c>
       <c r="EP18" t="n">
-        <v>0.0001693708472885191</v>
+        <v>3.983285923325752e-12</v>
       </c>
       <c r="EQ18" t="n">
-        <v>0.000262957822997123</v>
+        <v>6.775257022084702e-10</v>
       </c>
       <c r="ER18" t="n">
-        <v>0.0003585810482036322</v>
+        <v>2.070992266567373e-10</v>
       </c>
       <c r="ES18" t="n">
-        <v>0.0003869709034916013</v>
+        <v>3.827691774649367e-10</v>
       </c>
       <c r="ET18" t="n">
-        <v>0.0003347900055814534</v>
+        <v>9.619798291282677e-10</v>
       </c>
       <c r="EU18" t="n">
-        <v>0.0006096265278756618</v>
+        <v>7.548487945818749e-10</v>
       </c>
       <c r="EV18" t="n">
-        <v>0.0007073567830957472</v>
+        <v>1.61466517933917e-09</v>
       </c>
       <c r="EW18" t="n">
-        <v>6.676313932985067e-05</v>
+        <v>4.053851698770927e-10</v>
       </c>
       <c r="EX18" t="n">
-        <v>7.824660133337602e-05</v>
+        <v>3.342817411766674e-10</v>
       </c>
       <c r="EY18" t="n">
-        <v>0.0003918937582056969</v>
+        <v>3.948020521615803e-10</v>
       </c>
       <c r="EZ18" t="n">
-        <v>0.0001951446174643934</v>
+        <v>1.348101352771636e-10</v>
       </c>
       <c r="FA18" t="n">
-        <v>0.0001275360118597746</v>
+        <v>3.613380705758118e-10</v>
       </c>
       <c r="FB18" t="n">
-        <v>0.0001704374881228432</v>
+        <v>1.948922551120447e-10</v>
       </c>
       <c r="FC18" t="n">
-        <v>0.000183706171810627</v>
+        <v>5.585690798781684e-10</v>
       </c>
       <c r="FD18" t="n">
-        <v>0.0003731484466698021</v>
+        <v>2.775762952822447e-10</v>
       </c>
       <c r="FE18" t="n">
-        <v>0.0002252680569654331</v>
+        <v>2.598820325605544e-10</v>
       </c>
       <c r="FF18" t="n">
-        <v>0.000266029528575018</v>
+        <v>4.080865645406107e-10</v>
       </c>
       <c r="FG18" t="n">
-        <v>7.550418376922607e-05</v>
+        <v>2.374224150614168e-10</v>
       </c>
       <c r="FH18" t="n">
-        <v>9.998406312661245e-05</v>
+        <v>1.901848262209072e-10</v>
       </c>
       <c r="FI18" t="n">
-        <v>0.0003071638639084995</v>
+        <v>1.106628788605235e-09</v>
       </c>
       <c r="FJ18" t="n">
-        <v>0.0004240829148329794</v>
+        <v>5.463833274710339e-10</v>
       </c>
       <c r="FK18" t="n">
-        <v>1.118220097851008e-05</v>
+        <v>2.403585663834917e-10</v>
       </c>
       <c r="FL18" t="n">
-        <v>5.717105523217469e-05</v>
+        <v>1.956302009276101e-09</v>
       </c>
       <c r="FM18" t="n">
-        <v>0.0002257265732623637</v>
+        <v>4.824257660018816e-10</v>
       </c>
       <c r="FN18" t="n">
-        <v>6.079641752876341e-05</v>
+        <v>2.782817587476671e-10</v>
       </c>
       <c r="FO18" t="n">
-        <v>0.000345197826391086</v>
+        <v>2.576377999830015e-09</v>
       </c>
       <c r="FP18" t="n">
-        <v>0.0003050802915822715</v>
+        <v>3.950859195356315e-09</v>
       </c>
       <c r="FQ18" t="n">
-        <v>0.000434919202234596</v>
+        <v>6.225787663183269e-10</v>
       </c>
       <c r="FR18" t="n">
-        <v>0.0002511414350010455</v>
+        <v>1.13027920356501e-10</v>
       </c>
       <c r="FS18" t="n">
-        <v>0.0002872783225029707</v>
+        <v>3.762307798638176e-09</v>
       </c>
       <c r="FT18" t="n">
-        <v>0.000116741270176135</v>
+        <v>5.230837096803498e-09</v>
       </c>
       <c r="FU18" t="n">
-        <v>0.0004089983412995934</v>
+        <v>2.019049788470895e-10</v>
       </c>
       <c r="FV18" t="n">
-        <v>0.0004194100620225072</v>
+        <v>5.048952367303627e-10</v>
       </c>
       <c r="FW18" t="n">
-        <v>0.0003814916126430035</v>
+        <v>2.77741407650467e-09</v>
       </c>
       <c r="FX18" t="n">
-        <v>0.0001091506346710958</v>
+        <v>1.736822130560256e-09</v>
       </c>
       <c r="FY18" t="n">
-        <v>0.0006044681067578495</v>
+        <v>1.514693259707656e-09</v>
       </c>
       <c r="FZ18" t="n">
-        <v>0.0002085015585180372</v>
+        <v>2.054626468961374e-09</v>
       </c>
       <c r="GA18" t="n">
-        <v>0.0001774251140886918</v>
+        <v>2.464641379873456e-09</v>
       </c>
       <c r="GB18" t="n">
-        <v>0.0002003666886594146</v>
+        <v>8.85141848705473e-10</v>
       </c>
       <c r="GC18" t="n">
-        <v>8.001503010746092e-05</v>
+        <v>9.614725682283165e-10</v>
       </c>
       <c r="GD18" t="n">
-        <v>0.0003490187809802592</v>
+        <v>5.827221483123424e-10</v>
       </c>
       <c r="GE18" t="n">
-        <v>0.0008567256736569107</v>
+        <v>1.23270582630397e-09</v>
       </c>
       <c r="GF18" t="n">
-        <v>8.090276969596744e-05</v>
+        <v>1.787985315360174e-09</v>
       </c>
       <c r="GG18" t="n">
-        <v>1.013339351629838e-05</v>
+        <v>1.038917951667884e-09</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2.809473244269611e-06</v>
+        <v>7.666378110116057e-08</v>
       </c>
       <c r="B19" t="n">
-        <v>1.658105065871496e-05</v>
+        <v>1.142393131203789e-07</v>
       </c>
       <c r="C19" t="n">
-        <v>1.605075112820487e-06</v>
+        <v>6.666982699243817e-08</v>
       </c>
       <c r="D19" t="n">
-        <v>1.32879322336521e-05</v>
+        <v>9.207350615270116e-08</v>
       </c>
       <c r="E19" t="n">
-        <v>6.22611514700111e-06</v>
+        <v>1.335000234803374e-07</v>
       </c>
       <c r="F19" t="n">
-        <v>2.223194542239071e-06</v>
+        <v>1.286963424718124e-07</v>
       </c>
       <c r="G19" t="n">
-        <v>8.398512818530435e-07</v>
+        <v>1.311272512793948e-07</v>
       </c>
       <c r="H19" t="n">
-        <v>2.130318989657098e-06</v>
+        <v>2.169415154185117e-07</v>
       </c>
       <c r="I19" t="n">
-        <v>1.094757521968859e-06</v>
+        <v>1.133433187305855e-07</v>
       </c>
       <c r="J19" t="n">
-        <v>3.828065473499009e-06</v>
+        <v>5.397252778038819e-08</v>
       </c>
       <c r="K19" t="n">
-        <v>1.241134486917872e-05</v>
+        <v>7.538301360909827e-08</v>
       </c>
       <c r="L19" t="n">
-        <v>1.159369844572211e-06</v>
+        <v>1.491211065740572e-08</v>
       </c>
       <c r="M19" t="n">
-        <v>1.002973112917971e-05</v>
+        <v>2.057678614164615e-07</v>
       </c>
       <c r="N19" t="n">
-        <v>8.280100701085757e-06</v>
+        <v>2.513957895189378e-07</v>
       </c>
       <c r="O19" t="n">
-        <v>8.352429176738951e-06</v>
+        <v>1.423844651071704e-07</v>
       </c>
       <c r="P19" t="n">
-        <v>1.777254055923549e-06</v>
+        <v>1.491587937607619e-07</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.003791905735852e-06</v>
+        <v>1.973313032976876e-07</v>
       </c>
       <c r="R19" t="n">
-        <v>6.815682809246937e-07</v>
+        <v>7.097307985759471e-08</v>
       </c>
       <c r="S19" t="n">
-        <v>6.895140813867329e-08</v>
+        <v>1.843956454194995e-08</v>
       </c>
       <c r="T19" t="n">
-        <v>3.878578809235478e-06</v>
+        <v>3.11217362991556e-08</v>
       </c>
       <c r="U19" t="n">
-        <v>4.591151423483097e-07</v>
+        <v>6.276657416037779e-08</v>
       </c>
       <c r="V19" t="n">
-        <v>1.505763520981418e-06</v>
+        <v>4.70584726741663e-09</v>
       </c>
       <c r="W19" t="n">
-        <v>2.640689444888267e-06</v>
+        <v>1.275452987670178e-08</v>
       </c>
       <c r="X19" t="n">
-        <v>2.468265392963076e-06</v>
+        <v>1.828394502467745e-08</v>
       </c>
       <c r="Y19" t="n">
-        <v>3.219713562430115e-06</v>
+        <v>1.332370325179966e-09</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.567921913192549e-06</v>
+        <v>4.874821968314791e-08</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.478800181255792e-06</v>
+        <v>1.346854716643975e-08</v>
       </c>
       <c r="AB19" t="n">
-        <v>3.984489467256935e-07</v>
+        <v>4.153099553150241e-08</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.431965185678564e-06</v>
+        <v>8.077962831976038e-08</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.809280774978106e-06</v>
+        <v>4.737391634535015e-08</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.185483142762678e-06</v>
+        <v>3.38214931616676e-08</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.133084083448921e-06</v>
+        <v>7.312953442806247e-08</v>
       </c>
       <c r="AG19" t="n">
-        <v>9.486973340244731e-07</v>
+        <v>1.107517135778835e-07</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.22671042138245e-06</v>
+        <v>3.254137403985169e-09</v>
       </c>
       <c r="AI19" t="n">
-        <v>5.360205364013382e-07</v>
+        <v>1.523067396647093e-07</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.450937503477689e-07</v>
+        <v>4.317388402341749e-08</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.443326593493111e-06</v>
+        <v>2.199340620734347e-08</v>
       </c>
       <c r="AL19" t="n">
-        <v>2.041759671556065e-06</v>
+        <v>1.205190613973173e-09</v>
       </c>
       <c r="AM19" t="n">
-        <v>5.144946726431954e-07</v>
+        <v>7.529398260430753e-08</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.061771740751283e-06</v>
+        <v>2.361327577915517e-09</v>
       </c>
       <c r="AO19" t="n">
-        <v>2.21239315578714e-06</v>
+        <v>5.973059558073146e-08</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.200173045390329e-07</v>
+        <v>1.214316203146382e-08</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.775652208380052e-06</v>
+        <v>1.267436999796701e-08</v>
       </c>
       <c r="AR19" t="n">
-        <v>7.75310468270618e-07</v>
+        <v>5.439726180611615e-08</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.284649670196814e-06</v>
+        <v>5.127210211952615e-09</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.178708998850198e-06</v>
+        <v>4.252233765100755e-08</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.331370276602684e-05</v>
+        <v>9.398021916240396e-08</v>
       </c>
       <c r="AV19" t="n">
-        <v>2.574056907178601e-06</v>
+        <v>7.300906190721435e-08</v>
       </c>
       <c r="AW19" t="n">
-        <v>3.190767074556788e-06</v>
+        <v>4.131797126660786e-08</v>
       </c>
       <c r="AX19" t="n">
-        <v>2.370091749526182e-07</v>
+        <v>2.608620093269565e-07</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.698324751941982e-07</v>
+        <v>2.224664115146879e-07</v>
       </c>
       <c r="AZ19" t="n">
-        <v>3.269332182753715e-07</v>
+        <v>5.142092618370953e-08</v>
       </c>
       <c r="BA19" t="n">
-        <v>4.538101165962871e-06</v>
+        <v>4.602244985107973e-08</v>
       </c>
       <c r="BB19" t="n">
-        <v>9.294667506765109e-07</v>
+        <v>8.630051340219325e-09</v>
       </c>
       <c r="BC19" t="n">
-        <v>7.504449968109839e-07</v>
+        <v>1.558508699872618e-08</v>
       </c>
       <c r="BD19" t="n">
-        <v>3.340929879414034e-07</v>
+        <v>1.499589217246466e-07</v>
       </c>
       <c r="BE19" t="n">
-        <v>6.515310360555304e-06</v>
+        <v>2.675900390158858e-09</v>
       </c>
       <c r="BF19" t="n">
-        <v>2.645339691298432e-06</v>
+        <v>9.812899293137889e-08</v>
       </c>
       <c r="BG19" t="n">
-        <v>6.591756118723424e-06</v>
+        <v>8.939556295217699e-08</v>
       </c>
       <c r="BH19" t="n">
-        <v>2.827209527822561e-06</v>
+        <v>1.121560373462671e-07</v>
       </c>
       <c r="BI19" t="n">
-        <v>1.662858153395064e-06</v>
+        <v>1.136353677821944e-09</v>
       </c>
       <c r="BJ19" t="n">
-        <v>3.237367081965203e-06</v>
+        <v>1.530198545651729e-07</v>
       </c>
       <c r="BK19" t="n">
-        <v>2.02917163960592e-07</v>
+        <v>1.128953996953896e-07</v>
       </c>
       <c r="BL19" t="n">
-        <v>2.653547653608257e-06</v>
+        <v>3.774696111236153e-08</v>
       </c>
       <c r="BM19" t="n">
-        <v>4.667727353080409e-06</v>
+        <v>1.40971422979419e-07</v>
       </c>
       <c r="BN19" t="n">
-        <v>3.254913735872833e-06</v>
+        <v>3.354147537493191e-08</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.914081167342374e-06</v>
+        <v>5.713424400255462e-08</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.27467512054136e-06</v>
+        <v>6.767412230601622e-08</v>
       </c>
       <c r="BQ19" t="n">
-        <v>2.169065965063055e-06</v>
+        <v>3.681805527122606e-09</v>
       </c>
       <c r="BR19" t="n">
-        <v>7.402444452964119e-07</v>
+        <v>5.31133359515934e-08</v>
       </c>
       <c r="BS19" t="n">
-        <v>2.984867478517117e-06</v>
+        <v>8.477314139554437e-08</v>
       </c>
       <c r="BT19" t="n">
-        <v>2.047148427664069e-06</v>
+        <v>9.939686407278714e-09</v>
       </c>
       <c r="BU19" t="n">
-        <v>7.451351393683581e-07</v>
+        <v>1.143999739383617e-08</v>
       </c>
       <c r="BV19" t="n">
-        <v>6.710606157867005e-06</v>
+        <v>3.516134938763571e-08</v>
       </c>
       <c r="BW19" t="n">
-        <v>2.459396000631386e-06</v>
+        <v>7.791922485012037e-08</v>
       </c>
       <c r="BX19" t="n">
-        <v>1.465961418034567e-06</v>
+        <v>3.367996015413155e-08</v>
       </c>
       <c r="BY19" t="n">
-        <v>1.474168129789177e-07</v>
+        <v>4.429355016100089e-08</v>
       </c>
       <c r="BZ19" t="n">
-        <v>1.282732682739152e-06</v>
+        <v>7.478642061187202e-08</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.100333287875401e-06</v>
+        <v>5.113400192158224e-08</v>
       </c>
       <c r="CB19" t="n">
-        <v>1.165748471976258e-06</v>
+        <v>5.392017143890371e-08</v>
       </c>
       <c r="CC19" t="n">
-        <v>1.697987158877368e-06</v>
+        <v>1.881521072277792e-08</v>
       </c>
       <c r="CD19" t="n">
-        <v>1.699668246146757e-07</v>
+        <v>1.695892670738885e-08</v>
       </c>
       <c r="CE19" t="n">
-        <v>2.706833356569405e-06</v>
+        <v>2.223516126775849e-08</v>
       </c>
       <c r="CF19" t="n">
-        <v>1.99351802621095e-06</v>
+        <v>2.672535526215825e-09</v>
       </c>
       <c r="CG19" t="n">
-        <v>1.016632836581266e-06</v>
+        <v>4.258269470369669e-08</v>
       </c>
       <c r="CH19" t="n">
-        <v>3.712572151925997e-07</v>
+        <v>5.270984360095099e-08</v>
       </c>
       <c r="CI19" t="n">
-        <v>1.194514766211796e-06</v>
+        <v>5.013703230360989e-08</v>
       </c>
       <c r="CJ19" t="n">
-        <v>4.662415449274704e-07</v>
+        <v>4.870466696615949e-09</v>
       </c>
       <c r="CK19" t="n">
-        <v>5.907945705985185e-07</v>
+        <v>2.529981557586325e-09</v>
       </c>
       <c r="CL19" t="n">
-        <v>1.726179561956087e-06</v>
+        <v>2.685296074389498e-08</v>
       </c>
       <c r="CM19" t="n">
-        <v>3.896803718816955e-06</v>
+        <v>6.747257685901786e-08</v>
       </c>
       <c r="CN19" t="n">
-        <v>8.374228741558909e-07</v>
+        <v>1.467820283096444e-07</v>
       </c>
       <c r="CO19" t="n">
-        <v>1.735265414026799e-06</v>
+        <v>1.704007814851138e-07</v>
       </c>
       <c r="CP19" t="n">
-        <v>5.204315129958559e-06</v>
+        <v>7.928220924213747e-08</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3.590785354390391e-06</v>
+        <v>1.460927556706793e-08</v>
       </c>
       <c r="CR19" t="n">
-        <v>5.84658437219332e-07</v>
+        <v>2.108678209822301e-08</v>
       </c>
       <c r="CS19" t="n">
-        <v>3.449613359407522e-06</v>
+        <v>7.756336373176964e-08</v>
       </c>
       <c r="CT19" t="n">
-        <v>2.641771459366282e-07</v>
+        <v>2.913237118207235e-08</v>
       </c>
       <c r="CU19" t="n">
-        <v>1.19770004403108e-06</v>
+        <v>4.369183059793613e-08</v>
       </c>
       <c r="CV19" t="n">
-        <v>1.620220047016119e-07</v>
+        <v>1.143700689709704e-08</v>
       </c>
       <c r="CW19" t="n">
-        <v>2.274733787999139e-06</v>
+        <v>1.376211855586007e-08</v>
       </c>
       <c r="CX19" t="n">
-        <v>1.821907858357008e-06</v>
+        <v>3.24557536401926e-09</v>
       </c>
       <c r="CY19" t="n">
-        <v>2.093994680762989e-06</v>
+        <v>6.005127062280735e-08</v>
       </c>
       <c r="CZ19" t="n">
-        <v>1.07400137494551e-06</v>
+        <v>5.187101947967676e-08</v>
       </c>
       <c r="DA19" t="n">
-        <v>1.511067694082158e-06</v>
+        <v>5.420010040779744e-08</v>
       </c>
       <c r="DB19" t="n">
-        <v>1.092303591576638e-06</v>
+        <v>3.166989448466495e-10</v>
       </c>
       <c r="DC19" t="n">
-        <v>7.208464580799046e-07</v>
+        <v>4.274438580864626e-09</v>
       </c>
       <c r="DD19" t="n">
-        <v>1.220538251800463e-06</v>
+        <v>1.916687075720347e-08</v>
       </c>
       <c r="DE19" t="n">
-        <v>3.031518417628831e-06</v>
+        <v>2.352812344952326e-08</v>
       </c>
       <c r="DF19" t="n">
-        <v>3.221072120140889e-07</v>
+        <v>5.848043826972571e-09</v>
       </c>
       <c r="DG19" t="n">
-        <v>4.860785793425748e-06</v>
+        <v>3.576339224764524e-08</v>
       </c>
       <c r="DH19" t="n">
-        <v>7.570969501102809e-06</v>
+        <v>4.980568490964288e-08</v>
       </c>
       <c r="DI19" t="n">
-        <v>2.432720521028386e-06</v>
+        <v>1.863024756687537e-08</v>
       </c>
       <c r="DJ19" t="n">
-        <v>4.838684617425315e-07</v>
+        <v>1.301893064464821e-07</v>
       </c>
       <c r="DK19" t="n">
-        <v>8.364089580936707e-07</v>
+        <v>5.858970197891722e-09</v>
       </c>
       <c r="DL19" t="n">
-        <v>2.800397624014295e-06</v>
+        <v>4.649939810974502e-08</v>
       </c>
       <c r="DM19" t="n">
-        <v>9.829374221226317e-07</v>
+        <v>4.802363662292919e-08</v>
       </c>
       <c r="DN19" t="n">
-        <v>4.081823590240674e-07</v>
+        <v>4.201914904911064e-08</v>
       </c>
       <c r="DO19" t="n">
-        <v>5.601468728855252e-07</v>
+        <v>3.242634250000265e-08</v>
       </c>
       <c r="DP19" t="n">
-        <v>2.538873559387866e-06</v>
+        <v>3.587302899177303e-08</v>
       </c>
       <c r="DQ19" t="n">
-        <v>8.181287398656423e-07</v>
+        <v>1.201062893585458e-08</v>
       </c>
       <c r="DR19" t="n">
-        <v>5.066428343525331e-07</v>
+        <v>1.837563345929993e-08</v>
       </c>
       <c r="DS19" t="n">
-        <v>4.894052381132497e-07</v>
+        <v>1.904609980840632e-08</v>
       </c>
       <c r="DT19" t="n">
-        <v>4.803117690244108e-07</v>
+        <v>2.795776765651681e-08</v>
       </c>
       <c r="DU19" t="n">
-        <v>9.217226306645898e-07</v>
+        <v>9.967153857814992e-08</v>
       </c>
       <c r="DV19" t="n">
-        <v>2.551777242842945e-06</v>
+        <v>2.757466788239071e-08</v>
       </c>
       <c r="DW19" t="n">
-        <v>3.246645974286366e-07</v>
+        <v>7.45004236080149e-09</v>
       </c>
       <c r="DX19" t="n">
-        <v>3.581598321034107e-06</v>
+        <v>5.454862517240144e-08</v>
       </c>
       <c r="DY19" t="n">
-        <v>3.698319687828189e-06</v>
+        <v>1.733764420919215e-08</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.470144349648763e-08</v>
+        <v>3.711538099082645e-08</v>
       </c>
       <c r="EA19" t="n">
-        <v>1.202561065838381e-06</v>
+        <v>2.042419389169936e-08</v>
       </c>
       <c r="EB19" t="n">
-        <v>3.359319180162856e-06</v>
+        <v>5.464642782726514e-08</v>
       </c>
       <c r="EC19" t="n">
-        <v>7.601746574437129e-07</v>
+        <v>3.939147319442782e-08</v>
       </c>
       <c r="ED19" t="n">
-        <v>4.90560807975271e-07</v>
+        <v>8.908649107297606e-08</v>
       </c>
       <c r="EE19" t="n">
-        <v>6.324876267171931e-07</v>
+        <v>4.074786374985706e-08</v>
       </c>
       <c r="EF19" t="n">
-        <v>1.300747840105032e-06</v>
+        <v>1.78909509429559e-09</v>
       </c>
       <c r="EG19" t="n">
-        <v>1.682904212430003e-06</v>
+        <v>2.728243941874098e-08</v>
       </c>
       <c r="EH19" t="n">
-        <v>9.904517810355173e-07</v>
+        <v>2.249021413547325e-09</v>
       </c>
       <c r="EI19" t="n">
-        <v>1.479862589803815e-06</v>
+        <v>6.334451541079034e-08</v>
       </c>
       <c r="EJ19" t="n">
-        <v>2.116036284860456e-06</v>
+        <v>1.693055118323628e-08</v>
       </c>
       <c r="EK19" t="n">
-        <v>1.07140670024819e-06</v>
+        <v>8.43279650553086e-08</v>
       </c>
       <c r="EL19" t="n">
-        <v>1.600597784090496e-06</v>
+        <v>1.413357697543915e-08</v>
       </c>
       <c r="EM19" t="n">
-        <v>1.282399011870439e-06</v>
+        <v>3.010802984704242e-08</v>
       </c>
       <c r="EN19" t="n">
-        <v>5.887015959160635e-07</v>
+        <v>1.480539246756507e-08</v>
       </c>
       <c r="EO19" t="n">
-        <v>2.981901161547285e-07</v>
+        <v>3.371987133959919e-08</v>
       </c>
       <c r="EP19" t="n">
-        <v>9.577230457580299e-07</v>
+        <v>3.970955475551818e-08</v>
       </c>
       <c r="EQ19" t="n">
-        <v>2.396980107732816e-06</v>
+        <v>2.341771043745666e-08</v>
       </c>
       <c r="ER19" t="n">
-        <v>8.789331218395091e-08</v>
+        <v>2.85736856397989e-08</v>
       </c>
       <c r="ES19" t="n">
-        <v>1.868050617304107e-06</v>
+        <v>2.787458086572769e-08</v>
       </c>
       <c r="ET19" t="n">
-        <v>3.958626564326551e-07</v>
+        <v>7.817769542839414e-09</v>
       </c>
       <c r="EU19" t="n">
-        <v>1.253853383786918e-06</v>
+        <v>1.851905295779943e-08</v>
       </c>
       <c r="EV19" t="n">
-        <v>3.106696567556355e-06</v>
+        <v>7.268605273225148e-09</v>
       </c>
       <c r="EW19" t="n">
-        <v>1.211161702485697e-06</v>
+        <v>3.322644914760531e-08</v>
       </c>
       <c r="EX19" t="n">
-        <v>4.331501770593604e-07</v>
+        <v>1.608668043218131e-08</v>
       </c>
       <c r="EY19" t="n">
-        <v>2.164047828046023e-06</v>
+        <v>4.290904342951762e-08</v>
       </c>
       <c r="EZ19" t="n">
-        <v>1.599482970959798e-06</v>
+        <v>4.358436278550926e-09</v>
       </c>
       <c r="FA19" t="n">
-        <v>1.294003823204548e-06</v>
+        <v>5.068621433679255e-08</v>
       </c>
       <c r="FB19" t="n">
-        <v>5.680760750692571e-09</v>
+        <v>4.829842126241601e-08</v>
       </c>
       <c r="FC19" t="n">
-        <v>1.438951358068152e-06</v>
+        <v>5.794620605570344e-08</v>
       </c>
       <c r="FD19" t="n">
-        <v>8.006699658835714e-07</v>
+        <v>4.497165306815987e-09</v>
       </c>
       <c r="FE19" t="n">
-        <v>2.691105294161389e-07</v>
+        <v>8.498227010989012e-09</v>
       </c>
       <c r="FF19" t="n">
-        <v>1.930848384290584e-06</v>
+        <v>6.303824573450356e-09</v>
       </c>
       <c r="FG19" t="n">
-        <v>1.300948497373611e-06</v>
+        <v>5.824424675893169e-08</v>
       </c>
       <c r="FH19" t="n">
-        <v>1.608064394531539e-06</v>
+        <v>2.038168034346199e-08</v>
       </c>
       <c r="FI19" t="n">
-        <v>4.365230324765434e-06</v>
+        <v>3.523457792198315e-08</v>
       </c>
       <c r="FJ19" t="n">
-        <v>2.795230329866172e-06</v>
+        <v>1.030277019253845e-08</v>
       </c>
       <c r="FK19" t="n">
-        <v>7.644734409950615e-07</v>
+        <v>9.620501373319712e-08</v>
       </c>
       <c r="FL19" t="n">
-        <v>2.412725450540165e-07</v>
+        <v>3.053911257211439e-08</v>
       </c>
       <c r="FM19" t="n">
-        <v>9.829577720665839e-07</v>
+        <v>3.812516879975192e-08</v>
       </c>
       <c r="FN19" t="n">
-        <v>2.222478315161425e-06</v>
+        <v>7.333856899549573e-08</v>
       </c>
       <c r="FO19" t="n">
-        <v>1.936860599016654e-06</v>
+        <v>1.10916204221212e-07</v>
       </c>
       <c r="FP19" t="n">
-        <v>7.505830694753968e-07</v>
+        <v>8.43411029904928e-09</v>
       </c>
       <c r="FQ19" t="n">
-        <v>2.772993411781499e-06</v>
+        <v>1.121446047136487e-08</v>
       </c>
       <c r="FR19" t="n">
-        <v>1.430886982234369e-07</v>
+        <v>1.164857863500401e-07</v>
       </c>
       <c r="FS19" t="n">
-        <v>1.464575802856416e-07</v>
+        <v>4.967944988720774e-08</v>
       </c>
       <c r="FT19" t="n">
-        <v>3.865409325953806e-06</v>
+        <v>2.583567138003673e-08</v>
       </c>
       <c r="FU19" t="n">
-        <v>1.085606982087484e-06</v>
+        <v>2.533671228377443e-08</v>
       </c>
       <c r="FV19" t="n">
-        <v>2.746762220340315e-06</v>
+        <v>1.227571431172692e-07</v>
       </c>
       <c r="FW19" t="n">
-        <v>1.084993527911138e-06</v>
+        <v>1.650891476856486e-07</v>
       </c>
       <c r="FX19" t="n">
-        <v>2.35415541283146e-06</v>
+        <v>5.950145265387619e-08</v>
       </c>
       <c r="FY19" t="n">
-        <v>4.188178536423948e-06</v>
+        <v>2.006828481171397e-08</v>
       </c>
       <c r="FZ19" t="n">
-        <v>2.135103841283126e-06</v>
+        <v>7.2347930313299e-08</v>
       </c>
       <c r="GA19" t="n">
-        <v>9.346578622171364e-08</v>
+        <v>1.069696651256891e-07</v>
       </c>
       <c r="GB19" t="n">
-        <v>3.643971808742208e-07</v>
+        <v>7.64851293411084e-09</v>
       </c>
       <c r="GC19" t="n">
-        <v>5.334486559149809e-06</v>
+        <v>1.134008016379084e-07</v>
       </c>
       <c r="GD19" t="n">
-        <v>2.460961695760489e-06</v>
+        <v>1.268072082893923e-07</v>
       </c>
       <c r="GE19" t="n">
-        <v>5.809892627439694e-06</v>
+        <v>3.212984722722467e-08</v>
       </c>
       <c r="GF19" t="n">
-        <v>5.639505502585962e-07</v>
+        <v>2.953648881032223e-09</v>
       </c>
       <c r="GG19" t="n">
-        <v>2.144426616723649e-06</v>
+        <v>1.667858740006523e-09</v>
       </c>
     </row>
   </sheetData>
